--- a/doc/template_utilisateurs_kostango.xlsx
+++ b/doc/template_utilisateurs_kostango.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,66 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F7FB"/>
-        <bgColor rgb="00F2F7FB"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -93,37 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B0B0B0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,424 +417,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Import utilisateurs (Kostango)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Remplacer la ligne exemple par vos données. Conserver l'en-tête (ligne 4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>personne email</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Prénom</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nom</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Matricule</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Date de naissance</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Date d'embauche</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Date de sortie</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sexe</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Site (nom complet)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Type contrat</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Coefficient</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Forfait jour</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Tickets restaurant</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Agence d'intérim</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>valideur N+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>jean.dupont@isb.fr</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Jean</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>DUPONT</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>00000001</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>15/03/1985</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>01/09/2020</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>ISB France &gt; Paris</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Développeur</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>Cadre</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Marie MARTIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Description des colonnes :</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  personne email</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Email professionnel (clé de liaison)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prénom</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Prénom</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nom</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Matricule</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Matricule unique</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Date de naissance</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>JJ/MM/AAAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Date d'embauche</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>JJ/MM/AAAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Date de sortie</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>JJ/MM/AAAA (vide si actif)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sexe</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Homme / Femme</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Site (nom complet)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Chemin complet du site (ex: ISB France &gt; Paris)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Poste</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Intitulé du poste</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Type contrat</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>CDI / CDD / Intérim / Alternance / Stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Statut</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Statut RH (ex: Cadre, FJ-Cadre, Non-cadre)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Coefficient</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Forfait jour</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Tickets restaurant</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Agence d'intérim</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Nom de l'agence (intérim uniquement)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  valideur N+1</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Prénom Nom du N+1 (résolu automatiquement)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:Q1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/doc/template_utilisateurs_kostango.xlsx
+++ b/doc/template_utilisateurs_kostango.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -433,10 +433,8 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,20 +505,10 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Forfait jour</t>
+          <t>Agence d'intérim</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Tickets restaurant</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Agence d'intérim</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>valideur N+1</t>
         </is>

--- a/doc/template_utilisateurs_kostango.xlsx
+++ b/doc/template_utilisateurs_kostango.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -433,8 +433,10 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,30 +487,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Type contrat</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Coefficient</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Rôle</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Agence d'intérim</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>valideur N+1</t>
         </is>

--- a/doc/template_utilisateurs_kostango.xlsx
+++ b/doc/template_utilisateurs_kostango.xlsx
@@ -436,7 +436,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>valideur N+1</t>
+          <t>Matricule N+1</t>
         </is>
       </c>
     </row>

--- a/doc/template_utilisateurs_kostango.xlsx
+++ b/doc/template_utilisateurs_kostango.xlsx
@@ -49,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -526,6 +527,3998 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="D2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="D3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="D4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="D5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="D6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="D7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="D8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="D11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="D15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="D17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="2" t="n"/>
+      <c r="Q48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="2" t="n"/>
+      <c r="Q49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="2" t="n"/>
+      <c r="Q50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="2" t="n"/>
+      <c r="Q51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="2" t="n"/>
+      <c r="Q52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="2" t="n"/>
+      <c r="Q53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="2" t="n"/>
+      <c r="Q58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="2" t="n"/>
+      <c r="Q59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="2" t="n"/>
+      <c r="Q61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="2" t="n"/>
+      <c r="Q62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="2" t="n"/>
+      <c r="Q63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="2" t="n"/>
+      <c r="Q64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="2" t="n"/>
+      <c r="Q65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="2" t="n"/>
+      <c r="Q67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="2" t="n"/>
+      <c r="Q68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="2" t="n"/>
+      <c r="Q69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="2" t="n"/>
+      <c r="Q70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="2" t="n"/>
+      <c r="Q71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="2" t="n"/>
+      <c r="Q72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="2" t="n"/>
+      <c r="Q73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="2" t="n"/>
+      <c r="Q74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="2" t="n"/>
+      <c r="Q75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="2" t="n"/>
+      <c r="Q76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="2" t="n"/>
+      <c r="Q77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="2" t="n"/>
+      <c r="Q78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="2" t="n"/>
+      <c r="Q79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="2" t="n"/>
+      <c r="Q80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="2" t="n"/>
+      <c r="Q81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="2" t="n"/>
+      <c r="Q82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="2" t="n"/>
+      <c r="Q83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="2" t="n"/>
+      <c r="Q84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="2" t="n"/>
+      <c r="Q85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="2" t="n"/>
+      <c r="Q86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="2" t="n"/>
+      <c r="Q87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="2" t="n"/>
+      <c r="Q88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="2" t="n"/>
+      <c r="Q89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="2" t="n"/>
+      <c r="Q90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="2" t="n"/>
+      <c r="Q91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="2" t="n"/>
+      <c r="Q92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="2" t="n"/>
+      <c r="Q93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="2" t="n"/>
+      <c r="Q94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="D95" s="2" t="n"/>
+      <c r="Q95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="D96" s="2" t="n"/>
+      <c r="Q96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="2" t="n"/>
+      <c r="Q97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="2" t="n"/>
+      <c r="Q98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="2" t="n"/>
+      <c r="Q99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="2" t="n"/>
+      <c r="Q100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="2" t="n"/>
+      <c r="Q101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="2" t="n"/>
+      <c r="Q102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="2" t="n"/>
+      <c r="Q103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="2" t="n"/>
+      <c r="Q104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="2" t="n"/>
+      <c r="Q105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="2" t="n"/>
+      <c r="Q106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="2" t="n"/>
+      <c r="Q107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="2" t="n"/>
+      <c r="Q108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="2" t="n"/>
+      <c r="Q109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="2" t="n"/>
+      <c r="Q110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="2" t="n"/>
+      <c r="Q111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="2" t="n"/>
+      <c r="Q112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="2" t="n"/>
+      <c r="Q113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="2" t="n"/>
+      <c r="Q114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="2" t="n"/>
+      <c r="Q115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="2" t="n"/>
+      <c r="Q116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="2" t="n"/>
+      <c r="Q117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="2" t="n"/>
+      <c r="Q118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="2" t="n"/>
+      <c r="Q119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="2" t="n"/>
+      <c r="Q120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="2" t="n"/>
+      <c r="Q121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="2" t="n"/>
+      <c r="Q122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="2" t="n"/>
+      <c r="Q123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="2" t="n"/>
+      <c r="Q124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="2" t="n"/>
+      <c r="Q125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="2" t="n"/>
+      <c r="Q126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="2" t="n"/>
+      <c r="Q127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="2" t="n"/>
+      <c r="Q128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="2" t="n"/>
+      <c r="Q129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="2" t="n"/>
+      <c r="Q130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="2" t="n"/>
+      <c r="Q131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="2" t="n"/>
+      <c r="Q132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="2" t="n"/>
+      <c r="Q133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="2" t="n"/>
+      <c r="Q134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="2" t="n"/>
+      <c r="Q135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="2" t="n"/>
+      <c r="Q136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="2" t="n"/>
+      <c r="Q137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="2" t="n"/>
+      <c r="Q138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="2" t="n"/>
+      <c r="Q139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="2" t="n"/>
+      <c r="Q140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="2" t="n"/>
+      <c r="Q141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="2" t="n"/>
+      <c r="Q142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="2" t="n"/>
+      <c r="Q143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="2" t="n"/>
+      <c r="Q144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="2" t="n"/>
+      <c r="Q145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="2" t="n"/>
+      <c r="Q146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="2" t="n"/>
+      <c r="Q147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="2" t="n"/>
+      <c r="Q148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="2" t="n"/>
+      <c r="Q149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="2" t="n"/>
+      <c r="Q150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="2" t="n"/>
+      <c r="Q151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="2" t="n"/>
+      <c r="Q152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="2" t="n"/>
+      <c r="Q153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="2" t="n"/>
+      <c r="Q154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="2" t="n"/>
+      <c r="Q155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="2" t="n"/>
+      <c r="Q156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="2" t="n"/>
+      <c r="Q157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="2" t="n"/>
+      <c r="Q158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="2" t="n"/>
+      <c r="Q159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="2" t="n"/>
+      <c r="Q160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="2" t="n"/>
+      <c r="Q161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="2" t="n"/>
+      <c r="Q162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="2" t="n"/>
+      <c r="Q163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="2" t="n"/>
+      <c r="Q164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="2" t="n"/>
+      <c r="Q165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="2" t="n"/>
+      <c r="Q166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="2" t="n"/>
+      <c r="Q167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="2" t="n"/>
+      <c r="Q168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="2" t="n"/>
+      <c r="Q169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="2" t="n"/>
+      <c r="Q170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="2" t="n"/>
+      <c r="Q171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="2" t="n"/>
+      <c r="Q172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="2" t="n"/>
+      <c r="Q173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="2" t="n"/>
+      <c r="Q174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="2" t="n"/>
+      <c r="Q175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="2" t="n"/>
+      <c r="Q176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="2" t="n"/>
+      <c r="Q177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="2" t="n"/>
+      <c r="Q178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="2" t="n"/>
+      <c r="Q179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="2" t="n"/>
+      <c r="Q180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="2" t="n"/>
+      <c r="Q181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="2" t="n"/>
+      <c r="Q182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="2" t="n"/>
+      <c r="Q183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="2" t="n"/>
+      <c r="Q184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="2" t="n"/>
+      <c r="Q185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="2" t="n"/>
+      <c r="Q186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="2" t="n"/>
+      <c r="Q187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="2" t="n"/>
+      <c r="Q188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="2" t="n"/>
+      <c r="Q189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="2" t="n"/>
+      <c r="Q190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="2" t="n"/>
+      <c r="Q191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="2" t="n"/>
+      <c r="Q192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="2" t="n"/>
+      <c r="Q193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="2" t="n"/>
+      <c r="Q194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="2" t="n"/>
+      <c r="Q195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="2" t="n"/>
+      <c r="Q196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="2" t="n"/>
+      <c r="Q197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="2" t="n"/>
+      <c r="Q198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="2" t="n"/>
+      <c r="Q199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="2" t="n"/>
+      <c r="Q200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="D201" s="2" t="n"/>
+      <c r="Q201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="2" t="n"/>
+      <c r="Q202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="D203" s="2" t="n"/>
+      <c r="Q203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="D204" s="2" t="n"/>
+      <c r="Q204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="D205" s="2" t="n"/>
+      <c r="Q205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="D206" s="2" t="n"/>
+      <c r="Q206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="D207" s="2" t="n"/>
+      <c r="Q207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="D208" s="2" t="n"/>
+      <c r="Q208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="D209" s="2" t="n"/>
+      <c r="Q209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="D210" s="2" t="n"/>
+      <c r="Q210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="D211" s="2" t="n"/>
+      <c r="Q211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="D212" s="2" t="n"/>
+      <c r="Q212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="D213" s="2" t="n"/>
+      <c r="Q213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="D214" s="2" t="n"/>
+      <c r="Q214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="D215" s="2" t="n"/>
+      <c r="Q215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="D216" s="2" t="n"/>
+      <c r="Q216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="D217" s="2" t="n"/>
+      <c r="Q217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="D218" s="2" t="n"/>
+      <c r="Q218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="D219" s="2" t="n"/>
+      <c r="Q219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="D220" s="2" t="n"/>
+      <c r="Q220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="D221" s="2" t="n"/>
+      <c r="Q221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="D222" s="2" t="n"/>
+      <c r="Q222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="D223" s="2" t="n"/>
+      <c r="Q223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="D224" s="2" t="n"/>
+      <c r="Q224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="D225" s="2" t="n"/>
+      <c r="Q225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="D226" s="2" t="n"/>
+      <c r="Q226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="D227" s="2" t="n"/>
+      <c r="Q227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="D228" s="2" t="n"/>
+      <c r="Q228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="D229" s="2" t="n"/>
+      <c r="Q229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="D230" s="2" t="n"/>
+      <c r="Q230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="2" t="n"/>
+      <c r="Q231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="D232" s="2" t="n"/>
+      <c r="Q232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="D233" s="2" t="n"/>
+      <c r="Q233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="D234" s="2" t="n"/>
+      <c r="Q234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="D235" s="2" t="n"/>
+      <c r="Q235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="D236" s="2" t="n"/>
+      <c r="Q236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="D237" s="2" t="n"/>
+      <c r="Q237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="D238" s="2" t="n"/>
+      <c r="Q238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="D239" s="2" t="n"/>
+      <c r="Q239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="D240" s="2" t="n"/>
+      <c r="Q240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="D241" s="2" t="n"/>
+      <c r="Q241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="D242" s="2" t="n"/>
+      <c r="Q242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="D243" s="2" t="n"/>
+      <c r="Q243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="D244" s="2" t="n"/>
+      <c r="Q244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="D245" s="2" t="n"/>
+      <c r="Q245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="D246" s="2" t="n"/>
+      <c r="Q246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="D247" s="2" t="n"/>
+      <c r="Q247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="D248" s="2" t="n"/>
+      <c r="Q248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="D249" s="2" t="n"/>
+      <c r="Q249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="D250" s="2" t="n"/>
+      <c r="Q250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="D251" s="2" t="n"/>
+      <c r="Q251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="D252" s="2" t="n"/>
+      <c r="Q252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="D253" s="2" t="n"/>
+      <c r="Q253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="D254" s="2" t="n"/>
+      <c r="Q254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="D255" s="2" t="n"/>
+      <c r="Q255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="D256" s="2" t="n"/>
+      <c r="Q256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="D257" s="2" t="n"/>
+      <c r="Q257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="D258" s="2" t="n"/>
+      <c r="Q258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="D259" s="2" t="n"/>
+      <c r="Q259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="D260" s="2" t="n"/>
+      <c r="Q260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="D261" s="2" t="n"/>
+      <c r="Q261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="D262" s="2" t="n"/>
+      <c r="Q262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="D263" s="2" t="n"/>
+      <c r="Q263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="D264" s="2" t="n"/>
+      <c r="Q264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="D265" s="2" t="n"/>
+      <c r="Q265" s="2" t="n"/>
+    </row>
+    <row r="266">
+      <c r="D266" s="2" t="n"/>
+      <c r="Q266" s="2" t="n"/>
+    </row>
+    <row r="267">
+      <c r="D267" s="2" t="n"/>
+      <c r="Q267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="D268" s="2" t="n"/>
+      <c r="Q268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="D269" s="2" t="n"/>
+      <c r="Q269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="D270" s="2" t="n"/>
+      <c r="Q270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="D271" s="2" t="n"/>
+      <c r="Q271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="D272" s="2" t="n"/>
+      <c r="Q272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="D273" s="2" t="n"/>
+      <c r="Q273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="D274" s="2" t="n"/>
+      <c r="Q274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="D275" s="2" t="n"/>
+      <c r="Q275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="D276" s="2" t="n"/>
+      <c r="Q276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="D277" s="2" t="n"/>
+      <c r="Q277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="D278" s="2" t="n"/>
+      <c r="Q278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="D279" s="2" t="n"/>
+      <c r="Q279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="D280" s="2" t="n"/>
+      <c r="Q280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="D281" s="2" t="n"/>
+      <c r="Q281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="D282" s="2" t="n"/>
+      <c r="Q282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="D283" s="2" t="n"/>
+      <c r="Q283" s="2" t="n"/>
+    </row>
+    <row r="284">
+      <c r="D284" s="2" t="n"/>
+      <c r="Q284" s="2" t="n"/>
+    </row>
+    <row r="285">
+      <c r="D285" s="2" t="n"/>
+      <c r="Q285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="D286" s="2" t="n"/>
+      <c r="Q286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="D287" s="2" t="n"/>
+      <c r="Q287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="D288" s="2" t="n"/>
+      <c r="Q288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="D289" s="2" t="n"/>
+      <c r="Q289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="2" t="n"/>
+      <c r="Q290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="2" t="n"/>
+      <c r="Q291" s="2" t="n"/>
+    </row>
+    <row r="292">
+      <c r="D292" s="2" t="n"/>
+      <c r="Q292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="D293" s="2" t="n"/>
+      <c r="Q293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="D294" s="2" t="n"/>
+      <c r="Q294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="D295" s="2" t="n"/>
+      <c r="Q295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="D296" s="2" t="n"/>
+      <c r="Q296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="D297" s="2" t="n"/>
+      <c r="Q297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="D298" s="2" t="n"/>
+      <c r="Q298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="D299" s="2" t="n"/>
+      <c r="Q299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="D300" s="2" t="n"/>
+      <c r="Q300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="D301" s="2" t="n"/>
+      <c r="Q301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="D302" s="2" t="n"/>
+      <c r="Q302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="D303" s="2" t="n"/>
+      <c r="Q303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="D304" s="2" t="n"/>
+      <c r="Q304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="D305" s="2" t="n"/>
+      <c r="Q305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="D306" s="2" t="n"/>
+      <c r="Q306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="D307" s="2" t="n"/>
+      <c r="Q307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="D308" s="2" t="n"/>
+      <c r="Q308" s="2" t="n"/>
+    </row>
+    <row r="309">
+      <c r="D309" s="2" t="n"/>
+      <c r="Q309" s="2" t="n"/>
+    </row>
+    <row r="310">
+      <c r="D310" s="2" t="n"/>
+      <c r="Q310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="D311" s="2" t="n"/>
+      <c r="Q311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="D312" s="2" t="n"/>
+      <c r="Q312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="D313" s="2" t="n"/>
+      <c r="Q313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="D314" s="2" t="n"/>
+      <c r="Q314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="D315" s="2" t="n"/>
+      <c r="Q315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="D316" s="2" t="n"/>
+      <c r="Q316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="D317" s="2" t="n"/>
+      <c r="Q317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="D318" s="2" t="n"/>
+      <c r="Q318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="D319" s="2" t="n"/>
+      <c r="Q319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="D320" s="2" t="n"/>
+      <c r="Q320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="D321" s="2" t="n"/>
+      <c r="Q321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="D322" s="2" t="n"/>
+      <c r="Q322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="D323" s="2" t="n"/>
+      <c r="Q323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="D324" s="2" t="n"/>
+      <c r="Q324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="D325" s="2" t="n"/>
+      <c r="Q325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="D326" s="2" t="n"/>
+      <c r="Q326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="D327" s="2" t="n"/>
+      <c r="Q327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="D328" s="2" t="n"/>
+      <c r="Q328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="D329" s="2" t="n"/>
+      <c r="Q329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="D330" s="2" t="n"/>
+      <c r="Q330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="D331" s="2" t="n"/>
+      <c r="Q331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="D332" s="2" t="n"/>
+      <c r="Q332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="D333" s="2" t="n"/>
+      <c r="Q333" s="2" t="n"/>
+    </row>
+    <row r="334">
+      <c r="D334" s="2" t="n"/>
+      <c r="Q334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="D335" s="2" t="n"/>
+      <c r="Q335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="D336" s="2" t="n"/>
+      <c r="Q336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="D337" s="2" t="n"/>
+      <c r="Q337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="D338" s="2" t="n"/>
+      <c r="Q338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="D339" s="2" t="n"/>
+      <c r="Q339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="D340" s="2" t="n"/>
+      <c r="Q340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="D341" s="2" t="n"/>
+      <c r="Q341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="D342" s="2" t="n"/>
+      <c r="Q342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="D343" s="2" t="n"/>
+      <c r="Q343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="D344" s="2" t="n"/>
+      <c r="Q344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="D345" s="2" t="n"/>
+      <c r="Q345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="D346" s="2" t="n"/>
+      <c r="Q346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="D347" s="2" t="n"/>
+      <c r="Q347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="D348" s="2" t="n"/>
+      <c r="Q348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="D349" s="2" t="n"/>
+      <c r="Q349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="D350" s="2" t="n"/>
+      <c r="Q350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="D351" s="2" t="n"/>
+      <c r="Q351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="D352" s="2" t="n"/>
+      <c r="Q352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="D353" s="2" t="n"/>
+      <c r="Q353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="D354" s="2" t="n"/>
+      <c r="Q354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="D355" s="2" t="n"/>
+      <c r="Q355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="D356" s="2" t="n"/>
+      <c r="Q356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="D357" s="2" t="n"/>
+      <c r="Q357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="D358" s="2" t="n"/>
+      <c r="Q358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="D359" s="2" t="n"/>
+      <c r="Q359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="D360" s="2" t="n"/>
+      <c r="Q360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="D361" s="2" t="n"/>
+      <c r="Q361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="D362" s="2" t="n"/>
+      <c r="Q362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="D363" s="2" t="n"/>
+      <c r="Q363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="D364" s="2" t="n"/>
+      <c r="Q364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="D365" s="2" t="n"/>
+      <c r="Q365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="D366" s="2" t="n"/>
+      <c r="Q366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="D367" s="2" t="n"/>
+      <c r="Q367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="D368" s="2" t="n"/>
+      <c r="Q368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="D369" s="2" t="n"/>
+      <c r="Q369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="D370" s="2" t="n"/>
+      <c r="Q370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="D371" s="2" t="n"/>
+      <c r="Q371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="D372" s="2" t="n"/>
+      <c r="Q372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="D373" s="2" t="n"/>
+      <c r="Q373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="D374" s="2" t="n"/>
+      <c r="Q374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="D375" s="2" t="n"/>
+      <c r="Q375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="D376" s="2" t="n"/>
+      <c r="Q376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="D377" s="2" t="n"/>
+      <c r="Q377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="D378" s="2" t="n"/>
+      <c r="Q378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="D379" s="2" t="n"/>
+      <c r="Q379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="D380" s="2" t="n"/>
+      <c r="Q380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="D381" s="2" t="n"/>
+      <c r="Q381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="D382" s="2" t="n"/>
+      <c r="Q382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="D383" s="2" t="n"/>
+      <c r="Q383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="D384" s="2" t="n"/>
+      <c r="Q384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="D385" s="2" t="n"/>
+      <c r="Q385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="D386" s="2" t="n"/>
+      <c r="Q386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="D387" s="2" t="n"/>
+      <c r="Q387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="D388" s="2" t="n"/>
+      <c r="Q388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="D389" s="2" t="n"/>
+      <c r="Q389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="D390" s="2" t="n"/>
+      <c r="Q390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="D391" s="2" t="n"/>
+      <c r="Q391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="D392" s="2" t="n"/>
+      <c r="Q392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="D393" s="2" t="n"/>
+      <c r="Q393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="D394" s="2" t="n"/>
+      <c r="Q394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="D395" s="2" t="n"/>
+      <c r="Q395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="D396" s="2" t="n"/>
+      <c r="Q396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="D397" s="2" t="n"/>
+      <c r="Q397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="D398" s="2" t="n"/>
+      <c r="Q398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="D399" s="2" t="n"/>
+      <c r="Q399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="D400" s="2" t="n"/>
+      <c r="Q400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="D401" s="2" t="n"/>
+      <c r="Q401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="D402" s="2" t="n"/>
+      <c r="Q402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="D403" s="2" t="n"/>
+      <c r="Q403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="D404" s="2" t="n"/>
+      <c r="Q404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="D405" s="2" t="n"/>
+      <c r="Q405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="D406" s="2" t="n"/>
+      <c r="Q406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="D407" s="2" t="n"/>
+      <c r="Q407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="D408" s="2" t="n"/>
+      <c r="Q408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="D409" s="2" t="n"/>
+      <c r="Q409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="D410" s="2" t="n"/>
+      <c r="Q410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="D411" s="2" t="n"/>
+      <c r="Q411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="D412" s="2" t="n"/>
+      <c r="Q412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="D413" s="2" t="n"/>
+      <c r="Q413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="D414" s="2" t="n"/>
+      <c r="Q414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="D415" s="2" t="n"/>
+      <c r="Q415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="D416" s="2" t="n"/>
+      <c r="Q416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="D417" s="2" t="n"/>
+      <c r="Q417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="D418" s="2" t="n"/>
+      <c r="Q418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="D419" s="2" t="n"/>
+      <c r="Q419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="D420" s="2" t="n"/>
+      <c r="Q420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="D421" s="2" t="n"/>
+      <c r="Q421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="D422" s="2" t="n"/>
+      <c r="Q422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="D423" s="2" t="n"/>
+      <c r="Q423" s="2" t="n"/>
+    </row>
+    <row r="424">
+      <c r="D424" s="2" t="n"/>
+      <c r="Q424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="D425" s="2" t="n"/>
+      <c r="Q425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="D426" s="2" t="n"/>
+      <c r="Q426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="D427" s="2" t="n"/>
+      <c r="Q427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="D428" s="2" t="n"/>
+      <c r="Q428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="D429" s="2" t="n"/>
+      <c r="Q429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="D430" s="2" t="n"/>
+      <c r="Q430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="D431" s="2" t="n"/>
+      <c r="Q431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="D432" s="2" t="n"/>
+      <c r="Q432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="D433" s="2" t="n"/>
+      <c r="Q433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="D434" s="2" t="n"/>
+      <c r="Q434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="D435" s="2" t="n"/>
+      <c r="Q435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="D436" s="2" t="n"/>
+      <c r="Q436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="D437" s="2" t="n"/>
+      <c r="Q437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="D438" s="2" t="n"/>
+      <c r="Q438" s="2" t="n"/>
+    </row>
+    <row r="439">
+      <c r="D439" s="2" t="n"/>
+      <c r="Q439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="D440" s="2" t="n"/>
+      <c r="Q440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="D441" s="2" t="n"/>
+      <c r="Q441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="D442" s="2" t="n"/>
+      <c r="Q442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="D443" s="2" t="n"/>
+      <c r="Q443" s="2" t="n"/>
+    </row>
+    <row r="444">
+      <c r="D444" s="2" t="n"/>
+      <c r="Q444" s="2" t="n"/>
+    </row>
+    <row r="445">
+      <c r="D445" s="2" t="n"/>
+      <c r="Q445" s="2" t="n"/>
+    </row>
+    <row r="446">
+      <c r="D446" s="2" t="n"/>
+      <c r="Q446" s="2" t="n"/>
+    </row>
+    <row r="447">
+      <c r="D447" s="2" t="n"/>
+      <c r="Q447" s="2" t="n"/>
+    </row>
+    <row r="448">
+      <c r="D448" s="2" t="n"/>
+      <c r="Q448" s="2" t="n"/>
+    </row>
+    <row r="449">
+      <c r="D449" s="2" t="n"/>
+      <c r="Q449" s="2" t="n"/>
+    </row>
+    <row r="450">
+      <c r="D450" s="2" t="n"/>
+      <c r="Q450" s="2" t="n"/>
+    </row>
+    <row r="451">
+      <c r="D451" s="2" t="n"/>
+      <c r="Q451" s="2" t="n"/>
+    </row>
+    <row r="452">
+      <c r="D452" s="2" t="n"/>
+      <c r="Q452" s="2" t="n"/>
+    </row>
+    <row r="453">
+      <c r="D453" s="2" t="n"/>
+      <c r="Q453" s="2" t="n"/>
+    </row>
+    <row r="454">
+      <c r="D454" s="2" t="n"/>
+      <c r="Q454" s="2" t="n"/>
+    </row>
+    <row r="455">
+      <c r="D455" s="2" t="n"/>
+      <c r="Q455" s="2" t="n"/>
+    </row>
+    <row r="456">
+      <c r="D456" s="2" t="n"/>
+      <c r="Q456" s="2" t="n"/>
+    </row>
+    <row r="457">
+      <c r="D457" s="2" t="n"/>
+      <c r="Q457" s="2" t="n"/>
+    </row>
+    <row r="458">
+      <c r="D458" s="2" t="n"/>
+      <c r="Q458" s="2" t="n"/>
+    </row>
+    <row r="459">
+      <c r="D459" s="2" t="n"/>
+      <c r="Q459" s="2" t="n"/>
+    </row>
+    <row r="460">
+      <c r="D460" s="2" t="n"/>
+      <c r="Q460" s="2" t="n"/>
+    </row>
+    <row r="461">
+      <c r="D461" s="2" t="n"/>
+      <c r="Q461" s="2" t="n"/>
+    </row>
+    <row r="462">
+      <c r="D462" s="2" t="n"/>
+      <c r="Q462" s="2" t="n"/>
+    </row>
+    <row r="463">
+      <c r="D463" s="2" t="n"/>
+      <c r="Q463" s="2" t="n"/>
+    </row>
+    <row r="464">
+      <c r="D464" s="2" t="n"/>
+      <c r="Q464" s="2" t="n"/>
+    </row>
+    <row r="465">
+      <c r="D465" s="2" t="n"/>
+      <c r="Q465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="D466" s="2" t="n"/>
+      <c r="Q466" s="2" t="n"/>
+    </row>
+    <row r="467">
+      <c r="D467" s="2" t="n"/>
+      <c r="Q467" s="2" t="n"/>
+    </row>
+    <row r="468">
+      <c r="D468" s="2" t="n"/>
+      <c r="Q468" s="2" t="n"/>
+    </row>
+    <row r="469">
+      <c r="D469" s="2" t="n"/>
+      <c r="Q469" s="2" t="n"/>
+    </row>
+    <row r="470">
+      <c r="D470" s="2" t="n"/>
+      <c r="Q470" s="2" t="n"/>
+    </row>
+    <row r="471">
+      <c r="D471" s="2" t="n"/>
+      <c r="Q471" s="2" t="n"/>
+    </row>
+    <row r="472">
+      <c r="D472" s="2" t="n"/>
+      <c r="Q472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="D473" s="2" t="n"/>
+      <c r="Q473" s="2" t="n"/>
+    </row>
+    <row r="474">
+      <c r="D474" s="2" t="n"/>
+      <c r="Q474" s="2" t="n"/>
+    </row>
+    <row r="475">
+      <c r="D475" s="2" t="n"/>
+      <c r="Q475" s="2" t="n"/>
+    </row>
+    <row r="476">
+      <c r="D476" s="2" t="n"/>
+      <c r="Q476" s="2" t="n"/>
+    </row>
+    <row r="477">
+      <c r="D477" s="2" t="n"/>
+      <c r="Q477" s="2" t="n"/>
+    </row>
+    <row r="478">
+      <c r="D478" s="2" t="n"/>
+      <c r="Q478" s="2" t="n"/>
+    </row>
+    <row r="479">
+      <c r="D479" s="2" t="n"/>
+      <c r="Q479" s="2" t="n"/>
+    </row>
+    <row r="480">
+      <c r="D480" s="2" t="n"/>
+      <c r="Q480" s="2" t="n"/>
+    </row>
+    <row r="481">
+      <c r="D481" s="2" t="n"/>
+      <c r="Q481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="D482" s="2" t="n"/>
+      <c r="Q482" s="2" t="n"/>
+    </row>
+    <row r="483">
+      <c r="D483" s="2" t="n"/>
+      <c r="Q483" s="2" t="n"/>
+    </row>
+    <row r="484">
+      <c r="D484" s="2" t="n"/>
+      <c r="Q484" s="2" t="n"/>
+    </row>
+    <row r="485">
+      <c r="D485" s="2" t="n"/>
+      <c r="Q485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="D486" s="2" t="n"/>
+      <c r="Q486" s="2" t="n"/>
+    </row>
+    <row r="487">
+      <c r="D487" s="2" t="n"/>
+      <c r="Q487" s="2" t="n"/>
+    </row>
+    <row r="488">
+      <c r="D488" s="2" t="n"/>
+      <c r="Q488" s="2" t="n"/>
+    </row>
+    <row r="489">
+      <c r="D489" s="2" t="n"/>
+      <c r="Q489" s="2" t="n"/>
+    </row>
+    <row r="490">
+      <c r="D490" s="2" t="n"/>
+      <c r="Q490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="D491" s="2" t="n"/>
+      <c r="Q491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="D492" s="2" t="n"/>
+      <c r="Q492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="D493" s="2" t="n"/>
+      <c r="Q493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="D494" s="2" t="n"/>
+      <c r="Q494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="D495" s="2" t="n"/>
+      <c r="Q495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="D496" s="2" t="n"/>
+      <c r="Q496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="D497" s="2" t="n"/>
+      <c r="Q497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="D498" s="2" t="n"/>
+      <c r="Q498" s="2" t="n"/>
+    </row>
+    <row r="499">
+      <c r="D499" s="2" t="n"/>
+      <c r="Q499" s="2" t="n"/>
+    </row>
+    <row r="500">
+      <c r="D500" s="2" t="n"/>
+      <c r="Q500" s="2" t="n"/>
+    </row>
+    <row r="501">
+      <c r="D501" s="2" t="n"/>
+      <c r="Q501" s="2" t="n"/>
+    </row>
+    <row r="502">
+      <c r="D502" s="2" t="n"/>
+      <c r="Q502" s="2" t="n"/>
+    </row>
+    <row r="503">
+      <c r="D503" s="2" t="n"/>
+      <c r="Q503" s="2" t="n"/>
+    </row>
+    <row r="504">
+      <c r="D504" s="2" t="n"/>
+      <c r="Q504" s="2" t="n"/>
+    </row>
+    <row r="505">
+      <c r="D505" s="2" t="n"/>
+      <c r="Q505" s="2" t="n"/>
+    </row>
+    <row r="506">
+      <c r="D506" s="2" t="n"/>
+      <c r="Q506" s="2" t="n"/>
+    </row>
+    <row r="507">
+      <c r="D507" s="2" t="n"/>
+      <c r="Q507" s="2" t="n"/>
+    </row>
+    <row r="508">
+      <c r="D508" s="2" t="n"/>
+      <c r="Q508" s="2" t="n"/>
+    </row>
+    <row r="509">
+      <c r="D509" s="2" t="n"/>
+      <c r="Q509" s="2" t="n"/>
+    </row>
+    <row r="510">
+      <c r="D510" s="2" t="n"/>
+      <c r="Q510" s="2" t="n"/>
+    </row>
+    <row r="511">
+      <c r="D511" s="2" t="n"/>
+      <c r="Q511" s="2" t="n"/>
+    </row>
+    <row r="512">
+      <c r="D512" s="2" t="n"/>
+      <c r="Q512" s="2" t="n"/>
+    </row>
+    <row r="513">
+      <c r="D513" s="2" t="n"/>
+      <c r="Q513" s="2" t="n"/>
+    </row>
+    <row r="514">
+      <c r="D514" s="2" t="n"/>
+      <c r="Q514" s="2" t="n"/>
+    </row>
+    <row r="515">
+      <c r="D515" s="2" t="n"/>
+      <c r="Q515" s="2" t="n"/>
+    </row>
+    <row r="516">
+      <c r="D516" s="2" t="n"/>
+      <c r="Q516" s="2" t="n"/>
+    </row>
+    <row r="517">
+      <c r="D517" s="2" t="n"/>
+      <c r="Q517" s="2" t="n"/>
+    </row>
+    <row r="518">
+      <c r="D518" s="2" t="n"/>
+      <c r="Q518" s="2" t="n"/>
+    </row>
+    <row r="519">
+      <c r="D519" s="2" t="n"/>
+      <c r="Q519" s="2" t="n"/>
+    </row>
+    <row r="520">
+      <c r="D520" s="2" t="n"/>
+      <c r="Q520" s="2" t="n"/>
+    </row>
+    <row r="521">
+      <c r="D521" s="2" t="n"/>
+      <c r="Q521" s="2" t="n"/>
+    </row>
+    <row r="522">
+      <c r="D522" s="2" t="n"/>
+      <c r="Q522" s="2" t="n"/>
+    </row>
+    <row r="523">
+      <c r="D523" s="2" t="n"/>
+      <c r="Q523" s="2" t="n"/>
+    </row>
+    <row r="524">
+      <c r="D524" s="2" t="n"/>
+      <c r="Q524" s="2" t="n"/>
+    </row>
+    <row r="525">
+      <c r="D525" s="2" t="n"/>
+      <c r="Q525" s="2" t="n"/>
+    </row>
+    <row r="526">
+      <c r="D526" s="2" t="n"/>
+      <c r="Q526" s="2" t="n"/>
+    </row>
+    <row r="527">
+      <c r="D527" s="2" t="n"/>
+      <c r="Q527" s="2" t="n"/>
+    </row>
+    <row r="528">
+      <c r="D528" s="2" t="n"/>
+      <c r="Q528" s="2" t="n"/>
+    </row>
+    <row r="529">
+      <c r="D529" s="2" t="n"/>
+      <c r="Q529" s="2" t="n"/>
+    </row>
+    <row r="530">
+      <c r="D530" s="2" t="n"/>
+      <c r="Q530" s="2" t="n"/>
+    </row>
+    <row r="531">
+      <c r="D531" s="2" t="n"/>
+      <c r="Q531" s="2" t="n"/>
+    </row>
+    <row r="532">
+      <c r="D532" s="2" t="n"/>
+      <c r="Q532" s="2" t="n"/>
+    </row>
+    <row r="533">
+      <c r="D533" s="2" t="n"/>
+      <c r="Q533" s="2" t="n"/>
+    </row>
+    <row r="534">
+      <c r="D534" s="2" t="n"/>
+      <c r="Q534" s="2" t="n"/>
+    </row>
+    <row r="535">
+      <c r="D535" s="2" t="n"/>
+      <c r="Q535" s="2" t="n"/>
+    </row>
+    <row r="536">
+      <c r="D536" s="2" t="n"/>
+      <c r="Q536" s="2" t="n"/>
+    </row>
+    <row r="537">
+      <c r="D537" s="2" t="n"/>
+      <c r="Q537" s="2" t="n"/>
+    </row>
+    <row r="538">
+      <c r="D538" s="2" t="n"/>
+      <c r="Q538" s="2" t="n"/>
+    </row>
+    <row r="539">
+      <c r="D539" s="2" t="n"/>
+      <c r="Q539" s="2" t="n"/>
+    </row>
+    <row r="540">
+      <c r="D540" s="2" t="n"/>
+      <c r="Q540" s="2" t="n"/>
+    </row>
+    <row r="541">
+      <c r="D541" s="2" t="n"/>
+      <c r="Q541" s="2" t="n"/>
+    </row>
+    <row r="542">
+      <c r="D542" s="2" t="n"/>
+      <c r="Q542" s="2" t="n"/>
+    </row>
+    <row r="543">
+      <c r="D543" s="2" t="n"/>
+      <c r="Q543" s="2" t="n"/>
+    </row>
+    <row r="544">
+      <c r="D544" s="2" t="n"/>
+      <c r="Q544" s="2" t="n"/>
+    </row>
+    <row r="545">
+      <c r="D545" s="2" t="n"/>
+      <c r="Q545" s="2" t="n"/>
+    </row>
+    <row r="546">
+      <c r="D546" s="2" t="n"/>
+      <c r="Q546" s="2" t="n"/>
+    </row>
+    <row r="547">
+      <c r="D547" s="2" t="n"/>
+      <c r="Q547" s="2" t="n"/>
+    </row>
+    <row r="548">
+      <c r="D548" s="2" t="n"/>
+      <c r="Q548" s="2" t="n"/>
+    </row>
+    <row r="549">
+      <c r="D549" s="2" t="n"/>
+      <c r="Q549" s="2" t="n"/>
+    </row>
+    <row r="550">
+      <c r="D550" s="2" t="n"/>
+      <c r="Q550" s="2" t="n"/>
+    </row>
+    <row r="551">
+      <c r="D551" s="2" t="n"/>
+      <c r="Q551" s="2" t="n"/>
+    </row>
+    <row r="552">
+      <c r="D552" s="2" t="n"/>
+      <c r="Q552" s="2" t="n"/>
+    </row>
+    <row r="553">
+      <c r="D553" s="2" t="n"/>
+      <c r="Q553" s="2" t="n"/>
+    </row>
+    <row r="554">
+      <c r="D554" s="2" t="n"/>
+      <c r="Q554" s="2" t="n"/>
+    </row>
+    <row r="555">
+      <c r="D555" s="2" t="n"/>
+      <c r="Q555" s="2" t="n"/>
+    </row>
+    <row r="556">
+      <c r="D556" s="2" t="n"/>
+      <c r="Q556" s="2" t="n"/>
+    </row>
+    <row r="557">
+      <c r="D557" s="2" t="n"/>
+      <c r="Q557" s="2" t="n"/>
+    </row>
+    <row r="558">
+      <c r="D558" s="2" t="n"/>
+      <c r="Q558" s="2" t="n"/>
+    </row>
+    <row r="559">
+      <c r="D559" s="2" t="n"/>
+      <c r="Q559" s="2" t="n"/>
+    </row>
+    <row r="560">
+      <c r="D560" s="2" t="n"/>
+      <c r="Q560" s="2" t="n"/>
+    </row>
+    <row r="561">
+      <c r="D561" s="2" t="n"/>
+      <c r="Q561" s="2" t="n"/>
+    </row>
+    <row r="562">
+      <c r="D562" s="2" t="n"/>
+      <c r="Q562" s="2" t="n"/>
+    </row>
+    <row r="563">
+      <c r="D563" s="2" t="n"/>
+      <c r="Q563" s="2" t="n"/>
+    </row>
+    <row r="564">
+      <c r="D564" s="2" t="n"/>
+      <c r="Q564" s="2" t="n"/>
+    </row>
+    <row r="565">
+      <c r="D565" s="2" t="n"/>
+      <c r="Q565" s="2" t="n"/>
+    </row>
+    <row r="566">
+      <c r="D566" s="2" t="n"/>
+      <c r="Q566" s="2" t="n"/>
+    </row>
+    <row r="567">
+      <c r="D567" s="2" t="n"/>
+      <c r="Q567" s="2" t="n"/>
+    </row>
+    <row r="568">
+      <c r="D568" s="2" t="n"/>
+      <c r="Q568" s="2" t="n"/>
+    </row>
+    <row r="569">
+      <c r="D569" s="2" t="n"/>
+      <c r="Q569" s="2" t="n"/>
+    </row>
+    <row r="570">
+      <c r="D570" s="2" t="n"/>
+      <c r="Q570" s="2" t="n"/>
+    </row>
+    <row r="571">
+      <c r="D571" s="2" t="n"/>
+      <c r="Q571" s="2" t="n"/>
+    </row>
+    <row r="572">
+      <c r="D572" s="2" t="n"/>
+      <c r="Q572" s="2" t="n"/>
+    </row>
+    <row r="573">
+      <c r="D573" s="2" t="n"/>
+      <c r="Q573" s="2" t="n"/>
+    </row>
+    <row r="574">
+      <c r="D574" s="2" t="n"/>
+      <c r="Q574" s="2" t="n"/>
+    </row>
+    <row r="575">
+      <c r="D575" s="2" t="n"/>
+      <c r="Q575" s="2" t="n"/>
+    </row>
+    <row r="576">
+      <c r="D576" s="2" t="n"/>
+      <c r="Q576" s="2" t="n"/>
+    </row>
+    <row r="577">
+      <c r="D577" s="2" t="n"/>
+      <c r="Q577" s="2" t="n"/>
+    </row>
+    <row r="578">
+      <c r="D578" s="2" t="n"/>
+      <c r="Q578" s="2" t="n"/>
+    </row>
+    <row r="579">
+      <c r="D579" s="2" t="n"/>
+      <c r="Q579" s="2" t="n"/>
+    </row>
+    <row r="580">
+      <c r="D580" s="2" t="n"/>
+      <c r="Q580" s="2" t="n"/>
+    </row>
+    <row r="581">
+      <c r="D581" s="2" t="n"/>
+      <c r="Q581" s="2" t="n"/>
+    </row>
+    <row r="582">
+      <c r="D582" s="2" t="n"/>
+      <c r="Q582" s="2" t="n"/>
+    </row>
+    <row r="583">
+      <c r="D583" s="2" t="n"/>
+      <c r="Q583" s="2" t="n"/>
+    </row>
+    <row r="584">
+      <c r="D584" s="2" t="n"/>
+      <c r="Q584" s="2" t="n"/>
+    </row>
+    <row r="585">
+      <c r="D585" s="2" t="n"/>
+      <c r="Q585" s="2" t="n"/>
+    </row>
+    <row r="586">
+      <c r="D586" s="2" t="n"/>
+      <c r="Q586" s="2" t="n"/>
+    </row>
+    <row r="587">
+      <c r="D587" s="2" t="n"/>
+      <c r="Q587" s="2" t="n"/>
+    </row>
+    <row r="588">
+      <c r="D588" s="2" t="n"/>
+      <c r="Q588" s="2" t="n"/>
+    </row>
+    <row r="589">
+      <c r="D589" s="2" t="n"/>
+      <c r="Q589" s="2" t="n"/>
+    </row>
+    <row r="590">
+      <c r="D590" s="2" t="n"/>
+      <c r="Q590" s="2" t="n"/>
+    </row>
+    <row r="591">
+      <c r="D591" s="2" t="n"/>
+      <c r="Q591" s="2" t="n"/>
+    </row>
+    <row r="592">
+      <c r="D592" s="2" t="n"/>
+      <c r="Q592" s="2" t="n"/>
+    </row>
+    <row r="593">
+      <c r="D593" s="2" t="n"/>
+      <c r="Q593" s="2" t="n"/>
+    </row>
+    <row r="594">
+      <c r="D594" s="2" t="n"/>
+      <c r="Q594" s="2" t="n"/>
+    </row>
+    <row r="595">
+      <c r="D595" s="2" t="n"/>
+      <c r="Q595" s="2" t="n"/>
+    </row>
+    <row r="596">
+      <c r="D596" s="2" t="n"/>
+      <c r="Q596" s="2" t="n"/>
+    </row>
+    <row r="597">
+      <c r="D597" s="2" t="n"/>
+      <c r="Q597" s="2" t="n"/>
+    </row>
+    <row r="598">
+      <c r="D598" s="2" t="n"/>
+      <c r="Q598" s="2" t="n"/>
+    </row>
+    <row r="599">
+      <c r="D599" s="2" t="n"/>
+      <c r="Q599" s="2" t="n"/>
+    </row>
+    <row r="600">
+      <c r="D600" s="2" t="n"/>
+      <c r="Q600" s="2" t="n"/>
+    </row>
+    <row r="601">
+      <c r="D601" s="2" t="n"/>
+      <c r="Q601" s="2" t="n"/>
+    </row>
+    <row r="602">
+      <c r="D602" s="2" t="n"/>
+      <c r="Q602" s="2" t="n"/>
+    </row>
+    <row r="603">
+      <c r="D603" s="2" t="n"/>
+      <c r="Q603" s="2" t="n"/>
+    </row>
+    <row r="604">
+      <c r="D604" s="2" t="n"/>
+      <c r="Q604" s="2" t="n"/>
+    </row>
+    <row r="605">
+      <c r="D605" s="2" t="n"/>
+      <c r="Q605" s="2" t="n"/>
+    </row>
+    <row r="606">
+      <c r="D606" s="2" t="n"/>
+      <c r="Q606" s="2" t="n"/>
+    </row>
+    <row r="607">
+      <c r="D607" s="2" t="n"/>
+      <c r="Q607" s="2" t="n"/>
+    </row>
+    <row r="608">
+      <c r="D608" s="2" t="n"/>
+      <c r="Q608" s="2" t="n"/>
+    </row>
+    <row r="609">
+      <c r="D609" s="2" t="n"/>
+      <c r="Q609" s="2" t="n"/>
+    </row>
+    <row r="610">
+      <c r="D610" s="2" t="n"/>
+      <c r="Q610" s="2" t="n"/>
+    </row>
+    <row r="611">
+      <c r="D611" s="2" t="n"/>
+      <c r="Q611" s="2" t="n"/>
+    </row>
+    <row r="612">
+      <c r="D612" s="2" t="n"/>
+      <c r="Q612" s="2" t="n"/>
+    </row>
+    <row r="613">
+      <c r="D613" s="2" t="n"/>
+      <c r="Q613" s="2" t="n"/>
+    </row>
+    <row r="614">
+      <c r="D614" s="2" t="n"/>
+      <c r="Q614" s="2" t="n"/>
+    </row>
+    <row r="615">
+      <c r="D615" s="2" t="n"/>
+      <c r="Q615" s="2" t="n"/>
+    </row>
+    <row r="616">
+      <c r="D616" s="2" t="n"/>
+      <c r="Q616" s="2" t="n"/>
+    </row>
+    <row r="617">
+      <c r="D617" s="2" t="n"/>
+      <c r="Q617" s="2" t="n"/>
+    </row>
+    <row r="618">
+      <c r="D618" s="2" t="n"/>
+      <c r="Q618" s="2" t="n"/>
+    </row>
+    <row r="619">
+      <c r="D619" s="2" t="n"/>
+      <c r="Q619" s="2" t="n"/>
+    </row>
+    <row r="620">
+      <c r="D620" s="2" t="n"/>
+      <c r="Q620" s="2" t="n"/>
+    </row>
+    <row r="621">
+      <c r="D621" s="2" t="n"/>
+      <c r="Q621" s="2" t="n"/>
+    </row>
+    <row r="622">
+      <c r="D622" s="2" t="n"/>
+      <c r="Q622" s="2" t="n"/>
+    </row>
+    <row r="623">
+      <c r="D623" s="2" t="n"/>
+      <c r="Q623" s="2" t="n"/>
+    </row>
+    <row r="624">
+      <c r="D624" s="2" t="n"/>
+      <c r="Q624" s="2" t="n"/>
+    </row>
+    <row r="625">
+      <c r="D625" s="2" t="n"/>
+      <c r="Q625" s="2" t="n"/>
+    </row>
+    <row r="626">
+      <c r="D626" s="2" t="n"/>
+      <c r="Q626" s="2" t="n"/>
+    </row>
+    <row r="627">
+      <c r="D627" s="2" t="n"/>
+      <c r="Q627" s="2" t="n"/>
+    </row>
+    <row r="628">
+      <c r="D628" s="2" t="n"/>
+      <c r="Q628" s="2" t="n"/>
+    </row>
+    <row r="629">
+      <c r="D629" s="2" t="n"/>
+      <c r="Q629" s="2" t="n"/>
+    </row>
+    <row r="630">
+      <c r="D630" s="2" t="n"/>
+      <c r="Q630" s="2" t="n"/>
+    </row>
+    <row r="631">
+      <c r="D631" s="2" t="n"/>
+      <c r="Q631" s="2" t="n"/>
+    </row>
+    <row r="632">
+      <c r="D632" s="2" t="n"/>
+      <c r="Q632" s="2" t="n"/>
+    </row>
+    <row r="633">
+      <c r="D633" s="2" t="n"/>
+      <c r="Q633" s="2" t="n"/>
+    </row>
+    <row r="634">
+      <c r="D634" s="2" t="n"/>
+      <c r="Q634" s="2" t="n"/>
+    </row>
+    <row r="635">
+      <c r="D635" s="2" t="n"/>
+      <c r="Q635" s="2" t="n"/>
+    </row>
+    <row r="636">
+      <c r="D636" s="2" t="n"/>
+      <c r="Q636" s="2" t="n"/>
+    </row>
+    <row r="637">
+      <c r="D637" s="2" t="n"/>
+      <c r="Q637" s="2" t="n"/>
+    </row>
+    <row r="638">
+      <c r="D638" s="2" t="n"/>
+      <c r="Q638" s="2" t="n"/>
+    </row>
+    <row r="639">
+      <c r="D639" s="2" t="n"/>
+      <c r="Q639" s="2" t="n"/>
+    </row>
+    <row r="640">
+      <c r="D640" s="2" t="n"/>
+      <c r="Q640" s="2" t="n"/>
+    </row>
+    <row r="641">
+      <c r="D641" s="2" t="n"/>
+      <c r="Q641" s="2" t="n"/>
+    </row>
+    <row r="642">
+      <c r="D642" s="2" t="n"/>
+      <c r="Q642" s="2" t="n"/>
+    </row>
+    <row r="643">
+      <c r="D643" s="2" t="n"/>
+      <c r="Q643" s="2" t="n"/>
+    </row>
+    <row r="644">
+      <c r="D644" s="2" t="n"/>
+      <c r="Q644" s="2" t="n"/>
+    </row>
+    <row r="645">
+      <c r="D645" s="2" t="n"/>
+      <c r="Q645" s="2" t="n"/>
+    </row>
+    <row r="646">
+      <c r="D646" s="2" t="n"/>
+      <c r="Q646" s="2" t="n"/>
+    </row>
+    <row r="647">
+      <c r="D647" s="2" t="n"/>
+      <c r="Q647" s="2" t="n"/>
+    </row>
+    <row r="648">
+      <c r="D648" s="2" t="n"/>
+      <c r="Q648" s="2" t="n"/>
+    </row>
+    <row r="649">
+      <c r="D649" s="2" t="n"/>
+      <c r="Q649" s="2" t="n"/>
+    </row>
+    <row r="650">
+      <c r="D650" s="2" t="n"/>
+      <c r="Q650" s="2" t="n"/>
+    </row>
+    <row r="651">
+      <c r="D651" s="2" t="n"/>
+      <c r="Q651" s="2" t="n"/>
+    </row>
+    <row r="652">
+      <c r="D652" s="2" t="n"/>
+      <c r="Q652" s="2" t="n"/>
+    </row>
+    <row r="653">
+      <c r="D653" s="2" t="n"/>
+      <c r="Q653" s="2" t="n"/>
+    </row>
+    <row r="654">
+      <c r="D654" s="2" t="n"/>
+      <c r="Q654" s="2" t="n"/>
+    </row>
+    <row r="655">
+      <c r="D655" s="2" t="n"/>
+      <c r="Q655" s="2" t="n"/>
+    </row>
+    <row r="656">
+      <c r="D656" s="2" t="n"/>
+      <c r="Q656" s="2" t="n"/>
+    </row>
+    <row r="657">
+      <c r="D657" s="2" t="n"/>
+      <c r="Q657" s="2" t="n"/>
+    </row>
+    <row r="658">
+      <c r="D658" s="2" t="n"/>
+      <c r="Q658" s="2" t="n"/>
+    </row>
+    <row r="659">
+      <c r="D659" s="2" t="n"/>
+      <c r="Q659" s="2" t="n"/>
+    </row>
+    <row r="660">
+      <c r="D660" s="2" t="n"/>
+      <c r="Q660" s="2" t="n"/>
+    </row>
+    <row r="661">
+      <c r="D661" s="2" t="n"/>
+      <c r="Q661" s="2" t="n"/>
+    </row>
+    <row r="662">
+      <c r="D662" s="2" t="n"/>
+      <c r="Q662" s="2" t="n"/>
+    </row>
+    <row r="663">
+      <c r="D663" s="2" t="n"/>
+      <c r="Q663" s="2" t="n"/>
+    </row>
+    <row r="664">
+      <c r="D664" s="2" t="n"/>
+      <c r="Q664" s="2" t="n"/>
+    </row>
+    <row r="665">
+      <c r="D665" s="2" t="n"/>
+      <c r="Q665" s="2" t="n"/>
+    </row>
+    <row r="666">
+      <c r="D666" s="2" t="n"/>
+      <c r="Q666" s="2" t="n"/>
+    </row>
+    <row r="667">
+      <c r="D667" s="2" t="n"/>
+      <c r="Q667" s="2" t="n"/>
+    </row>
+    <row r="668">
+      <c r="D668" s="2" t="n"/>
+      <c r="Q668" s="2" t="n"/>
+    </row>
+    <row r="669">
+      <c r="D669" s="2" t="n"/>
+      <c r="Q669" s="2" t="n"/>
+    </row>
+    <row r="670">
+      <c r="D670" s="2" t="n"/>
+      <c r="Q670" s="2" t="n"/>
+    </row>
+    <row r="671">
+      <c r="D671" s="2" t="n"/>
+      <c r="Q671" s="2" t="n"/>
+    </row>
+    <row r="672">
+      <c r="D672" s="2" t="n"/>
+      <c r="Q672" s="2" t="n"/>
+    </row>
+    <row r="673">
+      <c r="D673" s="2" t="n"/>
+      <c r="Q673" s="2" t="n"/>
+    </row>
+    <row r="674">
+      <c r="D674" s="2" t="n"/>
+      <c r="Q674" s="2" t="n"/>
+    </row>
+    <row r="675">
+      <c r="D675" s="2" t="n"/>
+      <c r="Q675" s="2" t="n"/>
+    </row>
+    <row r="676">
+      <c r="D676" s="2" t="n"/>
+      <c r="Q676" s="2" t="n"/>
+    </row>
+    <row r="677">
+      <c r="D677" s="2" t="n"/>
+      <c r="Q677" s="2" t="n"/>
+    </row>
+    <row r="678">
+      <c r="D678" s="2" t="n"/>
+      <c r="Q678" s="2" t="n"/>
+    </row>
+    <row r="679">
+      <c r="D679" s="2" t="n"/>
+      <c r="Q679" s="2" t="n"/>
+    </row>
+    <row r="680">
+      <c r="D680" s="2" t="n"/>
+      <c r="Q680" s="2" t="n"/>
+    </row>
+    <row r="681">
+      <c r="D681" s="2" t="n"/>
+      <c r="Q681" s="2" t="n"/>
+    </row>
+    <row r="682">
+      <c r="D682" s="2" t="n"/>
+      <c r="Q682" s="2" t="n"/>
+    </row>
+    <row r="683">
+      <c r="D683" s="2" t="n"/>
+      <c r="Q683" s="2" t="n"/>
+    </row>
+    <row r="684">
+      <c r="D684" s="2" t="n"/>
+      <c r="Q684" s="2" t="n"/>
+    </row>
+    <row r="685">
+      <c r="D685" s="2" t="n"/>
+      <c r="Q685" s="2" t="n"/>
+    </row>
+    <row r="686">
+      <c r="D686" s="2" t="n"/>
+      <c r="Q686" s="2" t="n"/>
+    </row>
+    <row r="687">
+      <c r="D687" s="2" t="n"/>
+      <c r="Q687" s="2" t="n"/>
+    </row>
+    <row r="688">
+      <c r="D688" s="2" t="n"/>
+      <c r="Q688" s="2" t="n"/>
+    </row>
+    <row r="689">
+      <c r="D689" s="2" t="n"/>
+      <c r="Q689" s="2" t="n"/>
+    </row>
+    <row r="690">
+      <c r="D690" s="2" t="n"/>
+      <c r="Q690" s="2" t="n"/>
+    </row>
+    <row r="691">
+      <c r="D691" s="2" t="n"/>
+      <c r="Q691" s="2" t="n"/>
+    </row>
+    <row r="692">
+      <c r="D692" s="2" t="n"/>
+      <c r="Q692" s="2" t="n"/>
+    </row>
+    <row r="693">
+      <c r="D693" s="2" t="n"/>
+      <c r="Q693" s="2" t="n"/>
+    </row>
+    <row r="694">
+      <c r="D694" s="2" t="n"/>
+      <c r="Q694" s="2" t="n"/>
+    </row>
+    <row r="695">
+      <c r="D695" s="2" t="n"/>
+      <c r="Q695" s="2" t="n"/>
+    </row>
+    <row r="696">
+      <c r="D696" s="2" t="n"/>
+      <c r="Q696" s="2" t="n"/>
+    </row>
+    <row r="697">
+      <c r="D697" s="2" t="n"/>
+      <c r="Q697" s="2" t="n"/>
+    </row>
+    <row r="698">
+      <c r="D698" s="2" t="n"/>
+      <c r="Q698" s="2" t="n"/>
+    </row>
+    <row r="699">
+      <c r="D699" s="2" t="n"/>
+      <c r="Q699" s="2" t="n"/>
+    </row>
+    <row r="700">
+      <c r="D700" s="2" t="n"/>
+      <c r="Q700" s="2" t="n"/>
+    </row>
+    <row r="701">
+      <c r="D701" s="2" t="n"/>
+      <c r="Q701" s="2" t="n"/>
+    </row>
+    <row r="702">
+      <c r="D702" s="2" t="n"/>
+      <c r="Q702" s="2" t="n"/>
+    </row>
+    <row r="703">
+      <c r="D703" s="2" t="n"/>
+      <c r="Q703" s="2" t="n"/>
+    </row>
+    <row r="704">
+      <c r="D704" s="2" t="n"/>
+      <c r="Q704" s="2" t="n"/>
+    </row>
+    <row r="705">
+      <c r="D705" s="2" t="n"/>
+      <c r="Q705" s="2" t="n"/>
+    </row>
+    <row r="706">
+      <c r="D706" s="2" t="n"/>
+      <c r="Q706" s="2" t="n"/>
+    </row>
+    <row r="707">
+      <c r="D707" s="2" t="n"/>
+      <c r="Q707" s="2" t="n"/>
+    </row>
+    <row r="708">
+      <c r="D708" s="2" t="n"/>
+      <c r="Q708" s="2" t="n"/>
+    </row>
+    <row r="709">
+      <c r="D709" s="2" t="n"/>
+      <c r="Q709" s="2" t="n"/>
+    </row>
+    <row r="710">
+      <c r="D710" s="2" t="n"/>
+      <c r="Q710" s="2" t="n"/>
+    </row>
+    <row r="711">
+      <c r="D711" s="2" t="n"/>
+      <c r="Q711" s="2" t="n"/>
+    </row>
+    <row r="712">
+      <c r="D712" s="2" t="n"/>
+      <c r="Q712" s="2" t="n"/>
+    </row>
+    <row r="713">
+      <c r="D713" s="2" t="n"/>
+      <c r="Q713" s="2" t="n"/>
+    </row>
+    <row r="714">
+      <c r="D714" s="2" t="n"/>
+      <c r="Q714" s="2" t="n"/>
+    </row>
+    <row r="715">
+      <c r="D715" s="2" t="n"/>
+      <c r="Q715" s="2" t="n"/>
+    </row>
+    <row r="716">
+      <c r="D716" s="2" t="n"/>
+      <c r="Q716" s="2" t="n"/>
+    </row>
+    <row r="717">
+      <c r="D717" s="2" t="n"/>
+      <c r="Q717" s="2" t="n"/>
+    </row>
+    <row r="718">
+      <c r="D718" s="2" t="n"/>
+      <c r="Q718" s="2" t="n"/>
+    </row>
+    <row r="719">
+      <c r="D719" s="2" t="n"/>
+      <c r="Q719" s="2" t="n"/>
+    </row>
+    <row r="720">
+      <c r="D720" s="2" t="n"/>
+      <c r="Q720" s="2" t="n"/>
+    </row>
+    <row r="721">
+      <c r="D721" s="2" t="n"/>
+      <c r="Q721" s="2" t="n"/>
+    </row>
+    <row r="722">
+      <c r="D722" s="2" t="n"/>
+      <c r="Q722" s="2" t="n"/>
+    </row>
+    <row r="723">
+      <c r="D723" s="2" t="n"/>
+      <c r="Q723" s="2" t="n"/>
+    </row>
+    <row r="724">
+      <c r="D724" s="2" t="n"/>
+      <c r="Q724" s="2" t="n"/>
+    </row>
+    <row r="725">
+      <c r="D725" s="2" t="n"/>
+      <c r="Q725" s="2" t="n"/>
+    </row>
+    <row r="726">
+      <c r="D726" s="2" t="n"/>
+      <c r="Q726" s="2" t="n"/>
+    </row>
+    <row r="727">
+      <c r="D727" s="2" t="n"/>
+      <c r="Q727" s="2" t="n"/>
+    </row>
+    <row r="728">
+      <c r="D728" s="2" t="n"/>
+      <c r="Q728" s="2" t="n"/>
+    </row>
+    <row r="729">
+      <c r="D729" s="2" t="n"/>
+      <c r="Q729" s="2" t="n"/>
+    </row>
+    <row r="730">
+      <c r="D730" s="2" t="n"/>
+      <c r="Q730" s="2" t="n"/>
+    </row>
+    <row r="731">
+      <c r="D731" s="2" t="n"/>
+      <c r="Q731" s="2" t="n"/>
+    </row>
+    <row r="732">
+      <c r="D732" s="2" t="n"/>
+      <c r="Q732" s="2" t="n"/>
+    </row>
+    <row r="733">
+      <c r="D733" s="2" t="n"/>
+      <c r="Q733" s="2" t="n"/>
+    </row>
+    <row r="734">
+      <c r="D734" s="2" t="n"/>
+      <c r="Q734" s="2" t="n"/>
+    </row>
+    <row r="735">
+      <c r="D735" s="2" t="n"/>
+      <c r="Q735" s="2" t="n"/>
+    </row>
+    <row r="736">
+      <c r="D736" s="2" t="n"/>
+      <c r="Q736" s="2" t="n"/>
+    </row>
+    <row r="737">
+      <c r="D737" s="2" t="n"/>
+      <c r="Q737" s="2" t="n"/>
+    </row>
+    <row r="738">
+      <c r="D738" s="2" t="n"/>
+      <c r="Q738" s="2" t="n"/>
+    </row>
+    <row r="739">
+      <c r="D739" s="2" t="n"/>
+      <c r="Q739" s="2" t="n"/>
+    </row>
+    <row r="740">
+      <c r="D740" s="2" t="n"/>
+      <c r="Q740" s="2" t="n"/>
+    </row>
+    <row r="741">
+      <c r="D741" s="2" t="n"/>
+      <c r="Q741" s="2" t="n"/>
+    </row>
+    <row r="742">
+      <c r="D742" s="2" t="n"/>
+      <c r="Q742" s="2" t="n"/>
+    </row>
+    <row r="743">
+      <c r="D743" s="2" t="n"/>
+      <c r="Q743" s="2" t="n"/>
+    </row>
+    <row r="744">
+      <c r="D744" s="2" t="n"/>
+      <c r="Q744" s="2" t="n"/>
+    </row>
+    <row r="745">
+      <c r="D745" s="2" t="n"/>
+      <c r="Q745" s="2" t="n"/>
+    </row>
+    <row r="746">
+      <c r="D746" s="2" t="n"/>
+      <c r="Q746" s="2" t="n"/>
+    </row>
+    <row r="747">
+      <c r="D747" s="2" t="n"/>
+      <c r="Q747" s="2" t="n"/>
+    </row>
+    <row r="748">
+      <c r="D748" s="2" t="n"/>
+      <c r="Q748" s="2" t="n"/>
+    </row>
+    <row r="749">
+      <c r="D749" s="2" t="n"/>
+      <c r="Q749" s="2" t="n"/>
+    </row>
+    <row r="750">
+      <c r="D750" s="2" t="n"/>
+      <c r="Q750" s="2" t="n"/>
+    </row>
+    <row r="751">
+      <c r="D751" s="2" t="n"/>
+      <c r="Q751" s="2" t="n"/>
+    </row>
+    <row r="752">
+      <c r="D752" s="2" t="n"/>
+      <c r="Q752" s="2" t="n"/>
+    </row>
+    <row r="753">
+      <c r="D753" s="2" t="n"/>
+      <c r="Q753" s="2" t="n"/>
+    </row>
+    <row r="754">
+      <c r="D754" s="2" t="n"/>
+      <c r="Q754" s="2" t="n"/>
+    </row>
+    <row r="755">
+      <c r="D755" s="2" t="n"/>
+      <c r="Q755" s="2" t="n"/>
+    </row>
+    <row r="756">
+      <c r="D756" s="2" t="n"/>
+      <c r="Q756" s="2" t="n"/>
+    </row>
+    <row r="757">
+      <c r="D757" s="2" t="n"/>
+      <c r="Q757" s="2" t="n"/>
+    </row>
+    <row r="758">
+      <c r="D758" s="2" t="n"/>
+      <c r="Q758" s="2" t="n"/>
+    </row>
+    <row r="759">
+      <c r="D759" s="2" t="n"/>
+      <c r="Q759" s="2" t="n"/>
+    </row>
+    <row r="760">
+      <c r="D760" s="2" t="n"/>
+      <c r="Q760" s="2" t="n"/>
+    </row>
+    <row r="761">
+      <c r="D761" s="2" t="n"/>
+      <c r="Q761" s="2" t="n"/>
+    </row>
+    <row r="762">
+      <c r="D762" s="2" t="n"/>
+      <c r="Q762" s="2" t="n"/>
+    </row>
+    <row r="763">
+      <c r="D763" s="2" t="n"/>
+      <c r="Q763" s="2" t="n"/>
+    </row>
+    <row r="764">
+      <c r="D764" s="2" t="n"/>
+      <c r="Q764" s="2" t="n"/>
+    </row>
+    <row r="765">
+      <c r="D765" s="2" t="n"/>
+      <c r="Q765" s="2" t="n"/>
+    </row>
+    <row r="766">
+      <c r="D766" s="2" t="n"/>
+      <c r="Q766" s="2" t="n"/>
+    </row>
+    <row r="767">
+      <c r="D767" s="2" t="n"/>
+      <c r="Q767" s="2" t="n"/>
+    </row>
+    <row r="768">
+      <c r="D768" s="2" t="n"/>
+      <c r="Q768" s="2" t="n"/>
+    </row>
+    <row r="769">
+      <c r="D769" s="2" t="n"/>
+      <c r="Q769" s="2" t="n"/>
+    </row>
+    <row r="770">
+      <c r="D770" s="2" t="n"/>
+      <c r="Q770" s="2" t="n"/>
+    </row>
+    <row r="771">
+      <c r="D771" s="2" t="n"/>
+      <c r="Q771" s="2" t="n"/>
+    </row>
+    <row r="772">
+      <c r="D772" s="2" t="n"/>
+      <c r="Q772" s="2" t="n"/>
+    </row>
+    <row r="773">
+      <c r="D773" s="2" t="n"/>
+      <c r="Q773" s="2" t="n"/>
+    </row>
+    <row r="774">
+      <c r="D774" s="2" t="n"/>
+      <c r="Q774" s="2" t="n"/>
+    </row>
+    <row r="775">
+      <c r="D775" s="2" t="n"/>
+      <c r="Q775" s="2" t="n"/>
+    </row>
+    <row r="776">
+      <c r="D776" s="2" t="n"/>
+      <c r="Q776" s="2" t="n"/>
+    </row>
+    <row r="777">
+      <c r="D777" s="2" t="n"/>
+      <c r="Q777" s="2" t="n"/>
+    </row>
+    <row r="778">
+      <c r="D778" s="2" t="n"/>
+      <c r="Q778" s="2" t="n"/>
+    </row>
+    <row r="779">
+      <c r="D779" s="2" t="n"/>
+      <c r="Q779" s="2" t="n"/>
+    </row>
+    <row r="780">
+      <c r="D780" s="2" t="n"/>
+      <c r="Q780" s="2" t="n"/>
+    </row>
+    <row r="781">
+      <c r="D781" s="2" t="n"/>
+      <c r="Q781" s="2" t="n"/>
+    </row>
+    <row r="782">
+      <c r="D782" s="2" t="n"/>
+      <c r="Q782" s="2" t="n"/>
+    </row>
+    <row r="783">
+      <c r="D783" s="2" t="n"/>
+      <c r="Q783" s="2" t="n"/>
+    </row>
+    <row r="784">
+      <c r="D784" s="2" t="n"/>
+      <c r="Q784" s="2" t="n"/>
+    </row>
+    <row r="785">
+      <c r="D785" s="2" t="n"/>
+      <c r="Q785" s="2" t="n"/>
+    </row>
+    <row r="786">
+      <c r="D786" s="2" t="n"/>
+      <c r="Q786" s="2" t="n"/>
+    </row>
+    <row r="787">
+      <c r="D787" s="2" t="n"/>
+      <c r="Q787" s="2" t="n"/>
+    </row>
+    <row r="788">
+      <c r="D788" s="2" t="n"/>
+      <c r="Q788" s="2" t="n"/>
+    </row>
+    <row r="789">
+      <c r="D789" s="2" t="n"/>
+      <c r="Q789" s="2" t="n"/>
+    </row>
+    <row r="790">
+      <c r="D790" s="2" t="n"/>
+      <c r="Q790" s="2" t="n"/>
+    </row>
+    <row r="791">
+      <c r="D791" s="2" t="n"/>
+      <c r="Q791" s="2" t="n"/>
+    </row>
+    <row r="792">
+      <c r="D792" s="2" t="n"/>
+      <c r="Q792" s="2" t="n"/>
+    </row>
+    <row r="793">
+      <c r="D793" s="2" t="n"/>
+      <c r="Q793" s="2" t="n"/>
+    </row>
+    <row r="794">
+      <c r="D794" s="2" t="n"/>
+      <c r="Q794" s="2" t="n"/>
+    </row>
+    <row r="795">
+      <c r="D795" s="2" t="n"/>
+      <c r="Q795" s="2" t="n"/>
+    </row>
+    <row r="796">
+      <c r="D796" s="2" t="n"/>
+      <c r="Q796" s="2" t="n"/>
+    </row>
+    <row r="797">
+      <c r="D797" s="2" t="n"/>
+      <c r="Q797" s="2" t="n"/>
+    </row>
+    <row r="798">
+      <c r="D798" s="2" t="n"/>
+      <c r="Q798" s="2" t="n"/>
+    </row>
+    <row r="799">
+      <c r="D799" s="2" t="n"/>
+      <c r="Q799" s="2" t="n"/>
+    </row>
+    <row r="800">
+      <c r="D800" s="2" t="n"/>
+      <c r="Q800" s="2" t="n"/>
+    </row>
+    <row r="801">
+      <c r="D801" s="2" t="n"/>
+      <c r="Q801" s="2" t="n"/>
+    </row>
+    <row r="802">
+      <c r="D802" s="2" t="n"/>
+      <c r="Q802" s="2" t="n"/>
+    </row>
+    <row r="803">
+      <c r="D803" s="2" t="n"/>
+      <c r="Q803" s="2" t="n"/>
+    </row>
+    <row r="804">
+      <c r="D804" s="2" t="n"/>
+      <c r="Q804" s="2" t="n"/>
+    </row>
+    <row r="805">
+      <c r="D805" s="2" t="n"/>
+      <c r="Q805" s="2" t="n"/>
+    </row>
+    <row r="806">
+      <c r="D806" s="2" t="n"/>
+      <c r="Q806" s="2" t="n"/>
+    </row>
+    <row r="807">
+      <c r="D807" s="2" t="n"/>
+      <c r="Q807" s="2" t="n"/>
+    </row>
+    <row r="808">
+      <c r="D808" s="2" t="n"/>
+      <c r="Q808" s="2" t="n"/>
+    </row>
+    <row r="809">
+      <c r="D809" s="2" t="n"/>
+      <c r="Q809" s="2" t="n"/>
+    </row>
+    <row r="810">
+      <c r="D810" s="2" t="n"/>
+      <c r="Q810" s="2" t="n"/>
+    </row>
+    <row r="811">
+      <c r="D811" s="2" t="n"/>
+      <c r="Q811" s="2" t="n"/>
+    </row>
+    <row r="812">
+      <c r="D812" s="2" t="n"/>
+      <c r="Q812" s="2" t="n"/>
+    </row>
+    <row r="813">
+      <c r="D813" s="2" t="n"/>
+      <c r="Q813" s="2" t="n"/>
+    </row>
+    <row r="814">
+      <c r="D814" s="2" t="n"/>
+      <c r="Q814" s="2" t="n"/>
+    </row>
+    <row r="815">
+      <c r="D815" s="2" t="n"/>
+      <c r="Q815" s="2" t="n"/>
+    </row>
+    <row r="816">
+      <c r="D816" s="2" t="n"/>
+      <c r="Q816" s="2" t="n"/>
+    </row>
+    <row r="817">
+      <c r="D817" s="2" t="n"/>
+      <c r="Q817" s="2" t="n"/>
+    </row>
+    <row r="818">
+      <c r="D818" s="2" t="n"/>
+      <c r="Q818" s="2" t="n"/>
+    </row>
+    <row r="819">
+      <c r="D819" s="2" t="n"/>
+      <c r="Q819" s="2" t="n"/>
+    </row>
+    <row r="820">
+      <c r="D820" s="2" t="n"/>
+      <c r="Q820" s="2" t="n"/>
+    </row>
+    <row r="821">
+      <c r="D821" s="2" t="n"/>
+      <c r="Q821" s="2" t="n"/>
+    </row>
+    <row r="822">
+      <c r="D822" s="2" t="n"/>
+      <c r="Q822" s="2" t="n"/>
+    </row>
+    <row r="823">
+      <c r="D823" s="2" t="n"/>
+      <c r="Q823" s="2" t="n"/>
+    </row>
+    <row r="824">
+      <c r="D824" s="2" t="n"/>
+      <c r="Q824" s="2" t="n"/>
+    </row>
+    <row r="825">
+      <c r="D825" s="2" t="n"/>
+      <c r="Q825" s="2" t="n"/>
+    </row>
+    <row r="826">
+      <c r="D826" s="2" t="n"/>
+      <c r="Q826" s="2" t="n"/>
+    </row>
+    <row r="827">
+      <c r="D827" s="2" t="n"/>
+      <c r="Q827" s="2" t="n"/>
+    </row>
+    <row r="828">
+      <c r="D828" s="2" t="n"/>
+      <c r="Q828" s="2" t="n"/>
+    </row>
+    <row r="829">
+      <c r="D829" s="2" t="n"/>
+      <c r="Q829" s="2" t="n"/>
+    </row>
+    <row r="830">
+      <c r="D830" s="2" t="n"/>
+      <c r="Q830" s="2" t="n"/>
+    </row>
+    <row r="831">
+      <c r="D831" s="2" t="n"/>
+      <c r="Q831" s="2" t="n"/>
+    </row>
+    <row r="832">
+      <c r="D832" s="2" t="n"/>
+      <c r="Q832" s="2" t="n"/>
+    </row>
+    <row r="833">
+      <c r="D833" s="2" t="n"/>
+      <c r="Q833" s="2" t="n"/>
+    </row>
+    <row r="834">
+      <c r="D834" s="2" t="n"/>
+      <c r="Q834" s="2" t="n"/>
+    </row>
+    <row r="835">
+      <c r="D835" s="2" t="n"/>
+      <c r="Q835" s="2" t="n"/>
+    </row>
+    <row r="836">
+      <c r="D836" s="2" t="n"/>
+      <c r="Q836" s="2" t="n"/>
+    </row>
+    <row r="837">
+      <c r="D837" s="2" t="n"/>
+      <c r="Q837" s="2" t="n"/>
+    </row>
+    <row r="838">
+      <c r="D838" s="2" t="n"/>
+      <c r="Q838" s="2" t="n"/>
+    </row>
+    <row r="839">
+      <c r="D839" s="2" t="n"/>
+      <c r="Q839" s="2" t="n"/>
+    </row>
+    <row r="840">
+      <c r="D840" s="2" t="n"/>
+      <c r="Q840" s="2" t="n"/>
+    </row>
+    <row r="841">
+      <c r="D841" s="2" t="n"/>
+      <c r="Q841" s="2" t="n"/>
+    </row>
+    <row r="842">
+      <c r="D842" s="2" t="n"/>
+      <c r="Q842" s="2" t="n"/>
+    </row>
+    <row r="843">
+      <c r="D843" s="2" t="n"/>
+      <c r="Q843" s="2" t="n"/>
+    </row>
+    <row r="844">
+      <c r="D844" s="2" t="n"/>
+      <c r="Q844" s="2" t="n"/>
+    </row>
+    <row r="845">
+      <c r="D845" s="2" t="n"/>
+      <c r="Q845" s="2" t="n"/>
+    </row>
+    <row r="846">
+      <c r="D846" s="2" t="n"/>
+      <c r="Q846" s="2" t="n"/>
+    </row>
+    <row r="847">
+      <c r="D847" s="2" t="n"/>
+      <c r="Q847" s="2" t="n"/>
+    </row>
+    <row r="848">
+      <c r="D848" s="2" t="n"/>
+      <c r="Q848" s="2" t="n"/>
+    </row>
+    <row r="849">
+      <c r="D849" s="2" t="n"/>
+      <c r="Q849" s="2" t="n"/>
+    </row>
+    <row r="850">
+      <c r="D850" s="2" t="n"/>
+      <c r="Q850" s="2" t="n"/>
+    </row>
+    <row r="851">
+      <c r="D851" s="2" t="n"/>
+      <c r="Q851" s="2" t="n"/>
+    </row>
+    <row r="852">
+      <c r="D852" s="2" t="n"/>
+      <c r="Q852" s="2" t="n"/>
+    </row>
+    <row r="853">
+      <c r="D853" s="2" t="n"/>
+      <c r="Q853" s="2" t="n"/>
+    </row>
+    <row r="854">
+      <c r="D854" s="2" t="n"/>
+      <c r="Q854" s="2" t="n"/>
+    </row>
+    <row r="855">
+      <c r="D855" s="2" t="n"/>
+      <c r="Q855" s="2" t="n"/>
+    </row>
+    <row r="856">
+      <c r="D856" s="2" t="n"/>
+      <c r="Q856" s="2" t="n"/>
+    </row>
+    <row r="857">
+      <c r="D857" s="2" t="n"/>
+      <c r="Q857" s="2" t="n"/>
+    </row>
+    <row r="858">
+      <c r="D858" s="2" t="n"/>
+      <c r="Q858" s="2" t="n"/>
+    </row>
+    <row r="859">
+      <c r="D859" s="2" t="n"/>
+      <c r="Q859" s="2" t="n"/>
+    </row>
+    <row r="860">
+      <c r="D860" s="2" t="n"/>
+      <c r="Q860" s="2" t="n"/>
+    </row>
+    <row r="861">
+      <c r="D861" s="2" t="n"/>
+      <c r="Q861" s="2" t="n"/>
+    </row>
+    <row r="862">
+      <c r="D862" s="2" t="n"/>
+      <c r="Q862" s="2" t="n"/>
+    </row>
+    <row r="863">
+      <c r="D863" s="2" t="n"/>
+      <c r="Q863" s="2" t="n"/>
+    </row>
+    <row r="864">
+      <c r="D864" s="2" t="n"/>
+      <c r="Q864" s="2" t="n"/>
+    </row>
+    <row r="865">
+      <c r="D865" s="2" t="n"/>
+      <c r="Q865" s="2" t="n"/>
+    </row>
+    <row r="866">
+      <c r="D866" s="2" t="n"/>
+      <c r="Q866" s="2" t="n"/>
+    </row>
+    <row r="867">
+      <c r="D867" s="2" t="n"/>
+      <c r="Q867" s="2" t="n"/>
+    </row>
+    <row r="868">
+      <c r="D868" s="2" t="n"/>
+      <c r="Q868" s="2" t="n"/>
+    </row>
+    <row r="869">
+      <c r="D869" s="2" t="n"/>
+      <c r="Q869" s="2" t="n"/>
+    </row>
+    <row r="870">
+      <c r="D870" s="2" t="n"/>
+      <c r="Q870" s="2" t="n"/>
+    </row>
+    <row r="871">
+      <c r="D871" s="2" t="n"/>
+      <c r="Q871" s="2" t="n"/>
+    </row>
+    <row r="872">
+      <c r="D872" s="2" t="n"/>
+      <c r="Q872" s="2" t="n"/>
+    </row>
+    <row r="873">
+      <c r="D873" s="2" t="n"/>
+      <c r="Q873" s="2" t="n"/>
+    </row>
+    <row r="874">
+      <c r="D874" s="2" t="n"/>
+      <c r="Q874" s="2" t="n"/>
+    </row>
+    <row r="875">
+      <c r="D875" s="2" t="n"/>
+      <c r="Q875" s="2" t="n"/>
+    </row>
+    <row r="876">
+      <c r="D876" s="2" t="n"/>
+      <c r="Q876" s="2" t="n"/>
+    </row>
+    <row r="877">
+      <c r="D877" s="2" t="n"/>
+      <c r="Q877" s="2" t="n"/>
+    </row>
+    <row r="878">
+      <c r="D878" s="2" t="n"/>
+      <c r="Q878" s="2" t="n"/>
+    </row>
+    <row r="879">
+      <c r="D879" s="2" t="n"/>
+      <c r="Q879" s="2" t="n"/>
+    </row>
+    <row r="880">
+      <c r="D880" s="2" t="n"/>
+      <c r="Q880" s="2" t="n"/>
+    </row>
+    <row r="881">
+      <c r="D881" s="2" t="n"/>
+      <c r="Q881" s="2" t="n"/>
+    </row>
+    <row r="882">
+      <c r="D882" s="2" t="n"/>
+      <c r="Q882" s="2" t="n"/>
+    </row>
+    <row r="883">
+      <c r="D883" s="2" t="n"/>
+      <c r="Q883" s="2" t="n"/>
+    </row>
+    <row r="884">
+      <c r="D884" s="2" t="n"/>
+      <c r="Q884" s="2" t="n"/>
+    </row>
+    <row r="885">
+      <c r="D885" s="2" t="n"/>
+      <c r="Q885" s="2" t="n"/>
+    </row>
+    <row r="886">
+      <c r="D886" s="2" t="n"/>
+      <c r="Q886" s="2" t="n"/>
+    </row>
+    <row r="887">
+      <c r="D887" s="2" t="n"/>
+      <c r="Q887" s="2" t="n"/>
+    </row>
+    <row r="888">
+      <c r="D888" s="2" t="n"/>
+      <c r="Q888" s="2" t="n"/>
+    </row>
+    <row r="889">
+      <c r="D889" s="2" t="n"/>
+      <c r="Q889" s="2" t="n"/>
+    </row>
+    <row r="890">
+      <c r="D890" s="2" t="n"/>
+      <c r="Q890" s="2" t="n"/>
+    </row>
+    <row r="891">
+      <c r="D891" s="2" t="n"/>
+      <c r="Q891" s="2" t="n"/>
+    </row>
+    <row r="892">
+      <c r="D892" s="2" t="n"/>
+      <c r="Q892" s="2" t="n"/>
+    </row>
+    <row r="893">
+      <c r="D893" s="2" t="n"/>
+      <c r="Q893" s="2" t="n"/>
+    </row>
+    <row r="894">
+      <c r="D894" s="2" t="n"/>
+      <c r="Q894" s="2" t="n"/>
+    </row>
+    <row r="895">
+      <c r="D895" s="2" t="n"/>
+      <c r="Q895" s="2" t="n"/>
+    </row>
+    <row r="896">
+      <c r="D896" s="2" t="n"/>
+      <c r="Q896" s="2" t="n"/>
+    </row>
+    <row r="897">
+      <c r="D897" s="2" t="n"/>
+      <c r="Q897" s="2" t="n"/>
+    </row>
+    <row r="898">
+      <c r="D898" s="2" t="n"/>
+      <c r="Q898" s="2" t="n"/>
+    </row>
+    <row r="899">
+      <c r="D899" s="2" t="n"/>
+      <c r="Q899" s="2" t="n"/>
+    </row>
+    <row r="900">
+      <c r="D900" s="2" t="n"/>
+      <c r="Q900" s="2" t="n"/>
+    </row>
+    <row r="901">
+      <c r="D901" s="2" t="n"/>
+      <c r="Q901" s="2" t="n"/>
+    </row>
+    <row r="902">
+      <c r="D902" s="2" t="n"/>
+      <c r="Q902" s="2" t="n"/>
+    </row>
+    <row r="903">
+      <c r="D903" s="2" t="n"/>
+      <c r="Q903" s="2" t="n"/>
+    </row>
+    <row r="904">
+      <c r="D904" s="2" t="n"/>
+      <c r="Q904" s="2" t="n"/>
+    </row>
+    <row r="905">
+      <c r="D905" s="2" t="n"/>
+      <c r="Q905" s="2" t="n"/>
+    </row>
+    <row r="906">
+      <c r="D906" s="2" t="n"/>
+      <c r="Q906" s="2" t="n"/>
+    </row>
+    <row r="907">
+      <c r="D907" s="2" t="n"/>
+      <c r="Q907" s="2" t="n"/>
+    </row>
+    <row r="908">
+      <c r="D908" s="2" t="n"/>
+      <c r="Q908" s="2" t="n"/>
+    </row>
+    <row r="909">
+      <c r="D909" s="2" t="n"/>
+      <c r="Q909" s="2" t="n"/>
+    </row>
+    <row r="910">
+      <c r="D910" s="2" t="n"/>
+      <c r="Q910" s="2" t="n"/>
+    </row>
+    <row r="911">
+      <c r="D911" s="2" t="n"/>
+      <c r="Q911" s="2" t="n"/>
+    </row>
+    <row r="912">
+      <c r="D912" s="2" t="n"/>
+      <c r="Q912" s="2" t="n"/>
+    </row>
+    <row r="913">
+      <c r="D913" s="2" t="n"/>
+      <c r="Q913" s="2" t="n"/>
+    </row>
+    <row r="914">
+      <c r="D914" s="2" t="n"/>
+      <c r="Q914" s="2" t="n"/>
+    </row>
+    <row r="915">
+      <c r="D915" s="2" t="n"/>
+      <c r="Q915" s="2" t="n"/>
+    </row>
+    <row r="916">
+      <c r="D916" s="2" t="n"/>
+      <c r="Q916" s="2" t="n"/>
+    </row>
+    <row r="917">
+      <c r="D917" s="2" t="n"/>
+      <c r="Q917" s="2" t="n"/>
+    </row>
+    <row r="918">
+      <c r="D918" s="2" t="n"/>
+      <c r="Q918" s="2" t="n"/>
+    </row>
+    <row r="919">
+      <c r="D919" s="2" t="n"/>
+      <c r="Q919" s="2" t="n"/>
+    </row>
+    <row r="920">
+      <c r="D920" s="2" t="n"/>
+      <c r="Q920" s="2" t="n"/>
+    </row>
+    <row r="921">
+      <c r="D921" s="2" t="n"/>
+      <c r="Q921" s="2" t="n"/>
+    </row>
+    <row r="922">
+      <c r="D922" s="2" t="n"/>
+      <c r="Q922" s="2" t="n"/>
+    </row>
+    <row r="923">
+      <c r="D923" s="2" t="n"/>
+      <c r="Q923" s="2" t="n"/>
+    </row>
+    <row r="924">
+      <c r="D924" s="2" t="n"/>
+      <c r="Q924" s="2" t="n"/>
+    </row>
+    <row r="925">
+      <c r="D925" s="2" t="n"/>
+      <c r="Q925" s="2" t="n"/>
+    </row>
+    <row r="926">
+      <c r="D926" s="2" t="n"/>
+      <c r="Q926" s="2" t="n"/>
+    </row>
+    <row r="927">
+      <c r="D927" s="2" t="n"/>
+      <c r="Q927" s="2" t="n"/>
+    </row>
+    <row r="928">
+      <c r="D928" s="2" t="n"/>
+      <c r="Q928" s="2" t="n"/>
+    </row>
+    <row r="929">
+      <c r="D929" s="2" t="n"/>
+      <c r="Q929" s="2" t="n"/>
+    </row>
+    <row r="930">
+      <c r="D930" s="2" t="n"/>
+      <c r="Q930" s="2" t="n"/>
+    </row>
+    <row r="931">
+      <c r="D931" s="2" t="n"/>
+      <c r="Q931" s="2" t="n"/>
+    </row>
+    <row r="932">
+      <c r="D932" s="2" t="n"/>
+      <c r="Q932" s="2" t="n"/>
+    </row>
+    <row r="933">
+      <c r="D933" s="2" t="n"/>
+      <c r="Q933" s="2" t="n"/>
+    </row>
+    <row r="934">
+      <c r="D934" s="2" t="n"/>
+      <c r="Q934" s="2" t="n"/>
+    </row>
+    <row r="935">
+      <c r="D935" s="2" t="n"/>
+      <c r="Q935" s="2" t="n"/>
+    </row>
+    <row r="936">
+      <c r="D936" s="2" t="n"/>
+      <c r="Q936" s="2" t="n"/>
+    </row>
+    <row r="937">
+      <c r="D937" s="2" t="n"/>
+      <c r="Q937" s="2" t="n"/>
+    </row>
+    <row r="938">
+      <c r="D938" s="2" t="n"/>
+      <c r="Q938" s="2" t="n"/>
+    </row>
+    <row r="939">
+      <c r="D939" s="2" t="n"/>
+      <c r="Q939" s="2" t="n"/>
+    </row>
+    <row r="940">
+      <c r="D940" s="2" t="n"/>
+      <c r="Q940" s="2" t="n"/>
+    </row>
+    <row r="941">
+      <c r="D941" s="2" t="n"/>
+      <c r="Q941" s="2" t="n"/>
+    </row>
+    <row r="942">
+      <c r="D942" s="2" t="n"/>
+      <c r="Q942" s="2" t="n"/>
+    </row>
+    <row r="943">
+      <c r="D943" s="2" t="n"/>
+      <c r="Q943" s="2" t="n"/>
+    </row>
+    <row r="944">
+      <c r="D944" s="2" t="n"/>
+      <c r="Q944" s="2" t="n"/>
+    </row>
+    <row r="945">
+      <c r="D945" s="2" t="n"/>
+      <c r="Q945" s="2" t="n"/>
+    </row>
+    <row r="946">
+      <c r="D946" s="2" t="n"/>
+      <c r="Q946" s="2" t="n"/>
+    </row>
+    <row r="947">
+      <c r="D947" s="2" t="n"/>
+      <c r="Q947" s="2" t="n"/>
+    </row>
+    <row r="948">
+      <c r="D948" s="2" t="n"/>
+      <c r="Q948" s="2" t="n"/>
+    </row>
+    <row r="949">
+      <c r="D949" s="2" t="n"/>
+      <c r="Q949" s="2" t="n"/>
+    </row>
+    <row r="950">
+      <c r="D950" s="2" t="n"/>
+      <c r="Q950" s="2" t="n"/>
+    </row>
+    <row r="951">
+      <c r="D951" s="2" t="n"/>
+      <c r="Q951" s="2" t="n"/>
+    </row>
+    <row r="952">
+      <c r="D952" s="2" t="n"/>
+      <c r="Q952" s="2" t="n"/>
+    </row>
+    <row r="953">
+      <c r="D953" s="2" t="n"/>
+      <c r="Q953" s="2" t="n"/>
+    </row>
+    <row r="954">
+      <c r="D954" s="2" t="n"/>
+      <c r="Q954" s="2" t="n"/>
+    </row>
+    <row r="955">
+      <c r="D955" s="2" t="n"/>
+      <c r="Q955" s="2" t="n"/>
+    </row>
+    <row r="956">
+      <c r="D956" s="2" t="n"/>
+      <c r="Q956" s="2" t="n"/>
+    </row>
+    <row r="957">
+      <c r="D957" s="2" t="n"/>
+      <c r="Q957" s="2" t="n"/>
+    </row>
+    <row r="958">
+      <c r="D958" s="2" t="n"/>
+      <c r="Q958" s="2" t="n"/>
+    </row>
+    <row r="959">
+      <c r="D959" s="2" t="n"/>
+      <c r="Q959" s="2" t="n"/>
+    </row>
+    <row r="960">
+      <c r="D960" s="2" t="n"/>
+      <c r="Q960" s="2" t="n"/>
+    </row>
+    <row r="961">
+      <c r="D961" s="2" t="n"/>
+      <c r="Q961" s="2" t="n"/>
+    </row>
+    <row r="962">
+      <c r="D962" s="2" t="n"/>
+      <c r="Q962" s="2" t="n"/>
+    </row>
+    <row r="963">
+      <c r="D963" s="2" t="n"/>
+      <c r="Q963" s="2" t="n"/>
+    </row>
+    <row r="964">
+      <c r="D964" s="2" t="n"/>
+      <c r="Q964" s="2" t="n"/>
+    </row>
+    <row r="965">
+      <c r="D965" s="2" t="n"/>
+      <c r="Q965" s="2" t="n"/>
+    </row>
+    <row r="966">
+      <c r="D966" s="2" t="n"/>
+      <c r="Q966" s="2" t="n"/>
+    </row>
+    <row r="967">
+      <c r="D967" s="2" t="n"/>
+      <c r="Q967" s="2" t="n"/>
+    </row>
+    <row r="968">
+      <c r="D968" s="2" t="n"/>
+      <c r="Q968" s="2" t="n"/>
+    </row>
+    <row r="969">
+      <c r="D969" s="2" t="n"/>
+      <c r="Q969" s="2" t="n"/>
+    </row>
+    <row r="970">
+      <c r="D970" s="2" t="n"/>
+      <c r="Q970" s="2" t="n"/>
+    </row>
+    <row r="971">
+      <c r="D971" s="2" t="n"/>
+      <c r="Q971" s="2" t="n"/>
+    </row>
+    <row r="972">
+      <c r="D972" s="2" t="n"/>
+      <c r="Q972" s="2" t="n"/>
+    </row>
+    <row r="973">
+      <c r="D973" s="2" t="n"/>
+      <c r="Q973" s="2" t="n"/>
+    </row>
+    <row r="974">
+      <c r="D974" s="2" t="n"/>
+      <c r="Q974" s="2" t="n"/>
+    </row>
+    <row r="975">
+      <c r="D975" s="2" t="n"/>
+      <c r="Q975" s="2" t="n"/>
+    </row>
+    <row r="976">
+      <c r="D976" s="2" t="n"/>
+      <c r="Q976" s="2" t="n"/>
+    </row>
+    <row r="977">
+      <c r="D977" s="2" t="n"/>
+      <c r="Q977" s="2" t="n"/>
+    </row>
+    <row r="978">
+      <c r="D978" s="2" t="n"/>
+      <c r="Q978" s="2" t="n"/>
+    </row>
+    <row r="979">
+      <c r="D979" s="2" t="n"/>
+      <c r="Q979" s="2" t="n"/>
+    </row>
+    <row r="980">
+      <c r="D980" s="2" t="n"/>
+      <c r="Q980" s="2" t="n"/>
+    </row>
+    <row r="981">
+      <c r="D981" s="2" t="n"/>
+      <c r="Q981" s="2" t="n"/>
+    </row>
+    <row r="982">
+      <c r="D982" s="2" t="n"/>
+      <c r="Q982" s="2" t="n"/>
+    </row>
+    <row r="983">
+      <c r="D983" s="2" t="n"/>
+      <c r="Q983" s="2" t="n"/>
+    </row>
+    <row r="984">
+      <c r="D984" s="2" t="n"/>
+      <c r="Q984" s="2" t="n"/>
+    </row>
+    <row r="985">
+      <c r="D985" s="2" t="n"/>
+      <c r="Q985" s="2" t="n"/>
+    </row>
+    <row r="986">
+      <c r="D986" s="2" t="n"/>
+      <c r="Q986" s="2" t="n"/>
+    </row>
+    <row r="987">
+      <c r="D987" s="2" t="n"/>
+      <c r="Q987" s="2" t="n"/>
+    </row>
+    <row r="988">
+      <c r="D988" s="2" t="n"/>
+      <c r="Q988" s="2" t="n"/>
+    </row>
+    <row r="989">
+      <c r="D989" s="2" t="n"/>
+      <c r="Q989" s="2" t="n"/>
+    </row>
+    <row r="990">
+      <c r="D990" s="2" t="n"/>
+      <c r="Q990" s="2" t="n"/>
+    </row>
+    <row r="991">
+      <c r="D991" s="2" t="n"/>
+      <c r="Q991" s="2" t="n"/>
+    </row>
+    <row r="992">
+      <c r="D992" s="2" t="n"/>
+      <c r="Q992" s="2" t="n"/>
+    </row>
+    <row r="993">
+      <c r="D993" s="2" t="n"/>
+      <c r="Q993" s="2" t="n"/>
+    </row>
+    <row r="994">
+      <c r="D994" s="2" t="n"/>
+      <c r="Q994" s="2" t="n"/>
+    </row>
+    <row r="995">
+      <c r="D995" s="2" t="n"/>
+      <c r="Q995" s="2" t="n"/>
+    </row>
+    <row r="996">
+      <c r="D996" s="2" t="n"/>
+      <c r="Q996" s="2" t="n"/>
+    </row>
+    <row r="997">
+      <c r="D997" s="2" t="n"/>
+      <c r="Q997" s="2" t="n"/>
+    </row>
+    <row r="998">
+      <c r="D998" s="2" t="n"/>
+      <c r="Q998" s="2" t="n"/>
+    </row>
+    <row r="999">
+      <c r="D999" s="2" t="n"/>
+      <c r="Q999" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/doc/template_utilisateurs_kostango.xlsx
+++ b/doc/template_utilisateurs_kostango.xlsx
@@ -49,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,8 +430,8 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -456,7 +457,7 @@
           <t>Nom</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Matricule</t>
         </is>
@@ -483,12 +484,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Site (nom complet)</t>
+          <t>Intitulé département</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Intitulé service</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -521,4003 +522,4003 @@
           <t>Agence d'intérim</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Matricule N+1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="D3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="D4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="D5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="D6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="D7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="D8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="D10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="D11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="D12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="D13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="D14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="D15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="D16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="D17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="D18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="D19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="D20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="D21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="D22" s="2" t="n"/>
-      <c r="Q22" s="2" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="D23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="D24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="Q24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="D25" s="2" t="n"/>
-      <c r="Q25" s="2" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="D26" s="2" t="n"/>
-      <c r="Q26" s="2" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="D27" s="2" t="n"/>
-      <c r="Q27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="D28" s="2" t="n"/>
-      <c r="Q28" s="2" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="D29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="D30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="D31" s="2" t="n"/>
-      <c r="Q31" s="2" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="D32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="D33" s="2" t="n"/>
-      <c r="Q33" s="2" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="D34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="D35" s="2" t="n"/>
-      <c r="Q35" s="2" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="D36" s="2" t="n"/>
-      <c r="Q36" s="2" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="Q36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="D37" s="2" t="n"/>
-      <c r="Q37" s="2" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="Q37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="D38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="Q38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="D39" s="2" t="n"/>
-      <c r="Q39" s="2" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="D40" s="2" t="n"/>
-      <c r="Q40" s="2" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="Q40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="D41" s="2" t="n"/>
-      <c r="Q41" s="2" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="Q41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="D42" s="2" t="n"/>
-      <c r="Q42" s="2" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="Q42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="D44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="D45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="D46" s="2" t="n"/>
-      <c r="Q46" s="2" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="Q46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="D47" s="2" t="n"/>
-      <c r="Q47" s="2" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="Q47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="2" t="n"/>
-      <c r="Q48" s="2" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="Q48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="2" t="n"/>
-      <c r="Q49" s="2" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="Q49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="D50" s="2" t="n"/>
-      <c r="Q50" s="2" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="Q50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="D51" s="2" t="n"/>
-      <c r="Q51" s="2" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="Q51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="D52" s="2" t="n"/>
-      <c r="Q52" s="2" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="Q52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="D53" s="2" t="n"/>
-      <c r="Q53" s="2" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="Q53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="D54" s="2" t="n"/>
-      <c r="Q54" s="2" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="Q54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="D55" s="2" t="n"/>
-      <c r="Q55" s="2" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="Q55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="D56" s="2" t="n"/>
-      <c r="Q56" s="2" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="Q56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="D57" s="2" t="n"/>
-      <c r="Q57" s="2" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="Q57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="D58" s="2" t="n"/>
-      <c r="Q58" s="2" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="Q58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="D59" s="2" t="n"/>
-      <c r="Q59" s="2" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="Q59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="D60" s="2" t="n"/>
-      <c r="Q60" s="2" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="Q60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="D61" s="2" t="n"/>
-      <c r="Q61" s="2" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="Q61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="D62" s="2" t="n"/>
-      <c r="Q62" s="2" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="Q62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="D63" s="2" t="n"/>
-      <c r="Q63" s="2" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="Q63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="D64" s="2" t="n"/>
-      <c r="Q64" s="2" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="Q64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="D65" s="2" t="n"/>
-      <c r="Q65" s="2" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="Q65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="D66" s="2" t="n"/>
-      <c r="Q66" s="2" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="Q66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="D67" s="2" t="n"/>
-      <c r="Q67" s="2" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="Q67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="D68" s="2" t="n"/>
-      <c r="Q68" s="2" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="Q68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="D69" s="2" t="n"/>
-      <c r="Q69" s="2" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="Q69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="D70" s="2" t="n"/>
-      <c r="Q70" s="2" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="Q70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="D71" s="2" t="n"/>
-      <c r="Q71" s="2" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="Q71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="D72" s="2" t="n"/>
-      <c r="Q72" s="2" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="Q72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="D73" s="2" t="n"/>
-      <c r="Q73" s="2" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="Q73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="D74" s="2" t="n"/>
-      <c r="Q74" s="2" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="Q74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="D75" s="2" t="n"/>
-      <c r="Q75" s="2" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="Q75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="D76" s="2" t="n"/>
-      <c r="Q76" s="2" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="Q76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="D77" s="2" t="n"/>
-      <c r="Q77" s="2" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="Q77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="D78" s="2" t="n"/>
-      <c r="Q78" s="2" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="Q78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="D79" s="2" t="n"/>
-      <c r="Q79" s="2" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="Q79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="D80" s="2" t="n"/>
-      <c r="Q80" s="2" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="Q80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="D81" s="2" t="n"/>
-      <c r="Q81" s="2" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="Q81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="D82" s="2" t="n"/>
-      <c r="Q82" s="2" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="Q82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="D83" s="2" t="n"/>
-      <c r="Q83" s="2" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="Q83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="D84" s="2" t="n"/>
-      <c r="Q84" s="2" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="Q84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="D85" s="2" t="n"/>
-      <c r="Q85" s="2" t="n"/>
+      <c r="D85" s="3" t="n"/>
+      <c r="Q85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="D86" s="2" t="n"/>
-      <c r="Q86" s="2" t="n"/>
+      <c r="D86" s="3" t="n"/>
+      <c r="Q86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="2" t="n"/>
-      <c r="Q87" s="2" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="Q87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="D88" s="2" t="n"/>
-      <c r="Q88" s="2" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="Q88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="D89" s="2" t="n"/>
-      <c r="Q89" s="2" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="Q89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="D90" s="2" t="n"/>
-      <c r="Q90" s="2" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="Q90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="D91" s="2" t="n"/>
-      <c r="Q91" s="2" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="Q91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="2" t="n"/>
-      <c r="Q92" s="2" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="Q92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="2" t="n"/>
-      <c r="Q93" s="2" t="n"/>
+      <c r="D93" s="3" t="n"/>
+      <c r="Q93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="2" t="n"/>
-      <c r="Q94" s="2" t="n"/>
+      <c r="D94" s="3" t="n"/>
+      <c r="Q94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="2" t="n"/>
-      <c r="Q95" s="2" t="n"/>
+      <c r="D95" s="3" t="n"/>
+      <c r="Q95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="D96" s="2" t="n"/>
-      <c r="Q96" s="2" t="n"/>
+      <c r="D96" s="3" t="n"/>
+      <c r="Q96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="2" t="n"/>
-      <c r="Q97" s="2" t="n"/>
+      <c r="D97" s="3" t="n"/>
+      <c r="Q97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="D98" s="2" t="n"/>
-      <c r="Q98" s="2" t="n"/>
+      <c r="D98" s="3" t="n"/>
+      <c r="Q98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="D99" s="2" t="n"/>
-      <c r="Q99" s="2" t="n"/>
+      <c r="D99" s="3" t="n"/>
+      <c r="Q99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="2" t="n"/>
-      <c r="Q100" s="2" t="n"/>
+      <c r="D100" s="3" t="n"/>
+      <c r="Q100" s="3" t="n"/>
     </row>
     <row r="101">
-      <c r="D101" s="2" t="n"/>
-      <c r="Q101" s="2" t="n"/>
+      <c r="D101" s="3" t="n"/>
+      <c r="Q101" s="3" t="n"/>
     </row>
     <row r="102">
-      <c r="D102" s="2" t="n"/>
-      <c r="Q102" s="2" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="Q102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="2" t="n"/>
-      <c r="Q103" s="2" t="n"/>
+      <c r="D103" s="3" t="n"/>
+      <c r="Q103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="2" t="n"/>
-      <c r="Q104" s="2" t="n"/>
+      <c r="D104" s="3" t="n"/>
+      <c r="Q104" s="3" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="2" t="n"/>
-      <c r="Q105" s="2" t="n"/>
+      <c r="D105" s="3" t="n"/>
+      <c r="Q105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="2" t="n"/>
-      <c r="Q106" s="2" t="n"/>
+      <c r="D106" s="3" t="n"/>
+      <c r="Q106" s="3" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="2" t="n"/>
-      <c r="Q107" s="2" t="n"/>
+      <c r="D107" s="3" t="n"/>
+      <c r="Q107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="2" t="n"/>
-      <c r="Q108" s="2" t="n"/>
+      <c r="D108" s="3" t="n"/>
+      <c r="Q108" s="3" t="n"/>
     </row>
     <row r="109">
-      <c r="D109" s="2" t="n"/>
-      <c r="Q109" s="2" t="n"/>
+      <c r="D109" s="3" t="n"/>
+      <c r="Q109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="D110" s="2" t="n"/>
-      <c r="Q110" s="2" t="n"/>
+      <c r="D110" s="3" t="n"/>
+      <c r="Q110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="D111" s="2" t="n"/>
-      <c r="Q111" s="2" t="n"/>
+      <c r="D111" s="3" t="n"/>
+      <c r="Q111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="D112" s="2" t="n"/>
-      <c r="Q112" s="2" t="n"/>
+      <c r="D112" s="3" t="n"/>
+      <c r="Q112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="D113" s="2" t="n"/>
-      <c r="Q113" s="2" t="n"/>
+      <c r="D113" s="3" t="n"/>
+      <c r="Q113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="D114" s="2" t="n"/>
-      <c r="Q114" s="2" t="n"/>
+      <c r="D114" s="3" t="n"/>
+      <c r="Q114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="D115" s="2" t="n"/>
-      <c r="Q115" s="2" t="n"/>
+      <c r="D115" s="3" t="n"/>
+      <c r="Q115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="D116" s="2" t="n"/>
-      <c r="Q116" s="2" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="Q116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="D117" s="2" t="n"/>
-      <c r="Q117" s="2" t="n"/>
+      <c r="D117" s="3" t="n"/>
+      <c r="Q117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="D118" s="2" t="n"/>
-      <c r="Q118" s="2" t="n"/>
+      <c r="D118" s="3" t="n"/>
+      <c r="Q118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="D119" s="2" t="n"/>
-      <c r="Q119" s="2" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="Q119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="D120" s="2" t="n"/>
-      <c r="Q120" s="2" t="n"/>
+      <c r="D120" s="3" t="n"/>
+      <c r="Q120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="D121" s="2" t="n"/>
-      <c r="Q121" s="2" t="n"/>
+      <c r="D121" s="3" t="n"/>
+      <c r="Q121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="D122" s="2" t="n"/>
-      <c r="Q122" s="2" t="n"/>
+      <c r="D122" s="3" t="n"/>
+      <c r="Q122" s="3" t="n"/>
     </row>
     <row r="123">
-      <c r="D123" s="2" t="n"/>
-      <c r="Q123" s="2" t="n"/>
+      <c r="D123" s="3" t="n"/>
+      <c r="Q123" s="3" t="n"/>
     </row>
     <row r="124">
-      <c r="D124" s="2" t="n"/>
-      <c r="Q124" s="2" t="n"/>
+      <c r="D124" s="3" t="n"/>
+      <c r="Q124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="D125" s="2" t="n"/>
-      <c r="Q125" s="2" t="n"/>
+      <c r="D125" s="3" t="n"/>
+      <c r="Q125" s="3" t="n"/>
     </row>
     <row r="126">
-      <c r="D126" s="2" t="n"/>
-      <c r="Q126" s="2" t="n"/>
+      <c r="D126" s="3" t="n"/>
+      <c r="Q126" s="3" t="n"/>
     </row>
     <row r="127">
-      <c r="D127" s="2" t="n"/>
-      <c r="Q127" s="2" t="n"/>
+      <c r="D127" s="3" t="n"/>
+      <c r="Q127" s="3" t="n"/>
     </row>
     <row r="128">
-      <c r="D128" s="2" t="n"/>
-      <c r="Q128" s="2" t="n"/>
+      <c r="D128" s="3" t="n"/>
+      <c r="Q128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="D129" s="2" t="n"/>
-      <c r="Q129" s="2" t="n"/>
+      <c r="D129" s="3" t="n"/>
+      <c r="Q129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="D130" s="2" t="n"/>
-      <c r="Q130" s="2" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="Q130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="D131" s="2" t="n"/>
-      <c r="Q131" s="2" t="n"/>
+      <c r="D131" s="3" t="n"/>
+      <c r="Q131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="D132" s="2" t="n"/>
-      <c r="Q132" s="2" t="n"/>
+      <c r="D132" s="3" t="n"/>
+      <c r="Q132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="D133" s="2" t="n"/>
-      <c r="Q133" s="2" t="n"/>
+      <c r="D133" s="3" t="n"/>
+      <c r="Q133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="D134" s="2" t="n"/>
-      <c r="Q134" s="2" t="n"/>
+      <c r="D134" s="3" t="n"/>
+      <c r="Q134" s="3" t="n"/>
     </row>
     <row r="135">
-      <c r="D135" s="2" t="n"/>
-      <c r="Q135" s="2" t="n"/>
+      <c r="D135" s="3" t="n"/>
+      <c r="Q135" s="3" t="n"/>
     </row>
     <row r="136">
-      <c r="D136" s="2" t="n"/>
-      <c r="Q136" s="2" t="n"/>
+      <c r="D136" s="3" t="n"/>
+      <c r="Q136" s="3" t="n"/>
     </row>
     <row r="137">
-      <c r="D137" s="2" t="n"/>
-      <c r="Q137" s="2" t="n"/>
+      <c r="D137" s="3" t="n"/>
+      <c r="Q137" s="3" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" s="2" t="n"/>
-      <c r="Q138" s="2" t="n"/>
+      <c r="D138" s="3" t="n"/>
+      <c r="Q138" s="3" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" s="2" t="n"/>
-      <c r="Q139" s="2" t="n"/>
+      <c r="D139" s="3" t="n"/>
+      <c r="Q139" s="3" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" s="2" t="n"/>
-      <c r="Q140" s="2" t="n"/>
+      <c r="D140" s="3" t="n"/>
+      <c r="Q140" s="3" t="n"/>
     </row>
     <row r="141">
-      <c r="D141" s="2" t="n"/>
-      <c r="Q141" s="2" t="n"/>
+      <c r="D141" s="3" t="n"/>
+      <c r="Q141" s="3" t="n"/>
     </row>
     <row r="142">
-      <c r="D142" s="2" t="n"/>
-      <c r="Q142" s="2" t="n"/>
+      <c r="D142" s="3" t="n"/>
+      <c r="Q142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" s="2" t="n"/>
-      <c r="Q143" s="2" t="n"/>
+      <c r="D143" s="3" t="n"/>
+      <c r="Q143" s="3" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" s="2" t="n"/>
-      <c r="Q144" s="2" t="n"/>
+      <c r="D144" s="3" t="n"/>
+      <c r="Q144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" s="2" t="n"/>
-      <c r="Q145" s="2" t="n"/>
+      <c r="D145" s="3" t="n"/>
+      <c r="Q145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="D146" s="2" t="n"/>
-      <c r="Q146" s="2" t="n"/>
+      <c r="D146" s="3" t="n"/>
+      <c r="Q146" s="3" t="n"/>
     </row>
     <row r="147">
-      <c r="D147" s="2" t="n"/>
-      <c r="Q147" s="2" t="n"/>
+      <c r="D147" s="3" t="n"/>
+      <c r="Q147" s="3" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" s="2" t="n"/>
-      <c r="Q148" s="2" t="n"/>
+      <c r="D148" s="3" t="n"/>
+      <c r="Q148" s="3" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" s="2" t="n"/>
-      <c r="Q149" s="2" t="n"/>
+      <c r="D149" s="3" t="n"/>
+      <c r="Q149" s="3" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" s="2" t="n"/>
-      <c r="Q150" s="2" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="Q150" s="3" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" s="2" t="n"/>
-      <c r="Q151" s="2" t="n"/>
+      <c r="D151" s="3" t="n"/>
+      <c r="Q151" s="3" t="n"/>
     </row>
     <row r="152">
-      <c r="D152" s="2" t="n"/>
-      <c r="Q152" s="2" t="n"/>
+      <c r="D152" s="3" t="n"/>
+      <c r="Q152" s="3" t="n"/>
     </row>
     <row r="153">
-      <c r="D153" s="2" t="n"/>
-      <c r="Q153" s="2" t="n"/>
+      <c r="D153" s="3" t="n"/>
+      <c r="Q153" s="3" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" s="2" t="n"/>
-      <c r="Q154" s="2" t="n"/>
+      <c r="D154" s="3" t="n"/>
+      <c r="Q154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" s="2" t="n"/>
-      <c r="Q155" s="2" t="n"/>
+      <c r="D155" s="3" t="n"/>
+      <c r="Q155" s="3" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" s="2" t="n"/>
-      <c r="Q156" s="2" t="n"/>
+      <c r="D156" s="3" t="n"/>
+      <c r="Q156" s="3" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" s="2" t="n"/>
-      <c r="Q157" s="2" t="n"/>
+      <c r="D157" s="3" t="n"/>
+      <c r="Q157" s="3" t="n"/>
     </row>
     <row r="158">
-      <c r="D158" s="2" t="n"/>
-      <c r="Q158" s="2" t="n"/>
+      <c r="D158" s="3" t="n"/>
+      <c r="Q158" s="3" t="n"/>
     </row>
     <row r="159">
-      <c r="D159" s="2" t="n"/>
-      <c r="Q159" s="2" t="n"/>
+      <c r="D159" s="3" t="n"/>
+      <c r="Q159" s="3" t="n"/>
     </row>
     <row r="160">
-      <c r="D160" s="2" t="n"/>
-      <c r="Q160" s="2" t="n"/>
+      <c r="D160" s="3" t="n"/>
+      <c r="Q160" s="3" t="n"/>
     </row>
     <row r="161">
-      <c r="D161" s="2" t="n"/>
-      <c r="Q161" s="2" t="n"/>
+      <c r="D161" s="3" t="n"/>
+      <c r="Q161" s="3" t="n"/>
     </row>
     <row r="162">
-      <c r="D162" s="2" t="n"/>
-      <c r="Q162" s="2" t="n"/>
+      <c r="D162" s="3" t="n"/>
+      <c r="Q162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="D163" s="2" t="n"/>
-      <c r="Q163" s="2" t="n"/>
+      <c r="D163" s="3" t="n"/>
+      <c r="Q163" s="3" t="n"/>
     </row>
     <row r="164">
-      <c r="D164" s="2" t="n"/>
-      <c r="Q164" s="2" t="n"/>
+      <c r="D164" s="3" t="n"/>
+      <c r="Q164" s="3" t="n"/>
     </row>
     <row r="165">
-      <c r="D165" s="2" t="n"/>
-      <c r="Q165" s="2" t="n"/>
+      <c r="D165" s="3" t="n"/>
+      <c r="Q165" s="3" t="n"/>
     </row>
     <row r="166">
-      <c r="D166" s="2" t="n"/>
-      <c r="Q166" s="2" t="n"/>
+      <c r="D166" s="3" t="n"/>
+      <c r="Q166" s="3" t="n"/>
     </row>
     <row r="167">
-      <c r="D167" s="2" t="n"/>
-      <c r="Q167" s="2" t="n"/>
+      <c r="D167" s="3" t="n"/>
+      <c r="Q167" s="3" t="n"/>
     </row>
     <row r="168">
-      <c r="D168" s="2" t="n"/>
-      <c r="Q168" s="2" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="Q168" s="3" t="n"/>
     </row>
     <row r="169">
-      <c r="D169" s="2" t="n"/>
-      <c r="Q169" s="2" t="n"/>
+      <c r="D169" s="3" t="n"/>
+      <c r="Q169" s="3" t="n"/>
     </row>
     <row r="170">
-      <c r="D170" s="2" t="n"/>
-      <c r="Q170" s="2" t="n"/>
+      <c r="D170" s="3" t="n"/>
+      <c r="Q170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="D171" s="2" t="n"/>
-      <c r="Q171" s="2" t="n"/>
+      <c r="D171" s="3" t="n"/>
+      <c r="Q171" s="3" t="n"/>
     </row>
     <row r="172">
-      <c r="D172" s="2" t="n"/>
-      <c r="Q172" s="2" t="n"/>
+      <c r="D172" s="3" t="n"/>
+      <c r="Q172" s="3" t="n"/>
     </row>
     <row r="173">
-      <c r="D173" s="2" t="n"/>
-      <c r="Q173" s="2" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="Q173" s="3" t="n"/>
     </row>
     <row r="174">
-      <c r="D174" s="2" t="n"/>
-      <c r="Q174" s="2" t="n"/>
+      <c r="D174" s="3" t="n"/>
+      <c r="Q174" s="3" t="n"/>
     </row>
     <row r="175">
-      <c r="D175" s="2" t="n"/>
-      <c r="Q175" s="2" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="Q175" s="3" t="n"/>
     </row>
     <row r="176">
-      <c r="D176" s="2" t="n"/>
-      <c r="Q176" s="2" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="Q176" s="3" t="n"/>
     </row>
     <row r="177">
-      <c r="D177" s="2" t="n"/>
-      <c r="Q177" s="2" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="Q177" s="3" t="n"/>
     </row>
     <row r="178">
-      <c r="D178" s="2" t="n"/>
-      <c r="Q178" s="2" t="n"/>
+      <c r="D178" s="3" t="n"/>
+      <c r="Q178" s="3" t="n"/>
     </row>
     <row r="179">
-      <c r="D179" s="2" t="n"/>
-      <c r="Q179" s="2" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="Q179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="D180" s="2" t="n"/>
-      <c r="Q180" s="2" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="Q180" s="3" t="n"/>
     </row>
     <row r="181">
-      <c r="D181" s="2" t="n"/>
-      <c r="Q181" s="2" t="n"/>
+      <c r="D181" s="3" t="n"/>
+      <c r="Q181" s="3" t="n"/>
     </row>
     <row r="182">
-      <c r="D182" s="2" t="n"/>
-      <c r="Q182" s="2" t="n"/>
+      <c r="D182" s="3" t="n"/>
+      <c r="Q182" s="3" t="n"/>
     </row>
     <row r="183">
-      <c r="D183" s="2" t="n"/>
-      <c r="Q183" s="2" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="Q183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="D184" s="2" t="n"/>
-      <c r="Q184" s="2" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="Q184" s="3" t="n"/>
     </row>
     <row r="185">
-      <c r="D185" s="2" t="n"/>
-      <c r="Q185" s="2" t="n"/>
+      <c r="D185" s="3" t="n"/>
+      <c r="Q185" s="3" t="n"/>
     </row>
     <row r="186">
-      <c r="D186" s="2" t="n"/>
-      <c r="Q186" s="2" t="n"/>
+      <c r="D186" s="3" t="n"/>
+      <c r="Q186" s="3" t="n"/>
     </row>
     <row r="187">
-      <c r="D187" s="2" t="n"/>
-      <c r="Q187" s="2" t="n"/>
+      <c r="D187" s="3" t="n"/>
+      <c r="Q187" s="3" t="n"/>
     </row>
     <row r="188">
-      <c r="D188" s="2" t="n"/>
-      <c r="Q188" s="2" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="Q188" s="3" t="n"/>
     </row>
     <row r="189">
-      <c r="D189" s="2" t="n"/>
-      <c r="Q189" s="2" t="n"/>
+      <c r="D189" s="3" t="n"/>
+      <c r="Q189" s="3" t="n"/>
     </row>
     <row r="190">
-      <c r="D190" s="2" t="n"/>
-      <c r="Q190" s="2" t="n"/>
+      <c r="D190" s="3" t="n"/>
+      <c r="Q190" s="3" t="n"/>
     </row>
     <row r="191">
-      <c r="D191" s="2" t="n"/>
-      <c r="Q191" s="2" t="n"/>
+      <c r="D191" s="3" t="n"/>
+      <c r="Q191" s="3" t="n"/>
     </row>
     <row r="192">
-      <c r="D192" s="2" t="n"/>
-      <c r="Q192" s="2" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="Q192" s="3" t="n"/>
     </row>
     <row r="193">
-      <c r="D193" s="2" t="n"/>
-      <c r="Q193" s="2" t="n"/>
+      <c r="D193" s="3" t="n"/>
+      <c r="Q193" s="3" t="n"/>
     </row>
     <row r="194">
-      <c r="D194" s="2" t="n"/>
-      <c r="Q194" s="2" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="Q194" s="3" t="n"/>
     </row>
     <row r="195">
-      <c r="D195" s="2" t="n"/>
-      <c r="Q195" s="2" t="n"/>
+      <c r="D195" s="3" t="n"/>
+      <c r="Q195" s="3" t="n"/>
     </row>
     <row r="196">
-      <c r="D196" s="2" t="n"/>
-      <c r="Q196" s="2" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="Q196" s="3" t="n"/>
     </row>
     <row r="197">
-      <c r="D197" s="2" t="n"/>
-      <c r="Q197" s="2" t="n"/>
+      <c r="D197" s="3" t="n"/>
+      <c r="Q197" s="3" t="n"/>
     </row>
     <row r="198">
-      <c r="D198" s="2" t="n"/>
-      <c r="Q198" s="2" t="n"/>
+      <c r="D198" s="3" t="n"/>
+      <c r="Q198" s="3" t="n"/>
     </row>
     <row r="199">
-      <c r="D199" s="2" t="n"/>
-      <c r="Q199" s="2" t="n"/>
+      <c r="D199" s="3" t="n"/>
+      <c r="Q199" s="3" t="n"/>
     </row>
     <row r="200">
-      <c r="D200" s="2" t="n"/>
-      <c r="Q200" s="2" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="Q200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="D201" s="2" t="n"/>
-      <c r="Q201" s="2" t="n"/>
+      <c r="D201" s="3" t="n"/>
+      <c r="Q201" s="3" t="n"/>
     </row>
     <row r="202">
-      <c r="D202" s="2" t="n"/>
-      <c r="Q202" s="2" t="n"/>
+      <c r="D202" s="3" t="n"/>
+      <c r="Q202" s="3" t="n"/>
     </row>
     <row r="203">
-      <c r="D203" s="2" t="n"/>
-      <c r="Q203" s="2" t="n"/>
+      <c r="D203" s="3" t="n"/>
+      <c r="Q203" s="3" t="n"/>
     </row>
     <row r="204">
-      <c r="D204" s="2" t="n"/>
-      <c r="Q204" s="2" t="n"/>
+      <c r="D204" s="3" t="n"/>
+      <c r="Q204" s="3" t="n"/>
     </row>
     <row r="205">
-      <c r="D205" s="2" t="n"/>
-      <c r="Q205" s="2" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="Q205" s="3" t="n"/>
     </row>
     <row r="206">
-      <c r="D206" s="2" t="n"/>
-      <c r="Q206" s="2" t="n"/>
+      <c r="D206" s="3" t="n"/>
+      <c r="Q206" s="3" t="n"/>
     </row>
     <row r="207">
-      <c r="D207" s="2" t="n"/>
-      <c r="Q207" s="2" t="n"/>
+      <c r="D207" s="3" t="n"/>
+      <c r="Q207" s="3" t="n"/>
     </row>
     <row r="208">
-      <c r="D208" s="2" t="n"/>
-      <c r="Q208" s="2" t="n"/>
+      <c r="D208" s="3" t="n"/>
+      <c r="Q208" s="3" t="n"/>
     </row>
     <row r="209">
-      <c r="D209" s="2" t="n"/>
-      <c r="Q209" s="2" t="n"/>
+      <c r="D209" s="3" t="n"/>
+      <c r="Q209" s="3" t="n"/>
     </row>
     <row r="210">
-      <c r="D210" s="2" t="n"/>
-      <c r="Q210" s="2" t="n"/>
+      <c r="D210" s="3" t="n"/>
+      <c r="Q210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="D211" s="2" t="n"/>
-      <c r="Q211" s="2" t="n"/>
+      <c r="D211" s="3" t="n"/>
+      <c r="Q211" s="3" t="n"/>
     </row>
     <row r="212">
-      <c r="D212" s="2" t="n"/>
-      <c r="Q212" s="2" t="n"/>
+      <c r="D212" s="3" t="n"/>
+      <c r="Q212" s="3" t="n"/>
     </row>
     <row r="213">
-      <c r="D213" s="2" t="n"/>
-      <c r="Q213" s="2" t="n"/>
+      <c r="D213" s="3" t="n"/>
+      <c r="Q213" s="3" t="n"/>
     </row>
     <row r="214">
-      <c r="D214" s="2" t="n"/>
-      <c r="Q214" s="2" t="n"/>
+      <c r="D214" s="3" t="n"/>
+      <c r="Q214" s="3" t="n"/>
     </row>
     <row r="215">
-      <c r="D215" s="2" t="n"/>
-      <c r="Q215" s="2" t="n"/>
+      <c r="D215" s="3" t="n"/>
+      <c r="Q215" s="3" t="n"/>
     </row>
     <row r="216">
-      <c r="D216" s="2" t="n"/>
-      <c r="Q216" s="2" t="n"/>
+      <c r="D216" s="3" t="n"/>
+      <c r="Q216" s="3" t="n"/>
     </row>
     <row r="217">
-      <c r="D217" s="2" t="n"/>
-      <c r="Q217" s="2" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="Q217" s="3" t="n"/>
     </row>
     <row r="218">
-      <c r="D218" s="2" t="n"/>
-      <c r="Q218" s="2" t="n"/>
+      <c r="D218" s="3" t="n"/>
+      <c r="Q218" s="3" t="n"/>
     </row>
     <row r="219">
-      <c r="D219" s="2" t="n"/>
-      <c r="Q219" s="2" t="n"/>
+      <c r="D219" s="3" t="n"/>
+      <c r="Q219" s="3" t="n"/>
     </row>
     <row r="220">
-      <c r="D220" s="2" t="n"/>
-      <c r="Q220" s="2" t="n"/>
+      <c r="D220" s="3" t="n"/>
+      <c r="Q220" s="3" t="n"/>
     </row>
     <row r="221">
-      <c r="D221" s="2" t="n"/>
-      <c r="Q221" s="2" t="n"/>
+      <c r="D221" s="3" t="n"/>
+      <c r="Q221" s="3" t="n"/>
     </row>
     <row r="222">
-      <c r="D222" s="2" t="n"/>
-      <c r="Q222" s="2" t="n"/>
+      <c r="D222" s="3" t="n"/>
+      <c r="Q222" s="3" t="n"/>
     </row>
     <row r="223">
-      <c r="D223" s="2" t="n"/>
-      <c r="Q223" s="2" t="n"/>
+      <c r="D223" s="3" t="n"/>
+      <c r="Q223" s="3" t="n"/>
     </row>
     <row r="224">
-      <c r="D224" s="2" t="n"/>
-      <c r="Q224" s="2" t="n"/>
+      <c r="D224" s="3" t="n"/>
+      <c r="Q224" s="3" t="n"/>
     </row>
     <row r="225">
-      <c r="D225" s="2" t="n"/>
-      <c r="Q225" s="2" t="n"/>
+      <c r="D225" s="3" t="n"/>
+      <c r="Q225" s="3" t="n"/>
     </row>
     <row r="226">
-      <c r="D226" s="2" t="n"/>
-      <c r="Q226" s="2" t="n"/>
+      <c r="D226" s="3" t="n"/>
+      <c r="Q226" s="3" t="n"/>
     </row>
     <row r="227">
-      <c r="D227" s="2" t="n"/>
-      <c r="Q227" s="2" t="n"/>
+      <c r="D227" s="3" t="n"/>
+      <c r="Q227" s="3" t="n"/>
     </row>
     <row r="228">
-      <c r="D228" s="2" t="n"/>
-      <c r="Q228" s="2" t="n"/>
+      <c r="D228" s="3" t="n"/>
+      <c r="Q228" s="3" t="n"/>
     </row>
     <row r="229">
-      <c r="D229" s="2" t="n"/>
-      <c r="Q229" s="2" t="n"/>
+      <c r="D229" s="3" t="n"/>
+      <c r="Q229" s="3" t="n"/>
     </row>
     <row r="230">
-      <c r="D230" s="2" t="n"/>
-      <c r="Q230" s="2" t="n"/>
+      <c r="D230" s="3" t="n"/>
+      <c r="Q230" s="3" t="n"/>
     </row>
     <row r="231">
-      <c r="D231" s="2" t="n"/>
-      <c r="Q231" s="2" t="n"/>
+      <c r="D231" s="3" t="n"/>
+      <c r="Q231" s="3" t="n"/>
     </row>
     <row r="232">
-      <c r="D232" s="2" t="n"/>
-      <c r="Q232" s="2" t="n"/>
+      <c r="D232" s="3" t="n"/>
+      <c r="Q232" s="3" t="n"/>
     </row>
     <row r="233">
-      <c r="D233" s="2" t="n"/>
-      <c r="Q233" s="2" t="n"/>
+      <c r="D233" s="3" t="n"/>
+      <c r="Q233" s="3" t="n"/>
     </row>
     <row r="234">
-      <c r="D234" s="2" t="n"/>
-      <c r="Q234" s="2" t="n"/>
+      <c r="D234" s="3" t="n"/>
+      <c r="Q234" s="3" t="n"/>
     </row>
     <row r="235">
-      <c r="D235" s="2" t="n"/>
-      <c r="Q235" s="2" t="n"/>
+      <c r="D235" s="3" t="n"/>
+      <c r="Q235" s="3" t="n"/>
     </row>
     <row r="236">
-      <c r="D236" s="2" t="n"/>
-      <c r="Q236" s="2" t="n"/>
+      <c r="D236" s="3" t="n"/>
+      <c r="Q236" s="3" t="n"/>
     </row>
     <row r="237">
-      <c r="D237" s="2" t="n"/>
-      <c r="Q237" s="2" t="n"/>
+      <c r="D237" s="3" t="n"/>
+      <c r="Q237" s="3" t="n"/>
     </row>
     <row r="238">
-      <c r="D238" s="2" t="n"/>
-      <c r="Q238" s="2" t="n"/>
+      <c r="D238" s="3" t="n"/>
+      <c r="Q238" s="3" t="n"/>
     </row>
     <row r="239">
-      <c r="D239" s="2" t="n"/>
-      <c r="Q239" s="2" t="n"/>
+      <c r="D239" s="3" t="n"/>
+      <c r="Q239" s="3" t="n"/>
     </row>
     <row r="240">
-      <c r="D240" s="2" t="n"/>
-      <c r="Q240" s="2" t="n"/>
+      <c r="D240" s="3" t="n"/>
+      <c r="Q240" s="3" t="n"/>
     </row>
     <row r="241">
-      <c r="D241" s="2" t="n"/>
-      <c r="Q241" s="2" t="n"/>
+      <c r="D241" s="3" t="n"/>
+      <c r="Q241" s="3" t="n"/>
     </row>
     <row r="242">
-      <c r="D242" s="2" t="n"/>
-      <c r="Q242" s="2" t="n"/>
+      <c r="D242" s="3" t="n"/>
+      <c r="Q242" s="3" t="n"/>
     </row>
     <row r="243">
-      <c r="D243" s="2" t="n"/>
-      <c r="Q243" s="2" t="n"/>
+      <c r="D243" s="3" t="n"/>
+      <c r="Q243" s="3" t="n"/>
     </row>
     <row r="244">
-      <c r="D244" s="2" t="n"/>
-      <c r="Q244" s="2" t="n"/>
+      <c r="D244" s="3" t="n"/>
+      <c r="Q244" s="3" t="n"/>
     </row>
     <row r="245">
-      <c r="D245" s="2" t="n"/>
-      <c r="Q245" s="2" t="n"/>
+      <c r="D245" s="3" t="n"/>
+      <c r="Q245" s="3" t="n"/>
     </row>
     <row r="246">
-      <c r="D246" s="2" t="n"/>
-      <c r="Q246" s="2" t="n"/>
+      <c r="D246" s="3" t="n"/>
+      <c r="Q246" s="3" t="n"/>
     </row>
     <row r="247">
-      <c r="D247" s="2" t="n"/>
-      <c r="Q247" s="2" t="n"/>
+      <c r="D247" s="3" t="n"/>
+      <c r="Q247" s="3" t="n"/>
     </row>
     <row r="248">
-      <c r="D248" s="2" t="n"/>
-      <c r="Q248" s="2" t="n"/>
+      <c r="D248" s="3" t="n"/>
+      <c r="Q248" s="3" t="n"/>
     </row>
     <row r="249">
-      <c r="D249" s="2" t="n"/>
-      <c r="Q249" s="2" t="n"/>
+      <c r="D249" s="3" t="n"/>
+      <c r="Q249" s="3" t="n"/>
     </row>
     <row r="250">
-      <c r="D250" s="2" t="n"/>
-      <c r="Q250" s="2" t="n"/>
+      <c r="D250" s="3" t="n"/>
+      <c r="Q250" s="3" t="n"/>
     </row>
     <row r="251">
-      <c r="D251" s="2" t="n"/>
-      <c r="Q251" s="2" t="n"/>
+      <c r="D251" s="3" t="n"/>
+      <c r="Q251" s="3" t="n"/>
     </row>
     <row r="252">
-      <c r="D252" s="2" t="n"/>
-      <c r="Q252" s="2" t="n"/>
+      <c r="D252" s="3" t="n"/>
+      <c r="Q252" s="3" t="n"/>
     </row>
     <row r="253">
-      <c r="D253" s="2" t="n"/>
-      <c r="Q253" s="2" t="n"/>
+      <c r="D253" s="3" t="n"/>
+      <c r="Q253" s="3" t="n"/>
     </row>
     <row r="254">
-      <c r="D254" s="2" t="n"/>
-      <c r="Q254" s="2" t="n"/>
+      <c r="D254" s="3" t="n"/>
+      <c r="Q254" s="3" t="n"/>
     </row>
     <row r="255">
-      <c r="D255" s="2" t="n"/>
-      <c r="Q255" s="2" t="n"/>
+      <c r="D255" s="3" t="n"/>
+      <c r="Q255" s="3" t="n"/>
     </row>
     <row r="256">
-      <c r="D256" s="2" t="n"/>
-      <c r="Q256" s="2" t="n"/>
+      <c r="D256" s="3" t="n"/>
+      <c r="Q256" s="3" t="n"/>
     </row>
     <row r="257">
-      <c r="D257" s="2" t="n"/>
-      <c r="Q257" s="2" t="n"/>
+      <c r="D257" s="3" t="n"/>
+      <c r="Q257" s="3" t="n"/>
     </row>
     <row r="258">
-      <c r="D258" s="2" t="n"/>
-      <c r="Q258" s="2" t="n"/>
+      <c r="D258" s="3" t="n"/>
+      <c r="Q258" s="3" t="n"/>
     </row>
     <row r="259">
-      <c r="D259" s="2" t="n"/>
-      <c r="Q259" s="2" t="n"/>
+      <c r="D259" s="3" t="n"/>
+      <c r="Q259" s="3" t="n"/>
     </row>
     <row r="260">
-      <c r="D260" s="2" t="n"/>
-      <c r="Q260" s="2" t="n"/>
+      <c r="D260" s="3" t="n"/>
+      <c r="Q260" s="3" t="n"/>
     </row>
     <row r="261">
-      <c r="D261" s="2" t="n"/>
-      <c r="Q261" s="2" t="n"/>
+      <c r="D261" s="3" t="n"/>
+      <c r="Q261" s="3" t="n"/>
     </row>
     <row r="262">
-      <c r="D262" s="2" t="n"/>
-      <c r="Q262" s="2" t="n"/>
+      <c r="D262" s="3" t="n"/>
+      <c r="Q262" s="3" t="n"/>
     </row>
     <row r="263">
-      <c r="D263" s="2" t="n"/>
-      <c r="Q263" s="2" t="n"/>
+      <c r="D263" s="3" t="n"/>
+      <c r="Q263" s="3" t="n"/>
     </row>
     <row r="264">
-      <c r="D264" s="2" t="n"/>
-      <c r="Q264" s="2" t="n"/>
+      <c r="D264" s="3" t="n"/>
+      <c r="Q264" s="3" t="n"/>
     </row>
     <row r="265">
-      <c r="D265" s="2" t="n"/>
-      <c r="Q265" s="2" t="n"/>
+      <c r="D265" s="3" t="n"/>
+      <c r="Q265" s="3" t="n"/>
     </row>
     <row r="266">
-      <c r="D266" s="2" t="n"/>
-      <c r="Q266" s="2" t="n"/>
+      <c r="D266" s="3" t="n"/>
+      <c r="Q266" s="3" t="n"/>
     </row>
     <row r="267">
-      <c r="D267" s="2" t="n"/>
-      <c r="Q267" s="2" t="n"/>
+      <c r="D267" s="3" t="n"/>
+      <c r="Q267" s="3" t="n"/>
     </row>
     <row r="268">
-      <c r="D268" s="2" t="n"/>
-      <c r="Q268" s="2" t="n"/>
+      <c r="D268" s="3" t="n"/>
+      <c r="Q268" s="3" t="n"/>
     </row>
     <row r="269">
-      <c r="D269" s="2" t="n"/>
-      <c r="Q269" s="2" t="n"/>
+      <c r="D269" s="3" t="n"/>
+      <c r="Q269" s="3" t="n"/>
     </row>
     <row r="270">
-      <c r="D270" s="2" t="n"/>
-      <c r="Q270" s="2" t="n"/>
+      <c r="D270" s="3" t="n"/>
+      <c r="Q270" s="3" t="n"/>
     </row>
     <row r="271">
-      <c r="D271" s="2" t="n"/>
-      <c r="Q271" s="2" t="n"/>
+      <c r="D271" s="3" t="n"/>
+      <c r="Q271" s="3" t="n"/>
     </row>
     <row r="272">
-      <c r="D272" s="2" t="n"/>
-      <c r="Q272" s="2" t="n"/>
+      <c r="D272" s="3" t="n"/>
+      <c r="Q272" s="3" t="n"/>
     </row>
     <row r="273">
-      <c r="D273" s="2" t="n"/>
-      <c r="Q273" s="2" t="n"/>
+      <c r="D273" s="3" t="n"/>
+      <c r="Q273" s="3" t="n"/>
     </row>
     <row r="274">
-      <c r="D274" s="2" t="n"/>
-      <c r="Q274" s="2" t="n"/>
+      <c r="D274" s="3" t="n"/>
+      <c r="Q274" s="3" t="n"/>
     </row>
     <row r="275">
-      <c r="D275" s="2" t="n"/>
-      <c r="Q275" s="2" t="n"/>
+      <c r="D275" s="3" t="n"/>
+      <c r="Q275" s="3" t="n"/>
     </row>
     <row r="276">
-      <c r="D276" s="2" t="n"/>
-      <c r="Q276" s="2" t="n"/>
+      <c r="D276" s="3" t="n"/>
+      <c r="Q276" s="3" t="n"/>
     </row>
     <row r="277">
-      <c r="D277" s="2" t="n"/>
-      <c r="Q277" s="2" t="n"/>
+      <c r="D277" s="3" t="n"/>
+      <c r="Q277" s="3" t="n"/>
     </row>
     <row r="278">
-      <c r="D278" s="2" t="n"/>
-      <c r="Q278" s="2" t="n"/>
+      <c r="D278" s="3" t="n"/>
+      <c r="Q278" s="3" t="n"/>
     </row>
     <row r="279">
-      <c r="D279" s="2" t="n"/>
-      <c r="Q279" s="2" t="n"/>
+      <c r="D279" s="3" t="n"/>
+      <c r="Q279" s="3" t="n"/>
     </row>
     <row r="280">
-      <c r="D280" s="2" t="n"/>
-      <c r="Q280" s="2" t="n"/>
+      <c r="D280" s="3" t="n"/>
+      <c r="Q280" s="3" t="n"/>
     </row>
     <row r="281">
-      <c r="D281" s="2" t="n"/>
-      <c r="Q281" s="2" t="n"/>
+      <c r="D281" s="3" t="n"/>
+      <c r="Q281" s="3" t="n"/>
     </row>
     <row r="282">
-      <c r="D282" s="2" t="n"/>
-      <c r="Q282" s="2" t="n"/>
+      <c r="D282" s="3" t="n"/>
+      <c r="Q282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="D283" s="2" t="n"/>
-      <c r="Q283" s="2" t="n"/>
+      <c r="D283" s="3" t="n"/>
+      <c r="Q283" s="3" t="n"/>
     </row>
     <row r="284">
-      <c r="D284" s="2" t="n"/>
-      <c r="Q284" s="2" t="n"/>
+      <c r="D284" s="3" t="n"/>
+      <c r="Q284" s="3" t="n"/>
     </row>
     <row r="285">
-      <c r="D285" s="2" t="n"/>
-      <c r="Q285" s="2" t="n"/>
+      <c r="D285" s="3" t="n"/>
+      <c r="Q285" s="3" t="n"/>
     </row>
     <row r="286">
-      <c r="D286" s="2" t="n"/>
-      <c r="Q286" s="2" t="n"/>
+      <c r="D286" s="3" t="n"/>
+      <c r="Q286" s="3" t="n"/>
     </row>
     <row r="287">
-      <c r="D287" s="2" t="n"/>
-      <c r="Q287" s="2" t="n"/>
+      <c r="D287" s="3" t="n"/>
+      <c r="Q287" s="3" t="n"/>
     </row>
     <row r="288">
-      <c r="D288" s="2" t="n"/>
-      <c r="Q288" s="2" t="n"/>
+      <c r="D288" s="3" t="n"/>
+      <c r="Q288" s="3" t="n"/>
     </row>
     <row r="289">
-      <c r="D289" s="2" t="n"/>
-      <c r="Q289" s="2" t="n"/>
+      <c r="D289" s="3" t="n"/>
+      <c r="Q289" s="3" t="n"/>
     </row>
     <row r="290">
-      <c r="D290" s="2" t="n"/>
-      <c r="Q290" s="2" t="n"/>
+      <c r="D290" s="3" t="n"/>
+      <c r="Q290" s="3" t="n"/>
     </row>
     <row r="291">
-      <c r="D291" s="2" t="n"/>
-      <c r="Q291" s="2" t="n"/>
+      <c r="D291" s="3" t="n"/>
+      <c r="Q291" s="3" t="n"/>
     </row>
     <row r="292">
-      <c r="D292" s="2" t="n"/>
-      <c r="Q292" s="2" t="n"/>
+      <c r="D292" s="3" t="n"/>
+      <c r="Q292" s="3" t="n"/>
     </row>
     <row r="293">
-      <c r="D293" s="2" t="n"/>
-      <c r="Q293" s="2" t="n"/>
+      <c r="D293" s="3" t="n"/>
+      <c r="Q293" s="3" t="n"/>
     </row>
     <row r="294">
-      <c r="D294" s="2" t="n"/>
-      <c r="Q294" s="2" t="n"/>
+      <c r="D294" s="3" t="n"/>
+      <c r="Q294" s="3" t="n"/>
     </row>
     <row r="295">
-      <c r="D295" s="2" t="n"/>
-      <c r="Q295" s="2" t="n"/>
+      <c r="D295" s="3" t="n"/>
+      <c r="Q295" s="3" t="n"/>
     </row>
     <row r="296">
-      <c r="D296" s="2" t="n"/>
-      <c r="Q296" s="2" t="n"/>
+      <c r="D296" s="3" t="n"/>
+      <c r="Q296" s="3" t="n"/>
     </row>
     <row r="297">
-      <c r="D297" s="2" t="n"/>
-      <c r="Q297" s="2" t="n"/>
+      <c r="D297" s="3" t="n"/>
+      <c r="Q297" s="3" t="n"/>
     </row>
     <row r="298">
-      <c r="D298" s="2" t="n"/>
-      <c r="Q298" s="2" t="n"/>
+      <c r="D298" s="3" t="n"/>
+      <c r="Q298" s="3" t="n"/>
     </row>
     <row r="299">
-      <c r="D299" s="2" t="n"/>
-      <c r="Q299" s="2" t="n"/>
+      <c r="D299" s="3" t="n"/>
+      <c r="Q299" s="3" t="n"/>
     </row>
     <row r="300">
-      <c r="D300" s="2" t="n"/>
-      <c r="Q300" s="2" t="n"/>
+      <c r="D300" s="3" t="n"/>
+      <c r="Q300" s="3" t="n"/>
     </row>
     <row r="301">
-      <c r="D301" s="2" t="n"/>
-      <c r="Q301" s="2" t="n"/>
+      <c r="D301" s="3" t="n"/>
+      <c r="Q301" s="3" t="n"/>
     </row>
     <row r="302">
-      <c r="D302" s="2" t="n"/>
-      <c r="Q302" s="2" t="n"/>
+      <c r="D302" s="3" t="n"/>
+      <c r="Q302" s="3" t="n"/>
     </row>
     <row r="303">
-      <c r="D303" s="2" t="n"/>
-      <c r="Q303" s="2" t="n"/>
+      <c r="D303" s="3" t="n"/>
+      <c r="Q303" s="3" t="n"/>
     </row>
     <row r="304">
-      <c r="D304" s="2" t="n"/>
-      <c r="Q304" s="2" t="n"/>
+      <c r="D304" s="3" t="n"/>
+      <c r="Q304" s="3" t="n"/>
     </row>
     <row r="305">
-      <c r="D305" s="2" t="n"/>
-      <c r="Q305" s="2" t="n"/>
+      <c r="D305" s="3" t="n"/>
+      <c r="Q305" s="3" t="n"/>
     </row>
     <row r="306">
-      <c r="D306" s="2" t="n"/>
-      <c r="Q306" s="2" t="n"/>
+      <c r="D306" s="3" t="n"/>
+      <c r="Q306" s="3" t="n"/>
     </row>
     <row r="307">
-      <c r="D307" s="2" t="n"/>
-      <c r="Q307" s="2" t="n"/>
+      <c r="D307" s="3" t="n"/>
+      <c r="Q307" s="3" t="n"/>
     </row>
     <row r="308">
-      <c r="D308" s="2" t="n"/>
-      <c r="Q308" s="2" t="n"/>
+      <c r="D308" s="3" t="n"/>
+      <c r="Q308" s="3" t="n"/>
     </row>
     <row r="309">
-      <c r="D309" s="2" t="n"/>
-      <c r="Q309" s="2" t="n"/>
+      <c r="D309" s="3" t="n"/>
+      <c r="Q309" s="3" t="n"/>
     </row>
     <row r="310">
-      <c r="D310" s="2" t="n"/>
-      <c r="Q310" s="2" t="n"/>
+      <c r="D310" s="3" t="n"/>
+      <c r="Q310" s="3" t="n"/>
     </row>
     <row r="311">
-      <c r="D311" s="2" t="n"/>
-      <c r="Q311" s="2" t="n"/>
+      <c r="D311" s="3" t="n"/>
+      <c r="Q311" s="3" t="n"/>
     </row>
     <row r="312">
-      <c r="D312" s="2" t="n"/>
-      <c r="Q312" s="2" t="n"/>
+      <c r="D312" s="3" t="n"/>
+      <c r="Q312" s="3" t="n"/>
     </row>
     <row r="313">
-      <c r="D313" s="2" t="n"/>
-      <c r="Q313" s="2" t="n"/>
+      <c r="D313" s="3" t="n"/>
+      <c r="Q313" s="3" t="n"/>
     </row>
     <row r="314">
-      <c r="D314" s="2" t="n"/>
-      <c r="Q314" s="2" t="n"/>
+      <c r="D314" s="3" t="n"/>
+      <c r="Q314" s="3" t="n"/>
     </row>
     <row r="315">
-      <c r="D315" s="2" t="n"/>
-      <c r="Q315" s="2" t="n"/>
+      <c r="D315" s="3" t="n"/>
+      <c r="Q315" s="3" t="n"/>
     </row>
     <row r="316">
-      <c r="D316" s="2" t="n"/>
-      <c r="Q316" s="2" t="n"/>
+      <c r="D316" s="3" t="n"/>
+      <c r="Q316" s="3" t="n"/>
     </row>
     <row r="317">
-      <c r="D317" s="2" t="n"/>
-      <c r="Q317" s="2" t="n"/>
+      <c r="D317" s="3" t="n"/>
+      <c r="Q317" s="3" t="n"/>
     </row>
     <row r="318">
-      <c r="D318" s="2" t="n"/>
-      <c r="Q318" s="2" t="n"/>
+      <c r="D318" s="3" t="n"/>
+      <c r="Q318" s="3" t="n"/>
     </row>
     <row r="319">
-      <c r="D319" s="2" t="n"/>
-      <c r="Q319" s="2" t="n"/>
+      <c r="D319" s="3" t="n"/>
+      <c r="Q319" s="3" t="n"/>
     </row>
     <row r="320">
-      <c r="D320" s="2" t="n"/>
-      <c r="Q320" s="2" t="n"/>
+      <c r="D320" s="3" t="n"/>
+      <c r="Q320" s="3" t="n"/>
     </row>
     <row r="321">
-      <c r="D321" s="2" t="n"/>
-      <c r="Q321" s="2" t="n"/>
+      <c r="D321" s="3" t="n"/>
+      <c r="Q321" s="3" t="n"/>
     </row>
     <row r="322">
-      <c r="D322" s="2" t="n"/>
-      <c r="Q322" s="2" t="n"/>
+      <c r="D322" s="3" t="n"/>
+      <c r="Q322" s="3" t="n"/>
     </row>
     <row r="323">
-      <c r="D323" s="2" t="n"/>
-      <c r="Q323" s="2" t="n"/>
+      <c r="D323" s="3" t="n"/>
+      <c r="Q323" s="3" t="n"/>
     </row>
     <row r="324">
-      <c r="D324" s="2" t="n"/>
-      <c r="Q324" s="2" t="n"/>
+      <c r="D324" s="3" t="n"/>
+      <c r="Q324" s="3" t="n"/>
     </row>
     <row r="325">
-      <c r="D325" s="2" t="n"/>
-      <c r="Q325" s="2" t="n"/>
+      <c r="D325" s="3" t="n"/>
+      <c r="Q325" s="3" t="n"/>
     </row>
     <row r="326">
-      <c r="D326" s="2" t="n"/>
-      <c r="Q326" s="2" t="n"/>
+      <c r="D326" s="3" t="n"/>
+      <c r="Q326" s="3" t="n"/>
     </row>
     <row r="327">
-      <c r="D327" s="2" t="n"/>
-      <c r="Q327" s="2" t="n"/>
+      <c r="D327" s="3" t="n"/>
+      <c r="Q327" s="3" t="n"/>
     </row>
     <row r="328">
-      <c r="D328" s="2" t="n"/>
-      <c r="Q328" s="2" t="n"/>
+      <c r="D328" s="3" t="n"/>
+      <c r="Q328" s="3" t="n"/>
     </row>
     <row r="329">
-      <c r="D329" s="2" t="n"/>
-      <c r="Q329" s="2" t="n"/>
+      <c r="D329" s="3" t="n"/>
+      <c r="Q329" s="3" t="n"/>
     </row>
     <row r="330">
-      <c r="D330" s="2" t="n"/>
-      <c r="Q330" s="2" t="n"/>
+      <c r="D330" s="3" t="n"/>
+      <c r="Q330" s="3" t="n"/>
     </row>
     <row r="331">
-      <c r="D331" s="2" t="n"/>
-      <c r="Q331" s="2" t="n"/>
+      <c r="D331" s="3" t="n"/>
+      <c r="Q331" s="3" t="n"/>
     </row>
     <row r="332">
-      <c r="D332" s="2" t="n"/>
-      <c r="Q332" s="2" t="n"/>
+      <c r="D332" s="3" t="n"/>
+      <c r="Q332" s="3" t="n"/>
     </row>
     <row r="333">
-      <c r="D333" s="2" t="n"/>
-      <c r="Q333" s="2" t="n"/>
+      <c r="D333" s="3" t="n"/>
+      <c r="Q333" s="3" t="n"/>
     </row>
     <row r="334">
-      <c r="D334" s="2" t="n"/>
-      <c r="Q334" s="2" t="n"/>
+      <c r="D334" s="3" t="n"/>
+      <c r="Q334" s="3" t="n"/>
     </row>
     <row r="335">
-      <c r="D335" s="2" t="n"/>
-      <c r="Q335" s="2" t="n"/>
+      <c r="D335" s="3" t="n"/>
+      <c r="Q335" s="3" t="n"/>
     </row>
     <row r="336">
-      <c r="D336" s="2" t="n"/>
-      <c r="Q336" s="2" t="n"/>
+      <c r="D336" s="3" t="n"/>
+      <c r="Q336" s="3" t="n"/>
     </row>
     <row r="337">
-      <c r="D337" s="2" t="n"/>
-      <c r="Q337" s="2" t="n"/>
+      <c r="D337" s="3" t="n"/>
+      <c r="Q337" s="3" t="n"/>
     </row>
     <row r="338">
-      <c r="D338" s="2" t="n"/>
-      <c r="Q338" s="2" t="n"/>
+      <c r="D338" s="3" t="n"/>
+      <c r="Q338" s="3" t="n"/>
     </row>
     <row r="339">
-      <c r="D339" s="2" t="n"/>
-      <c r="Q339" s="2" t="n"/>
+      <c r="D339" s="3" t="n"/>
+      <c r="Q339" s="3" t="n"/>
     </row>
     <row r="340">
-      <c r="D340" s="2" t="n"/>
-      <c r="Q340" s="2" t="n"/>
+      <c r="D340" s="3" t="n"/>
+      <c r="Q340" s="3" t="n"/>
     </row>
     <row r="341">
-      <c r="D341" s="2" t="n"/>
-      <c r="Q341" s="2" t="n"/>
+      <c r="D341" s="3" t="n"/>
+      <c r="Q341" s="3" t="n"/>
     </row>
     <row r="342">
-      <c r="D342" s="2" t="n"/>
-      <c r="Q342" s="2" t="n"/>
+      <c r="D342" s="3" t="n"/>
+      <c r="Q342" s="3" t="n"/>
     </row>
     <row r="343">
-      <c r="D343" s="2" t="n"/>
-      <c r="Q343" s="2" t="n"/>
+      <c r="D343" s="3" t="n"/>
+      <c r="Q343" s="3" t="n"/>
     </row>
     <row r="344">
-      <c r="D344" s="2" t="n"/>
-      <c r="Q344" s="2" t="n"/>
+      <c r="D344" s="3" t="n"/>
+      <c r="Q344" s="3" t="n"/>
     </row>
     <row r="345">
-      <c r="D345" s="2" t="n"/>
-      <c r="Q345" s="2" t="n"/>
+      <c r="D345" s="3" t="n"/>
+      <c r="Q345" s="3" t="n"/>
     </row>
     <row r="346">
-      <c r="D346" s="2" t="n"/>
-      <c r="Q346" s="2" t="n"/>
+      <c r="D346" s="3" t="n"/>
+      <c r="Q346" s="3" t="n"/>
     </row>
     <row r="347">
-      <c r="D347" s="2" t="n"/>
-      <c r="Q347" s="2" t="n"/>
+      <c r="D347" s="3" t="n"/>
+      <c r="Q347" s="3" t="n"/>
     </row>
     <row r="348">
-      <c r="D348" s="2" t="n"/>
-      <c r="Q348" s="2" t="n"/>
+      <c r="D348" s="3" t="n"/>
+      <c r="Q348" s="3" t="n"/>
     </row>
     <row r="349">
-      <c r="D349" s="2" t="n"/>
-      <c r="Q349" s="2" t="n"/>
+      <c r="D349" s="3" t="n"/>
+      <c r="Q349" s="3" t="n"/>
     </row>
     <row r="350">
-      <c r="D350" s="2" t="n"/>
-      <c r="Q350" s="2" t="n"/>
+      <c r="D350" s="3" t="n"/>
+      <c r="Q350" s="3" t="n"/>
     </row>
     <row r="351">
-      <c r="D351" s="2" t="n"/>
-      <c r="Q351" s="2" t="n"/>
+      <c r="D351" s="3" t="n"/>
+      <c r="Q351" s="3" t="n"/>
     </row>
     <row r="352">
-      <c r="D352" s="2" t="n"/>
-      <c r="Q352" s="2" t="n"/>
+      <c r="D352" s="3" t="n"/>
+      <c r="Q352" s="3" t="n"/>
     </row>
     <row r="353">
-      <c r="D353" s="2" t="n"/>
-      <c r="Q353" s="2" t="n"/>
+      <c r="D353" s="3" t="n"/>
+      <c r="Q353" s="3" t="n"/>
     </row>
     <row r="354">
-      <c r="D354" s="2" t="n"/>
-      <c r="Q354" s="2" t="n"/>
+      <c r="D354" s="3" t="n"/>
+      <c r="Q354" s="3" t="n"/>
     </row>
     <row r="355">
-      <c r="D355" s="2" t="n"/>
-      <c r="Q355" s="2" t="n"/>
+      <c r="D355" s="3" t="n"/>
+      <c r="Q355" s="3" t="n"/>
     </row>
     <row r="356">
-      <c r="D356" s="2" t="n"/>
-      <c r="Q356" s="2" t="n"/>
+      <c r="D356" s="3" t="n"/>
+      <c r="Q356" s="3" t="n"/>
     </row>
     <row r="357">
-      <c r="D357" s="2" t="n"/>
-      <c r="Q357" s="2" t="n"/>
+      <c r="D357" s="3" t="n"/>
+      <c r="Q357" s="3" t="n"/>
     </row>
     <row r="358">
-      <c r="D358" s="2" t="n"/>
-      <c r="Q358" s="2" t="n"/>
+      <c r="D358" s="3" t="n"/>
+      <c r="Q358" s="3" t="n"/>
     </row>
     <row r="359">
-      <c r="D359" s="2" t="n"/>
-      <c r="Q359" s="2" t="n"/>
+      <c r="D359" s="3" t="n"/>
+      <c r="Q359" s="3" t="n"/>
     </row>
     <row r="360">
-      <c r="D360" s="2" t="n"/>
-      <c r="Q360" s="2" t="n"/>
+      <c r="D360" s="3" t="n"/>
+      <c r="Q360" s="3" t="n"/>
     </row>
     <row r="361">
-      <c r="D361" s="2" t="n"/>
-      <c r="Q361" s="2" t="n"/>
+      <c r="D361" s="3" t="n"/>
+      <c r="Q361" s="3" t="n"/>
     </row>
     <row r="362">
-      <c r="D362" s="2" t="n"/>
-      <c r="Q362" s="2" t="n"/>
+      <c r="D362" s="3" t="n"/>
+      <c r="Q362" s="3" t="n"/>
     </row>
     <row r="363">
-      <c r="D363" s="2" t="n"/>
-      <c r="Q363" s="2" t="n"/>
+      <c r="D363" s="3" t="n"/>
+      <c r="Q363" s="3" t="n"/>
     </row>
     <row r="364">
-      <c r="D364" s="2" t="n"/>
-      <c r="Q364" s="2" t="n"/>
+      <c r="D364" s="3" t="n"/>
+      <c r="Q364" s="3" t="n"/>
     </row>
     <row r="365">
-      <c r="D365" s="2" t="n"/>
-      <c r="Q365" s="2" t="n"/>
+      <c r="D365" s="3" t="n"/>
+      <c r="Q365" s="3" t="n"/>
     </row>
     <row r="366">
-      <c r="D366" s="2" t="n"/>
-      <c r="Q366" s="2" t="n"/>
+      <c r="D366" s="3" t="n"/>
+      <c r="Q366" s="3" t="n"/>
     </row>
     <row r="367">
-      <c r="D367" s="2" t="n"/>
-      <c r="Q367" s="2" t="n"/>
+      <c r="D367" s="3" t="n"/>
+      <c r="Q367" s="3" t="n"/>
     </row>
     <row r="368">
-      <c r="D368" s="2" t="n"/>
-      <c r="Q368" s="2" t="n"/>
+      <c r="D368" s="3" t="n"/>
+      <c r="Q368" s="3" t="n"/>
     </row>
     <row r="369">
-      <c r="D369" s="2" t="n"/>
-      <c r="Q369" s="2" t="n"/>
+      <c r="D369" s="3" t="n"/>
+      <c r="Q369" s="3" t="n"/>
     </row>
     <row r="370">
-      <c r="D370" s="2" t="n"/>
-      <c r="Q370" s="2" t="n"/>
+      <c r="D370" s="3" t="n"/>
+      <c r="Q370" s="3" t="n"/>
     </row>
     <row r="371">
-      <c r="D371" s="2" t="n"/>
-      <c r="Q371" s="2" t="n"/>
+      <c r="D371" s="3" t="n"/>
+      <c r="Q371" s="3" t="n"/>
     </row>
     <row r="372">
-      <c r="D372" s="2" t="n"/>
-      <c r="Q372" s="2" t="n"/>
+      <c r="D372" s="3" t="n"/>
+      <c r="Q372" s="3" t="n"/>
     </row>
     <row r="373">
-      <c r="D373" s="2" t="n"/>
-      <c r="Q373" s="2" t="n"/>
+      <c r="D373" s="3" t="n"/>
+      <c r="Q373" s="3" t="n"/>
     </row>
     <row r="374">
-      <c r="D374" s="2" t="n"/>
-      <c r="Q374" s="2" t="n"/>
+      <c r="D374" s="3" t="n"/>
+      <c r="Q374" s="3" t="n"/>
     </row>
     <row r="375">
-      <c r="D375" s="2" t="n"/>
-      <c r="Q375" s="2" t="n"/>
+      <c r="D375" s="3" t="n"/>
+      <c r="Q375" s="3" t="n"/>
     </row>
     <row r="376">
-      <c r="D376" s="2" t="n"/>
-      <c r="Q376" s="2" t="n"/>
+      <c r="D376" s="3" t="n"/>
+      <c r="Q376" s="3" t="n"/>
     </row>
     <row r="377">
-      <c r="D377" s="2" t="n"/>
-      <c r="Q377" s="2" t="n"/>
+      <c r="D377" s="3" t="n"/>
+      <c r="Q377" s="3" t="n"/>
     </row>
     <row r="378">
-      <c r="D378" s="2" t="n"/>
-      <c r="Q378" s="2" t="n"/>
+      <c r="D378" s="3" t="n"/>
+      <c r="Q378" s="3" t="n"/>
     </row>
     <row r="379">
-      <c r="D379" s="2" t="n"/>
-      <c r="Q379" s="2" t="n"/>
+      <c r="D379" s="3" t="n"/>
+      <c r="Q379" s="3" t="n"/>
     </row>
     <row r="380">
-      <c r="D380" s="2" t="n"/>
-      <c r="Q380" s="2" t="n"/>
+      <c r="D380" s="3" t="n"/>
+      <c r="Q380" s="3" t="n"/>
     </row>
     <row r="381">
-      <c r="D381" s="2" t="n"/>
-      <c r="Q381" s="2" t="n"/>
+      <c r="D381" s="3" t="n"/>
+      <c r="Q381" s="3" t="n"/>
     </row>
     <row r="382">
-      <c r="D382" s="2" t="n"/>
-      <c r="Q382" s="2" t="n"/>
+      <c r="D382" s="3" t="n"/>
+      <c r="Q382" s="3" t="n"/>
     </row>
     <row r="383">
-      <c r="D383" s="2" t="n"/>
-      <c r="Q383" s="2" t="n"/>
+      <c r="D383" s="3" t="n"/>
+      <c r="Q383" s="3" t="n"/>
     </row>
     <row r="384">
-      <c r="D384" s="2" t="n"/>
-      <c r="Q384" s="2" t="n"/>
+      <c r="D384" s="3" t="n"/>
+      <c r="Q384" s="3" t="n"/>
     </row>
     <row r="385">
-      <c r="D385" s="2" t="n"/>
-      <c r="Q385" s="2" t="n"/>
+      <c r="D385" s="3" t="n"/>
+      <c r="Q385" s="3" t="n"/>
     </row>
     <row r="386">
-      <c r="D386" s="2" t="n"/>
-      <c r="Q386" s="2" t="n"/>
+      <c r="D386" s="3" t="n"/>
+      <c r="Q386" s="3" t="n"/>
     </row>
     <row r="387">
-      <c r="D387" s="2" t="n"/>
-      <c r="Q387" s="2" t="n"/>
+      <c r="D387" s="3" t="n"/>
+      <c r="Q387" s="3" t="n"/>
     </row>
     <row r="388">
-      <c r="D388" s="2" t="n"/>
-      <c r="Q388" s="2" t="n"/>
+      <c r="D388" s="3" t="n"/>
+      <c r="Q388" s="3" t="n"/>
     </row>
     <row r="389">
-      <c r="D389" s="2" t="n"/>
-      <c r="Q389" s="2" t="n"/>
+      <c r="D389" s="3" t="n"/>
+      <c r="Q389" s="3" t="n"/>
     </row>
     <row r="390">
-      <c r="D390" s="2" t="n"/>
-      <c r="Q390" s="2" t="n"/>
+      <c r="D390" s="3" t="n"/>
+      <c r="Q390" s="3" t="n"/>
     </row>
     <row r="391">
-      <c r="D391" s="2" t="n"/>
-      <c r="Q391" s="2" t="n"/>
+      <c r="D391" s="3" t="n"/>
+      <c r="Q391" s="3" t="n"/>
     </row>
     <row r="392">
-      <c r="D392" s="2" t="n"/>
-      <c r="Q392" s="2" t="n"/>
+      <c r="D392" s="3" t="n"/>
+      <c r="Q392" s="3" t="n"/>
     </row>
     <row r="393">
-      <c r="D393" s="2" t="n"/>
-      <c r="Q393" s="2" t="n"/>
+      <c r="D393" s="3" t="n"/>
+      <c r="Q393" s="3" t="n"/>
     </row>
     <row r="394">
-      <c r="D394" s="2" t="n"/>
-      <c r="Q394" s="2" t="n"/>
+      <c r="D394" s="3" t="n"/>
+      <c r="Q394" s="3" t="n"/>
     </row>
     <row r="395">
-      <c r="D395" s="2" t="n"/>
-      <c r="Q395" s="2" t="n"/>
+      <c r="D395" s="3" t="n"/>
+      <c r="Q395" s="3" t="n"/>
     </row>
     <row r="396">
-      <c r="D396" s="2" t="n"/>
-      <c r="Q396" s="2" t="n"/>
+      <c r="D396" s="3" t="n"/>
+      <c r="Q396" s="3" t="n"/>
     </row>
     <row r="397">
-      <c r="D397" s="2" t="n"/>
-      <c r="Q397" s="2" t="n"/>
+      <c r="D397" s="3" t="n"/>
+      <c r="Q397" s="3" t="n"/>
     </row>
     <row r="398">
-      <c r="D398" s="2" t="n"/>
-      <c r="Q398" s="2" t="n"/>
+      <c r="D398" s="3" t="n"/>
+      <c r="Q398" s="3" t="n"/>
     </row>
     <row r="399">
-      <c r="D399" s="2" t="n"/>
-      <c r="Q399" s="2" t="n"/>
+      <c r="D399" s="3" t="n"/>
+      <c r="Q399" s="3" t="n"/>
     </row>
     <row r="400">
-      <c r="D400" s="2" t="n"/>
-      <c r="Q400" s="2" t="n"/>
+      <c r="D400" s="3" t="n"/>
+      <c r="Q400" s="3" t="n"/>
     </row>
     <row r="401">
-      <c r="D401" s="2" t="n"/>
-      <c r="Q401" s="2" t="n"/>
+      <c r="D401" s="3" t="n"/>
+      <c r="Q401" s="3" t="n"/>
     </row>
     <row r="402">
-      <c r="D402" s="2" t="n"/>
-      <c r="Q402" s="2" t="n"/>
+      <c r="D402" s="3" t="n"/>
+      <c r="Q402" s="3" t="n"/>
     </row>
     <row r="403">
-      <c r="D403" s="2" t="n"/>
-      <c r="Q403" s="2" t="n"/>
+      <c r="D403" s="3" t="n"/>
+      <c r="Q403" s="3" t="n"/>
     </row>
     <row r="404">
-      <c r="D404" s="2" t="n"/>
-      <c r="Q404" s="2" t="n"/>
+      <c r="D404" s="3" t="n"/>
+      <c r="Q404" s="3" t="n"/>
     </row>
     <row r="405">
-      <c r="D405" s="2" t="n"/>
-      <c r="Q405" s="2" t="n"/>
+      <c r="D405" s="3" t="n"/>
+      <c r="Q405" s="3" t="n"/>
     </row>
     <row r="406">
-      <c r="D406" s="2" t="n"/>
-      <c r="Q406" s="2" t="n"/>
+      <c r="D406" s="3" t="n"/>
+      <c r="Q406" s="3" t="n"/>
     </row>
     <row r="407">
-      <c r="D407" s="2" t="n"/>
-      <c r="Q407" s="2" t="n"/>
+      <c r="D407" s="3" t="n"/>
+      <c r="Q407" s="3" t="n"/>
     </row>
     <row r="408">
-      <c r="D408" s="2" t="n"/>
-      <c r="Q408" s="2" t="n"/>
+      <c r="D408" s="3" t="n"/>
+      <c r="Q408" s="3" t="n"/>
     </row>
     <row r="409">
-      <c r="D409" s="2" t="n"/>
-      <c r="Q409" s="2" t="n"/>
+      <c r="D409" s="3" t="n"/>
+      <c r="Q409" s="3" t="n"/>
     </row>
     <row r="410">
-      <c r="D410" s="2" t="n"/>
-      <c r="Q410" s="2" t="n"/>
+      <c r="D410" s="3" t="n"/>
+      <c r="Q410" s="3" t="n"/>
     </row>
     <row r="411">
-      <c r="D411" s="2" t="n"/>
-      <c r="Q411" s="2" t="n"/>
+      <c r="D411" s="3" t="n"/>
+      <c r="Q411" s="3" t="n"/>
     </row>
     <row r="412">
-      <c r="D412" s="2" t="n"/>
-      <c r="Q412" s="2" t="n"/>
+      <c r="D412" s="3" t="n"/>
+      <c r="Q412" s="3" t="n"/>
     </row>
     <row r="413">
-      <c r="D413" s="2" t="n"/>
-      <c r="Q413" s="2" t="n"/>
+      <c r="D413" s="3" t="n"/>
+      <c r="Q413" s="3" t="n"/>
     </row>
     <row r="414">
-      <c r="D414" s="2" t="n"/>
-      <c r="Q414" s="2" t="n"/>
+      <c r="D414" s="3" t="n"/>
+      <c r="Q414" s="3" t="n"/>
     </row>
     <row r="415">
-      <c r="D415" s="2" t="n"/>
-      <c r="Q415" s="2" t="n"/>
+      <c r="D415" s="3" t="n"/>
+      <c r="Q415" s="3" t="n"/>
     </row>
     <row r="416">
-      <c r="D416" s="2" t="n"/>
-      <c r="Q416" s="2" t="n"/>
+      <c r="D416" s="3" t="n"/>
+      <c r="Q416" s="3" t="n"/>
     </row>
     <row r="417">
-      <c r="D417" s="2" t="n"/>
-      <c r="Q417" s="2" t="n"/>
+      <c r="D417" s="3" t="n"/>
+      <c r="Q417" s="3" t="n"/>
     </row>
     <row r="418">
-      <c r="D418" s="2" t="n"/>
-      <c r="Q418" s="2" t="n"/>
+      <c r="D418" s="3" t="n"/>
+      <c r="Q418" s="3" t="n"/>
     </row>
     <row r="419">
-      <c r="D419" s="2" t="n"/>
-      <c r="Q419" s="2" t="n"/>
+      <c r="D419" s="3" t="n"/>
+      <c r="Q419" s="3" t="n"/>
     </row>
     <row r="420">
-      <c r="D420" s="2" t="n"/>
-      <c r="Q420" s="2" t="n"/>
+      <c r="D420" s="3" t="n"/>
+      <c r="Q420" s="3" t="n"/>
     </row>
     <row r="421">
-      <c r="D421" s="2" t="n"/>
-      <c r="Q421" s="2" t="n"/>
+      <c r="D421" s="3" t="n"/>
+      <c r="Q421" s="3" t="n"/>
     </row>
     <row r="422">
-      <c r="D422" s="2" t="n"/>
-      <c r="Q422" s="2" t="n"/>
+      <c r="D422" s="3" t="n"/>
+      <c r="Q422" s="3" t="n"/>
     </row>
     <row r="423">
-      <c r="D423" s="2" t="n"/>
-      <c r="Q423" s="2" t="n"/>
+      <c r="D423" s="3" t="n"/>
+      <c r="Q423" s="3" t="n"/>
     </row>
     <row r="424">
-      <c r="D424" s="2" t="n"/>
-      <c r="Q424" s="2" t="n"/>
+      <c r="D424" s="3" t="n"/>
+      <c r="Q424" s="3" t="n"/>
     </row>
     <row r="425">
-      <c r="D425" s="2" t="n"/>
-      <c r="Q425" s="2" t="n"/>
+      <c r="D425" s="3" t="n"/>
+      <c r="Q425" s="3" t="n"/>
     </row>
     <row r="426">
-      <c r="D426" s="2" t="n"/>
-      <c r="Q426" s="2" t="n"/>
+      <c r="D426" s="3" t="n"/>
+      <c r="Q426" s="3" t="n"/>
     </row>
     <row r="427">
-      <c r="D427" s="2" t="n"/>
-      <c r="Q427" s="2" t="n"/>
+      <c r="D427" s="3" t="n"/>
+      <c r="Q427" s="3" t="n"/>
     </row>
     <row r="428">
-      <c r="D428" s="2" t="n"/>
-      <c r="Q428" s="2" t="n"/>
+      <c r="D428" s="3" t="n"/>
+      <c r="Q428" s="3" t="n"/>
     </row>
     <row r="429">
-      <c r="D429" s="2" t="n"/>
-      <c r="Q429" s="2" t="n"/>
+      <c r="D429" s="3" t="n"/>
+      <c r="Q429" s="3" t="n"/>
     </row>
     <row r="430">
-      <c r="D430" s="2" t="n"/>
-      <c r="Q430" s="2" t="n"/>
+      <c r="D430" s="3" t="n"/>
+      <c r="Q430" s="3" t="n"/>
     </row>
     <row r="431">
-      <c r="D431" s="2" t="n"/>
-      <c r="Q431" s="2" t="n"/>
+      <c r="D431" s="3" t="n"/>
+      <c r="Q431" s="3" t="n"/>
     </row>
     <row r="432">
-      <c r="D432" s="2" t="n"/>
-      <c r="Q432" s="2" t="n"/>
+      <c r="D432" s="3" t="n"/>
+      <c r="Q432" s="3" t="n"/>
     </row>
     <row r="433">
-      <c r="D433" s="2" t="n"/>
-      <c r="Q433" s="2" t="n"/>
+      <c r="D433" s="3" t="n"/>
+      <c r="Q433" s="3" t="n"/>
     </row>
     <row r="434">
-      <c r="D434" s="2" t="n"/>
-      <c r="Q434" s="2" t="n"/>
+      <c r="D434" s="3" t="n"/>
+      <c r="Q434" s="3" t="n"/>
     </row>
     <row r="435">
-      <c r="D435" s="2" t="n"/>
-      <c r="Q435" s="2" t="n"/>
+      <c r="D435" s="3" t="n"/>
+      <c r="Q435" s="3" t="n"/>
     </row>
     <row r="436">
-      <c r="D436" s="2" t="n"/>
-      <c r="Q436" s="2" t="n"/>
+      <c r="D436" s="3" t="n"/>
+      <c r="Q436" s="3" t="n"/>
     </row>
     <row r="437">
-      <c r="D437" s="2" t="n"/>
-      <c r="Q437" s="2" t="n"/>
+      <c r="D437" s="3" t="n"/>
+      <c r="Q437" s="3" t="n"/>
     </row>
     <row r="438">
-      <c r="D438" s="2" t="n"/>
-      <c r="Q438" s="2" t="n"/>
+      <c r="D438" s="3" t="n"/>
+      <c r="Q438" s="3" t="n"/>
     </row>
     <row r="439">
-      <c r="D439" s="2" t="n"/>
-      <c r="Q439" s="2" t="n"/>
+      <c r="D439" s="3" t="n"/>
+      <c r="Q439" s="3" t="n"/>
     </row>
     <row r="440">
-      <c r="D440" s="2" t="n"/>
-      <c r="Q440" s="2" t="n"/>
+      <c r="D440" s="3" t="n"/>
+      <c r="Q440" s="3" t="n"/>
     </row>
     <row r="441">
-      <c r="D441" s="2" t="n"/>
-      <c r="Q441" s="2" t="n"/>
+      <c r="D441" s="3" t="n"/>
+      <c r="Q441" s="3" t="n"/>
     </row>
     <row r="442">
-      <c r="D442" s="2" t="n"/>
-      <c r="Q442" s="2" t="n"/>
+      <c r="D442" s="3" t="n"/>
+      <c r="Q442" s="3" t="n"/>
     </row>
     <row r="443">
-      <c r="D443" s="2" t="n"/>
-      <c r="Q443" s="2" t="n"/>
+      <c r="D443" s="3" t="n"/>
+      <c r="Q443" s="3" t="n"/>
     </row>
     <row r="444">
-      <c r="D444" s="2" t="n"/>
-      <c r="Q444" s="2" t="n"/>
+      <c r="D444" s="3" t="n"/>
+      <c r="Q444" s="3" t="n"/>
     </row>
     <row r="445">
-      <c r="D445" s="2" t="n"/>
-      <c r="Q445" s="2" t="n"/>
+      <c r="D445" s="3" t="n"/>
+      <c r="Q445" s="3" t="n"/>
     </row>
     <row r="446">
-      <c r="D446" s="2" t="n"/>
-      <c r="Q446" s="2" t="n"/>
+      <c r="D446" s="3" t="n"/>
+      <c r="Q446" s="3" t="n"/>
     </row>
     <row r="447">
-      <c r="D447" s="2" t="n"/>
-      <c r="Q447" s="2" t="n"/>
+      <c r="D447" s="3" t="n"/>
+      <c r="Q447" s="3" t="n"/>
     </row>
     <row r="448">
-      <c r="D448" s="2" t="n"/>
-      <c r="Q448" s="2" t="n"/>
+      <c r="D448" s="3" t="n"/>
+      <c r="Q448" s="3" t="n"/>
     </row>
     <row r="449">
-      <c r="D449" s="2" t="n"/>
-      <c r="Q449" s="2" t="n"/>
+      <c r="D449" s="3" t="n"/>
+      <c r="Q449" s="3" t="n"/>
     </row>
     <row r="450">
-      <c r="D450" s="2" t="n"/>
-      <c r="Q450" s="2" t="n"/>
+      <c r="D450" s="3" t="n"/>
+      <c r="Q450" s="3" t="n"/>
     </row>
     <row r="451">
-      <c r="D451" s="2" t="n"/>
-      <c r="Q451" s="2" t="n"/>
+      <c r="D451" s="3" t="n"/>
+      <c r="Q451" s="3" t="n"/>
     </row>
     <row r="452">
-      <c r="D452" s="2" t="n"/>
-      <c r="Q452" s="2" t="n"/>
+      <c r="D452" s="3" t="n"/>
+      <c r="Q452" s="3" t="n"/>
     </row>
     <row r="453">
-      <c r="D453" s="2" t="n"/>
-      <c r="Q453" s="2" t="n"/>
+      <c r="D453" s="3" t="n"/>
+      <c r="Q453" s="3" t="n"/>
     </row>
     <row r="454">
-      <c r="D454" s="2" t="n"/>
-      <c r="Q454" s="2" t="n"/>
+      <c r="D454" s="3" t="n"/>
+      <c r="Q454" s="3" t="n"/>
     </row>
     <row r="455">
-      <c r="D455" s="2" t="n"/>
-      <c r="Q455" s="2" t="n"/>
+      <c r="D455" s="3" t="n"/>
+      <c r="Q455" s="3" t="n"/>
     </row>
     <row r="456">
-      <c r="D456" s="2" t="n"/>
-      <c r="Q456" s="2" t="n"/>
+      <c r="D456" s="3" t="n"/>
+      <c r="Q456" s="3" t="n"/>
     </row>
     <row r="457">
-      <c r="D457" s="2" t="n"/>
-      <c r="Q457" s="2" t="n"/>
+      <c r="D457" s="3" t="n"/>
+      <c r="Q457" s="3" t="n"/>
     </row>
     <row r="458">
-      <c r="D458" s="2" t="n"/>
-      <c r="Q458" s="2" t="n"/>
+      <c r="D458" s="3" t="n"/>
+      <c r="Q458" s="3" t="n"/>
     </row>
     <row r="459">
-      <c r="D459" s="2" t="n"/>
-      <c r="Q459" s="2" t="n"/>
+      <c r="D459" s="3" t="n"/>
+      <c r="Q459" s="3" t="n"/>
     </row>
     <row r="460">
-      <c r="D460" s="2" t="n"/>
-      <c r="Q460" s="2" t="n"/>
+      <c r="D460" s="3" t="n"/>
+      <c r="Q460" s="3" t="n"/>
     </row>
     <row r="461">
-      <c r="D461" s="2" t="n"/>
-      <c r="Q461" s="2" t="n"/>
+      <c r="D461" s="3" t="n"/>
+      <c r="Q461" s="3" t="n"/>
     </row>
     <row r="462">
-      <c r="D462" s="2" t="n"/>
-      <c r="Q462" s="2" t="n"/>
+      <c r="D462" s="3" t="n"/>
+      <c r="Q462" s="3" t="n"/>
     </row>
     <row r="463">
-      <c r="D463" s="2" t="n"/>
-      <c r="Q463" s="2" t="n"/>
+      <c r="D463" s="3" t="n"/>
+      <c r="Q463" s="3" t="n"/>
     </row>
     <row r="464">
-      <c r="D464" s="2" t="n"/>
-      <c r="Q464" s="2" t="n"/>
+      <c r="D464" s="3" t="n"/>
+      <c r="Q464" s="3" t="n"/>
     </row>
     <row r="465">
-      <c r="D465" s="2" t="n"/>
-      <c r="Q465" s="2" t="n"/>
+      <c r="D465" s="3" t="n"/>
+      <c r="Q465" s="3" t="n"/>
     </row>
     <row r="466">
-      <c r="D466" s="2" t="n"/>
-      <c r="Q466" s="2" t="n"/>
+      <c r="D466" s="3" t="n"/>
+      <c r="Q466" s="3" t="n"/>
     </row>
     <row r="467">
-      <c r="D467" s="2" t="n"/>
-      <c r="Q467" s="2" t="n"/>
+      <c r="D467" s="3" t="n"/>
+      <c r="Q467" s="3" t="n"/>
     </row>
     <row r="468">
-      <c r="D468" s="2" t="n"/>
-      <c r="Q468" s="2" t="n"/>
+      <c r="D468" s="3" t="n"/>
+      <c r="Q468" s="3" t="n"/>
     </row>
     <row r="469">
-      <c r="D469" s="2" t="n"/>
-      <c r="Q469" s="2" t="n"/>
+      <c r="D469" s="3" t="n"/>
+      <c r="Q469" s="3" t="n"/>
     </row>
     <row r="470">
-      <c r="D470" s="2" t="n"/>
-      <c r="Q470" s="2" t="n"/>
+      <c r="D470" s="3" t="n"/>
+      <c r="Q470" s="3" t="n"/>
     </row>
     <row r="471">
-      <c r="D471" s="2" t="n"/>
-      <c r="Q471" s="2" t="n"/>
+      <c r="D471" s="3" t="n"/>
+      <c r="Q471" s="3" t="n"/>
     </row>
     <row r="472">
-      <c r="D472" s="2" t="n"/>
-      <c r="Q472" s="2" t="n"/>
+      <c r="D472" s="3" t="n"/>
+      <c r="Q472" s="3" t="n"/>
     </row>
     <row r="473">
-      <c r="D473" s="2" t="n"/>
-      <c r="Q473" s="2" t="n"/>
+      <c r="D473" s="3" t="n"/>
+      <c r="Q473" s="3" t="n"/>
     </row>
     <row r="474">
-      <c r="D474" s="2" t="n"/>
-      <c r="Q474" s="2" t="n"/>
+      <c r="D474" s="3" t="n"/>
+      <c r="Q474" s="3" t="n"/>
     </row>
     <row r="475">
-      <c r="D475" s="2" t="n"/>
-      <c r="Q475" s="2" t="n"/>
+      <c r="D475" s="3" t="n"/>
+      <c r="Q475" s="3" t="n"/>
     </row>
     <row r="476">
-      <c r="D476" s="2" t="n"/>
-      <c r="Q476" s="2" t="n"/>
+      <c r="D476" s="3" t="n"/>
+      <c r="Q476" s="3" t="n"/>
     </row>
     <row r="477">
-      <c r="D477" s="2" t="n"/>
-      <c r="Q477" s="2" t="n"/>
+      <c r="D477" s="3" t="n"/>
+      <c r="Q477" s="3" t="n"/>
     </row>
     <row r="478">
-      <c r="D478" s="2" t="n"/>
-      <c r="Q478" s="2" t="n"/>
+      <c r="D478" s="3" t="n"/>
+      <c r="Q478" s="3" t="n"/>
     </row>
     <row r="479">
-      <c r="D479" s="2" t="n"/>
-      <c r="Q479" s="2" t="n"/>
+      <c r="D479" s="3" t="n"/>
+      <c r="Q479" s="3" t="n"/>
     </row>
     <row r="480">
-      <c r="D480" s="2" t="n"/>
-      <c r="Q480" s="2" t="n"/>
+      <c r="D480" s="3" t="n"/>
+      <c r="Q480" s="3" t="n"/>
     </row>
     <row r="481">
-      <c r="D481" s="2" t="n"/>
-      <c r="Q481" s="2" t="n"/>
+      <c r="D481" s="3" t="n"/>
+      <c r="Q481" s="3" t="n"/>
     </row>
     <row r="482">
-      <c r="D482" s="2" t="n"/>
-      <c r="Q482" s="2" t="n"/>
+      <c r="D482" s="3" t="n"/>
+      <c r="Q482" s="3" t="n"/>
     </row>
     <row r="483">
-      <c r="D483" s="2" t="n"/>
-      <c r="Q483" s="2" t="n"/>
+      <c r="D483" s="3" t="n"/>
+      <c r="Q483" s="3" t="n"/>
     </row>
     <row r="484">
-      <c r="D484" s="2" t="n"/>
-      <c r="Q484" s="2" t="n"/>
+      <c r="D484" s="3" t="n"/>
+      <c r="Q484" s="3" t="n"/>
     </row>
     <row r="485">
-      <c r="D485" s="2" t="n"/>
-      <c r="Q485" s="2" t="n"/>
+      <c r="D485" s="3" t="n"/>
+      <c r="Q485" s="3" t="n"/>
     </row>
     <row r="486">
-      <c r="D486" s="2" t="n"/>
-      <c r="Q486" s="2" t="n"/>
+      <c r="D486" s="3" t="n"/>
+      <c r="Q486" s="3" t="n"/>
     </row>
     <row r="487">
-      <c r="D487" s="2" t="n"/>
-      <c r="Q487" s="2" t="n"/>
+      <c r="D487" s="3" t="n"/>
+      <c r="Q487" s="3" t="n"/>
     </row>
     <row r="488">
-      <c r="D488" s="2" t="n"/>
-      <c r="Q488" s="2" t="n"/>
+      <c r="D488" s="3" t="n"/>
+      <c r="Q488" s="3" t="n"/>
     </row>
     <row r="489">
-      <c r="D489" s="2" t="n"/>
-      <c r="Q489" s="2" t="n"/>
+      <c r="D489" s="3" t="n"/>
+      <c r="Q489" s="3" t="n"/>
     </row>
     <row r="490">
-      <c r="D490" s="2" t="n"/>
-      <c r="Q490" s="2" t="n"/>
+      <c r="D490" s="3" t="n"/>
+      <c r="Q490" s="3" t="n"/>
     </row>
     <row r="491">
-      <c r="D491" s="2" t="n"/>
-      <c r="Q491" s="2" t="n"/>
+      <c r="D491" s="3" t="n"/>
+      <c r="Q491" s="3" t="n"/>
     </row>
     <row r="492">
-      <c r="D492" s="2" t="n"/>
-      <c r="Q492" s="2" t="n"/>
+      <c r="D492" s="3" t="n"/>
+      <c r="Q492" s="3" t="n"/>
     </row>
     <row r="493">
-      <c r="D493" s="2" t="n"/>
-      <c r="Q493" s="2" t="n"/>
+      <c r="D493" s="3" t="n"/>
+      <c r="Q493" s="3" t="n"/>
     </row>
     <row r="494">
-      <c r="D494" s="2" t="n"/>
-      <c r="Q494" s="2" t="n"/>
+      <c r="D494" s="3" t="n"/>
+      <c r="Q494" s="3" t="n"/>
     </row>
     <row r="495">
-      <c r="D495" s="2" t="n"/>
-      <c r="Q495" s="2" t="n"/>
+      <c r="D495" s="3" t="n"/>
+      <c r="Q495" s="3" t="n"/>
     </row>
     <row r="496">
-      <c r="D496" s="2" t="n"/>
-      <c r="Q496" s="2" t="n"/>
+      <c r="D496" s="3" t="n"/>
+      <c r="Q496" s="3" t="n"/>
     </row>
     <row r="497">
-      <c r="D497" s="2" t="n"/>
-      <c r="Q497" s="2" t="n"/>
+      <c r="D497" s="3" t="n"/>
+      <c r="Q497" s="3" t="n"/>
     </row>
     <row r="498">
-      <c r="D498" s="2" t="n"/>
-      <c r="Q498" s="2" t="n"/>
+      <c r="D498" s="3" t="n"/>
+      <c r="Q498" s="3" t="n"/>
     </row>
     <row r="499">
-      <c r="D499" s="2" t="n"/>
-      <c r="Q499" s="2" t="n"/>
+      <c r="D499" s="3" t="n"/>
+      <c r="Q499" s="3" t="n"/>
     </row>
     <row r="500">
-      <c r="D500" s="2" t="n"/>
-      <c r="Q500" s="2" t="n"/>
+      <c r="D500" s="3" t="n"/>
+      <c r="Q500" s="3" t="n"/>
     </row>
     <row r="501">
-      <c r="D501" s="2" t="n"/>
-      <c r="Q501" s="2" t="n"/>
+      <c r="D501" s="3" t="n"/>
+      <c r="Q501" s="3" t="n"/>
     </row>
     <row r="502">
-      <c r="D502" s="2" t="n"/>
-      <c r="Q502" s="2" t="n"/>
+      <c r="D502" s="3" t="n"/>
+      <c r="Q502" s="3" t="n"/>
     </row>
     <row r="503">
-      <c r="D503" s="2" t="n"/>
-      <c r="Q503" s="2" t="n"/>
+      <c r="D503" s="3" t="n"/>
+      <c r="Q503" s="3" t="n"/>
     </row>
     <row r="504">
-      <c r="D504" s="2" t="n"/>
-      <c r="Q504" s="2" t="n"/>
+      <c r="D504" s="3" t="n"/>
+      <c r="Q504" s="3" t="n"/>
     </row>
     <row r="505">
-      <c r="D505" s="2" t="n"/>
-      <c r="Q505" s="2" t="n"/>
+      <c r="D505" s="3" t="n"/>
+      <c r="Q505" s="3" t="n"/>
     </row>
     <row r="506">
-      <c r="D506" s="2" t="n"/>
-      <c r="Q506" s="2" t="n"/>
+      <c r="D506" s="3" t="n"/>
+      <c r="Q506" s="3" t="n"/>
     </row>
     <row r="507">
-      <c r="D507" s="2" t="n"/>
-      <c r="Q507" s="2" t="n"/>
+      <c r="D507" s="3" t="n"/>
+      <c r="Q507" s="3" t="n"/>
     </row>
     <row r="508">
-      <c r="D508" s="2" t="n"/>
-      <c r="Q508" s="2" t="n"/>
+      <c r="D508" s="3" t="n"/>
+      <c r="Q508" s="3" t="n"/>
     </row>
     <row r="509">
-      <c r="D509" s="2" t="n"/>
-      <c r="Q509" s="2" t="n"/>
+      <c r="D509" s="3" t="n"/>
+      <c r="Q509" s="3" t="n"/>
     </row>
     <row r="510">
-      <c r="D510" s="2" t="n"/>
-      <c r="Q510" s="2" t="n"/>
+      <c r="D510" s="3" t="n"/>
+      <c r="Q510" s="3" t="n"/>
     </row>
     <row r="511">
-      <c r="D511" s="2" t="n"/>
-      <c r="Q511" s="2" t="n"/>
+      <c r="D511" s="3" t="n"/>
+      <c r="Q511" s="3" t="n"/>
     </row>
     <row r="512">
-      <c r="D512" s="2" t="n"/>
-      <c r="Q512" s="2" t="n"/>
+      <c r="D512" s="3" t="n"/>
+      <c r="Q512" s="3" t="n"/>
     </row>
     <row r="513">
-      <c r="D513" s="2" t="n"/>
-      <c r="Q513" s="2" t="n"/>
+      <c r="D513" s="3" t="n"/>
+      <c r="Q513" s="3" t="n"/>
     </row>
     <row r="514">
-      <c r="D514" s="2" t="n"/>
-      <c r="Q514" s="2" t="n"/>
+      <c r="D514" s="3" t="n"/>
+      <c r="Q514" s="3" t="n"/>
     </row>
     <row r="515">
-      <c r="D515" s="2" t="n"/>
-      <c r="Q515" s="2" t="n"/>
+      <c r="D515" s="3" t="n"/>
+      <c r="Q515" s="3" t="n"/>
     </row>
     <row r="516">
-      <c r="D516" s="2" t="n"/>
-      <c r="Q516" s="2" t="n"/>
+      <c r="D516" s="3" t="n"/>
+      <c r="Q516" s="3" t="n"/>
     </row>
     <row r="517">
-      <c r="D517" s="2" t="n"/>
-      <c r="Q517" s="2" t="n"/>
+      <c r="D517" s="3" t="n"/>
+      <c r="Q517" s="3" t="n"/>
     </row>
     <row r="518">
-      <c r="D518" s="2" t="n"/>
-      <c r="Q518" s="2" t="n"/>
+      <c r="D518" s="3" t="n"/>
+      <c r="Q518" s="3" t="n"/>
     </row>
     <row r="519">
-      <c r="D519" s="2" t="n"/>
-      <c r="Q519" s="2" t="n"/>
+      <c r="D519" s="3" t="n"/>
+      <c r="Q519" s="3" t="n"/>
     </row>
     <row r="520">
-      <c r="D520" s="2" t="n"/>
-      <c r="Q520" s="2" t="n"/>
+      <c r="D520" s="3" t="n"/>
+      <c r="Q520" s="3" t="n"/>
     </row>
     <row r="521">
-      <c r="D521" s="2" t="n"/>
-      <c r="Q521" s="2" t="n"/>
+      <c r="D521" s="3" t="n"/>
+      <c r="Q521" s="3" t="n"/>
     </row>
     <row r="522">
-      <c r="D522" s="2" t="n"/>
-      <c r="Q522" s="2" t="n"/>
+      <c r="D522" s="3" t="n"/>
+      <c r="Q522" s="3" t="n"/>
     </row>
     <row r="523">
-      <c r="D523" s="2" t="n"/>
-      <c r="Q523" s="2" t="n"/>
+      <c r="D523" s="3" t="n"/>
+      <c r="Q523" s="3" t="n"/>
     </row>
     <row r="524">
-      <c r="D524" s="2" t="n"/>
-      <c r="Q524" s="2" t="n"/>
+      <c r="D524" s="3" t="n"/>
+      <c r="Q524" s="3" t="n"/>
     </row>
     <row r="525">
-      <c r="D525" s="2" t="n"/>
-      <c r="Q525" s="2" t="n"/>
+      <c r="D525" s="3" t="n"/>
+      <c r="Q525" s="3" t="n"/>
     </row>
     <row r="526">
-      <c r="D526" s="2" t="n"/>
-      <c r="Q526" s="2" t="n"/>
+      <c r="D526" s="3" t="n"/>
+      <c r="Q526" s="3" t="n"/>
     </row>
     <row r="527">
-      <c r="D527" s="2" t="n"/>
-      <c r="Q527" s="2" t="n"/>
+      <c r="D527" s="3" t="n"/>
+      <c r="Q527" s="3" t="n"/>
     </row>
     <row r="528">
-      <c r="D528" s="2" t="n"/>
-      <c r="Q528" s="2" t="n"/>
+      <c r="D528" s="3" t="n"/>
+      <c r="Q528" s="3" t="n"/>
     </row>
     <row r="529">
-      <c r="D529" s="2" t="n"/>
-      <c r="Q529" s="2" t="n"/>
+      <c r="D529" s="3" t="n"/>
+      <c r="Q529" s="3" t="n"/>
     </row>
     <row r="530">
-      <c r="D530" s="2" t="n"/>
-      <c r="Q530" s="2" t="n"/>
+      <c r="D530" s="3" t="n"/>
+      <c r="Q530" s="3" t="n"/>
     </row>
     <row r="531">
-      <c r="D531" s="2" t="n"/>
-      <c r="Q531" s="2" t="n"/>
+      <c r="D531" s="3" t="n"/>
+      <c r="Q531" s="3" t="n"/>
     </row>
     <row r="532">
-      <c r="D532" s="2" t="n"/>
-      <c r="Q532" s="2" t="n"/>
+      <c r="D532" s="3" t="n"/>
+      <c r="Q532" s="3" t="n"/>
     </row>
     <row r="533">
-      <c r="D533" s="2" t="n"/>
-      <c r="Q533" s="2" t="n"/>
+      <c r="D533" s="3" t="n"/>
+      <c r="Q533" s="3" t="n"/>
     </row>
     <row r="534">
-      <c r="D534" s="2" t="n"/>
-      <c r="Q534" s="2" t="n"/>
+      <c r="D534" s="3" t="n"/>
+      <c r="Q534" s="3" t="n"/>
     </row>
     <row r="535">
-      <c r="D535" s="2" t="n"/>
-      <c r="Q535" s="2" t="n"/>
+      <c r="D535" s="3" t="n"/>
+      <c r="Q535" s="3" t="n"/>
     </row>
     <row r="536">
-      <c r="D536" s="2" t="n"/>
-      <c r="Q536" s="2" t="n"/>
+      <c r="D536" s="3" t="n"/>
+      <c r="Q536" s="3" t="n"/>
     </row>
     <row r="537">
-      <c r="D537" s="2" t="n"/>
-      <c r="Q537" s="2" t="n"/>
+      <c r="D537" s="3" t="n"/>
+      <c r="Q537" s="3" t="n"/>
     </row>
     <row r="538">
-      <c r="D538" s="2" t="n"/>
-      <c r="Q538" s="2" t="n"/>
+      <c r="D538" s="3" t="n"/>
+      <c r="Q538" s="3" t="n"/>
     </row>
     <row r="539">
-      <c r="D539" s="2" t="n"/>
-      <c r="Q539" s="2" t="n"/>
+      <c r="D539" s="3" t="n"/>
+      <c r="Q539" s="3" t="n"/>
     </row>
     <row r="540">
-      <c r="D540" s="2" t="n"/>
-      <c r="Q540" s="2" t="n"/>
+      <c r="D540" s="3" t="n"/>
+      <c r="Q540" s="3" t="n"/>
     </row>
     <row r="541">
-      <c r="D541" s="2" t="n"/>
-      <c r="Q541" s="2" t="n"/>
+      <c r="D541" s="3" t="n"/>
+      <c r="Q541" s="3" t="n"/>
     </row>
     <row r="542">
-      <c r="D542" s="2" t="n"/>
-      <c r="Q542" s="2" t="n"/>
+      <c r="D542" s="3" t="n"/>
+      <c r="Q542" s="3" t="n"/>
     </row>
     <row r="543">
-      <c r="D543" s="2" t="n"/>
-      <c r="Q543" s="2" t="n"/>
+      <c r="D543" s="3" t="n"/>
+      <c r="Q543" s="3" t="n"/>
     </row>
     <row r="544">
-      <c r="D544" s="2" t="n"/>
-      <c r="Q544" s="2" t="n"/>
+      <c r="D544" s="3" t="n"/>
+      <c r="Q544" s="3" t="n"/>
     </row>
     <row r="545">
-      <c r="D545" s="2" t="n"/>
-      <c r="Q545" s="2" t="n"/>
+      <c r="D545" s="3" t="n"/>
+      <c r="Q545" s="3" t="n"/>
     </row>
     <row r="546">
-      <c r="D546" s="2" t="n"/>
-      <c r="Q546" s="2" t="n"/>
+      <c r="D546" s="3" t="n"/>
+      <c r="Q546" s="3" t="n"/>
     </row>
     <row r="547">
-      <c r="D547" s="2" t="n"/>
-      <c r="Q547" s="2" t="n"/>
+      <c r="D547" s="3" t="n"/>
+      <c r="Q547" s="3" t="n"/>
     </row>
     <row r="548">
-      <c r="D548" s="2" t="n"/>
-      <c r="Q548" s="2" t="n"/>
+      <c r="D548" s="3" t="n"/>
+      <c r="Q548" s="3" t="n"/>
     </row>
     <row r="549">
-      <c r="D549" s="2" t="n"/>
-      <c r="Q549" s="2" t="n"/>
+      <c r="D549" s="3" t="n"/>
+      <c r="Q549" s="3" t="n"/>
     </row>
     <row r="550">
-      <c r="D550" s="2" t="n"/>
-      <c r="Q550" s="2" t="n"/>
+      <c r="D550" s="3" t="n"/>
+      <c r="Q550" s="3" t="n"/>
     </row>
     <row r="551">
-      <c r="D551" s="2" t="n"/>
-      <c r="Q551" s="2" t="n"/>
+      <c r="D551" s="3" t="n"/>
+      <c r="Q551" s="3" t="n"/>
     </row>
     <row r="552">
-      <c r="D552" s="2" t="n"/>
-      <c r="Q552" s="2" t="n"/>
+      <c r="D552" s="3" t="n"/>
+      <c r="Q552" s="3" t="n"/>
     </row>
     <row r="553">
-      <c r="D553" s="2" t="n"/>
-      <c r="Q553" s="2" t="n"/>
+      <c r="D553" s="3" t="n"/>
+      <c r="Q553" s="3" t="n"/>
     </row>
     <row r="554">
-      <c r="D554" s="2" t="n"/>
-      <c r="Q554" s="2" t="n"/>
+      <c r="D554" s="3" t="n"/>
+      <c r="Q554" s="3" t="n"/>
     </row>
     <row r="555">
-      <c r="D555" s="2" t="n"/>
-      <c r="Q555" s="2" t="n"/>
+      <c r="D555" s="3" t="n"/>
+      <c r="Q555" s="3" t="n"/>
     </row>
     <row r="556">
-      <c r="D556" s="2" t="n"/>
-      <c r="Q556" s="2" t="n"/>
+      <c r="D556" s="3" t="n"/>
+      <c r="Q556" s="3" t="n"/>
     </row>
     <row r="557">
-      <c r="D557" s="2" t="n"/>
-      <c r="Q557" s="2" t="n"/>
+      <c r="D557" s="3" t="n"/>
+      <c r="Q557" s="3" t="n"/>
     </row>
     <row r="558">
-      <c r="D558" s="2" t="n"/>
-      <c r="Q558" s="2" t="n"/>
+      <c r="D558" s="3" t="n"/>
+      <c r="Q558" s="3" t="n"/>
     </row>
     <row r="559">
-      <c r="D559" s="2" t="n"/>
-      <c r="Q559" s="2" t="n"/>
+      <c r="D559" s="3" t="n"/>
+      <c r="Q559" s="3" t="n"/>
     </row>
     <row r="560">
-      <c r="D560" s="2" t="n"/>
-      <c r="Q560" s="2" t="n"/>
+      <c r="D560" s="3" t="n"/>
+      <c r="Q560" s="3" t="n"/>
     </row>
     <row r="561">
-      <c r="D561" s="2" t="n"/>
-      <c r="Q561" s="2" t="n"/>
+      <c r="D561" s="3" t="n"/>
+      <c r="Q561" s="3" t="n"/>
     </row>
     <row r="562">
-      <c r="D562" s="2" t="n"/>
-      <c r="Q562" s="2" t="n"/>
+      <c r="D562" s="3" t="n"/>
+      <c r="Q562" s="3" t="n"/>
     </row>
     <row r="563">
-      <c r="D563" s="2" t="n"/>
-      <c r="Q563" s="2" t="n"/>
+      <c r="D563" s="3" t="n"/>
+      <c r="Q563" s="3" t="n"/>
     </row>
     <row r="564">
-      <c r="D564" s="2" t="n"/>
-      <c r="Q564" s="2" t="n"/>
+      <c r="D564" s="3" t="n"/>
+      <c r="Q564" s="3" t="n"/>
     </row>
     <row r="565">
-      <c r="D565" s="2" t="n"/>
-      <c r="Q565" s="2" t="n"/>
+      <c r="D565" s="3" t="n"/>
+      <c r="Q565" s="3" t="n"/>
     </row>
     <row r="566">
-      <c r="D566" s="2" t="n"/>
-      <c r="Q566" s="2" t="n"/>
+      <c r="D566" s="3" t="n"/>
+      <c r="Q566" s="3" t="n"/>
     </row>
     <row r="567">
-      <c r="D567" s="2" t="n"/>
-      <c r="Q567" s="2" t="n"/>
+      <c r="D567" s="3" t="n"/>
+      <c r="Q567" s="3" t="n"/>
     </row>
     <row r="568">
-      <c r="D568" s="2" t="n"/>
-      <c r="Q568" s="2" t="n"/>
+      <c r="D568" s="3" t="n"/>
+      <c r="Q568" s="3" t="n"/>
     </row>
     <row r="569">
-      <c r="D569" s="2" t="n"/>
-      <c r="Q569" s="2" t="n"/>
+      <c r="D569" s="3" t="n"/>
+      <c r="Q569" s="3" t="n"/>
     </row>
     <row r="570">
-      <c r="D570" s="2" t="n"/>
-      <c r="Q570" s="2" t="n"/>
+      <c r="D570" s="3" t="n"/>
+      <c r="Q570" s="3" t="n"/>
     </row>
     <row r="571">
-      <c r="D571" s="2" t="n"/>
-      <c r="Q571" s="2" t="n"/>
+      <c r="D571" s="3" t="n"/>
+      <c r="Q571" s="3" t="n"/>
     </row>
     <row r="572">
-      <c r="D572" s="2" t="n"/>
-      <c r="Q572" s="2" t="n"/>
+      <c r="D572" s="3" t="n"/>
+      <c r="Q572" s="3" t="n"/>
     </row>
     <row r="573">
-      <c r="D573" s="2" t="n"/>
-      <c r="Q573" s="2" t="n"/>
+      <c r="D573" s="3" t="n"/>
+      <c r="Q573" s="3" t="n"/>
     </row>
     <row r="574">
-      <c r="D574" s="2" t="n"/>
-      <c r="Q574" s="2" t="n"/>
+      <c r="D574" s="3" t="n"/>
+      <c r="Q574" s="3" t="n"/>
     </row>
     <row r="575">
-      <c r="D575" s="2" t="n"/>
-      <c r="Q575" s="2" t="n"/>
+      <c r="D575" s="3" t="n"/>
+      <c r="Q575" s="3" t="n"/>
     </row>
     <row r="576">
-      <c r="D576" s="2" t="n"/>
-      <c r="Q576" s="2" t="n"/>
+      <c r="D576" s="3" t="n"/>
+      <c r="Q576" s="3" t="n"/>
     </row>
     <row r="577">
-      <c r="D577" s="2" t="n"/>
-      <c r="Q577" s="2" t="n"/>
+      <c r="D577" s="3" t="n"/>
+      <c r="Q577" s="3" t="n"/>
     </row>
     <row r="578">
-      <c r="D578" s="2" t="n"/>
-      <c r="Q578" s="2" t="n"/>
+      <c r="D578" s="3" t="n"/>
+      <c r="Q578" s="3" t="n"/>
     </row>
     <row r="579">
-      <c r="D579" s="2" t="n"/>
-      <c r="Q579" s="2" t="n"/>
+      <c r="D579" s="3" t="n"/>
+      <c r="Q579" s="3" t="n"/>
     </row>
     <row r="580">
-      <c r="D580" s="2" t="n"/>
-      <c r="Q580" s="2" t="n"/>
+      <c r="D580" s="3" t="n"/>
+      <c r="Q580" s="3" t="n"/>
     </row>
     <row r="581">
-      <c r="D581" s="2" t="n"/>
-      <c r="Q581" s="2" t="n"/>
+      <c r="D581" s="3" t="n"/>
+      <c r="Q581" s="3" t="n"/>
     </row>
     <row r="582">
-      <c r="D582" s="2" t="n"/>
-      <c r="Q582" s="2" t="n"/>
+      <c r="D582" s="3" t="n"/>
+      <c r="Q582" s="3" t="n"/>
     </row>
     <row r="583">
-      <c r="D583" s="2" t="n"/>
-      <c r="Q583" s="2" t="n"/>
+      <c r="D583" s="3" t="n"/>
+      <c r="Q583" s="3" t="n"/>
     </row>
     <row r="584">
-      <c r="D584" s="2" t="n"/>
-      <c r="Q584" s="2" t="n"/>
+      <c r="D584" s="3" t="n"/>
+      <c r="Q584" s="3" t="n"/>
     </row>
     <row r="585">
-      <c r="D585" s="2" t="n"/>
-      <c r="Q585" s="2" t="n"/>
+      <c r="D585" s="3" t="n"/>
+      <c r="Q585" s="3" t="n"/>
     </row>
     <row r="586">
-      <c r="D586" s="2" t="n"/>
-      <c r="Q586" s="2" t="n"/>
+      <c r="D586" s="3" t="n"/>
+      <c r="Q586" s="3" t="n"/>
     </row>
     <row r="587">
-      <c r="D587" s="2" t="n"/>
-      <c r="Q587" s="2" t="n"/>
+      <c r="D587" s="3" t="n"/>
+      <c r="Q587" s="3" t="n"/>
     </row>
     <row r="588">
-      <c r="D588" s="2" t="n"/>
-      <c r="Q588" s="2" t="n"/>
+      <c r="D588" s="3" t="n"/>
+      <c r="Q588" s="3" t="n"/>
     </row>
     <row r="589">
-      <c r="D589" s="2" t="n"/>
-      <c r="Q589" s="2" t="n"/>
+      <c r="D589" s="3" t="n"/>
+      <c r="Q589" s="3" t="n"/>
     </row>
     <row r="590">
-      <c r="D590" s="2" t="n"/>
-      <c r="Q590" s="2" t="n"/>
+      <c r="D590" s="3" t="n"/>
+      <c r="Q590" s="3" t="n"/>
     </row>
     <row r="591">
-      <c r="D591" s="2" t="n"/>
-      <c r="Q591" s="2" t="n"/>
+      <c r="D591" s="3" t="n"/>
+      <c r="Q591" s="3" t="n"/>
     </row>
     <row r="592">
-      <c r="D592" s="2" t="n"/>
-      <c r="Q592" s="2" t="n"/>
+      <c r="D592" s="3" t="n"/>
+      <c r="Q592" s="3" t="n"/>
     </row>
     <row r="593">
-      <c r="D593" s="2" t="n"/>
-      <c r="Q593" s="2" t="n"/>
+      <c r="D593" s="3" t="n"/>
+      <c r="Q593" s="3" t="n"/>
     </row>
     <row r="594">
-      <c r="D594" s="2" t="n"/>
-      <c r="Q594" s="2" t="n"/>
+      <c r="D594" s="3" t="n"/>
+      <c r="Q594" s="3" t="n"/>
     </row>
     <row r="595">
-      <c r="D595" s="2" t="n"/>
-      <c r="Q595" s="2" t="n"/>
+      <c r="D595" s="3" t="n"/>
+      <c r="Q595" s="3" t="n"/>
     </row>
     <row r="596">
-      <c r="D596" s="2" t="n"/>
-      <c r="Q596" s="2" t="n"/>
+      <c r="D596" s="3" t="n"/>
+      <c r="Q596" s="3" t="n"/>
     </row>
     <row r="597">
-      <c r="D597" s="2" t="n"/>
-      <c r="Q597" s="2" t="n"/>
+      <c r="D597" s="3" t="n"/>
+      <c r="Q597" s="3" t="n"/>
     </row>
     <row r="598">
-      <c r="D598" s="2" t="n"/>
-      <c r="Q598" s="2" t="n"/>
+      <c r="D598" s="3" t="n"/>
+      <c r="Q598" s="3" t="n"/>
     </row>
     <row r="599">
-      <c r="D599" s="2" t="n"/>
-      <c r="Q599" s="2" t="n"/>
+      <c r="D599" s="3" t="n"/>
+      <c r="Q599" s="3" t="n"/>
     </row>
     <row r="600">
-      <c r="D600" s="2" t="n"/>
-      <c r="Q600" s="2" t="n"/>
+      <c r="D600" s="3" t="n"/>
+      <c r="Q600" s="3" t="n"/>
     </row>
     <row r="601">
-      <c r="D601" s="2" t="n"/>
-      <c r="Q601" s="2" t="n"/>
+      <c r="D601" s="3" t="n"/>
+      <c r="Q601" s="3" t="n"/>
     </row>
     <row r="602">
-      <c r="D602" s="2" t="n"/>
-      <c r="Q602" s="2" t="n"/>
+      <c r="D602" s="3" t="n"/>
+      <c r="Q602" s="3" t="n"/>
     </row>
     <row r="603">
-      <c r="D603" s="2" t="n"/>
-      <c r="Q603" s="2" t="n"/>
+      <c r="D603" s="3" t="n"/>
+      <c r="Q603" s="3" t="n"/>
     </row>
     <row r="604">
-      <c r="D604" s="2" t="n"/>
-      <c r="Q604" s="2" t="n"/>
+      <c r="D604" s="3" t="n"/>
+      <c r="Q604" s="3" t="n"/>
     </row>
     <row r="605">
-      <c r="D605" s="2" t="n"/>
-      <c r="Q605" s="2" t="n"/>
+      <c r="D605" s="3" t="n"/>
+      <c r="Q605" s="3" t="n"/>
     </row>
     <row r="606">
-      <c r="D606" s="2" t="n"/>
-      <c r="Q606" s="2" t="n"/>
+      <c r="D606" s="3" t="n"/>
+      <c r="Q606" s="3" t="n"/>
     </row>
     <row r="607">
-      <c r="D607" s="2" t="n"/>
-      <c r="Q607" s="2" t="n"/>
+      <c r="D607" s="3" t="n"/>
+      <c r="Q607" s="3" t="n"/>
     </row>
     <row r="608">
-      <c r="D608" s="2" t="n"/>
-      <c r="Q608" s="2" t="n"/>
+      <c r="D608" s="3" t="n"/>
+      <c r="Q608" s="3" t="n"/>
     </row>
     <row r="609">
-      <c r="D609" s="2" t="n"/>
-      <c r="Q609" s="2" t="n"/>
+      <c r="D609" s="3" t="n"/>
+      <c r="Q609" s="3" t="n"/>
     </row>
     <row r="610">
-      <c r="D610" s="2" t="n"/>
-      <c r="Q610" s="2" t="n"/>
+      <c r="D610" s="3" t="n"/>
+      <c r="Q610" s="3" t="n"/>
     </row>
     <row r="611">
-      <c r="D611" s="2" t="n"/>
-      <c r="Q611" s="2" t="n"/>
+      <c r="D611" s="3" t="n"/>
+      <c r="Q611" s="3" t="n"/>
     </row>
     <row r="612">
-      <c r="D612" s="2" t="n"/>
-      <c r="Q612" s="2" t="n"/>
+      <c r="D612" s="3" t="n"/>
+      <c r="Q612" s="3" t="n"/>
     </row>
     <row r="613">
-      <c r="D613" s="2" t="n"/>
-      <c r="Q613" s="2" t="n"/>
+      <c r="D613" s="3" t="n"/>
+      <c r="Q613" s="3" t="n"/>
     </row>
     <row r="614">
-      <c r="D614" s="2" t="n"/>
-      <c r="Q614" s="2" t="n"/>
+      <c r="D614" s="3" t="n"/>
+      <c r="Q614" s="3" t="n"/>
     </row>
     <row r="615">
-      <c r="D615" s="2" t="n"/>
-      <c r="Q615" s="2" t="n"/>
+      <c r="D615" s="3" t="n"/>
+      <c r="Q615" s="3" t="n"/>
     </row>
     <row r="616">
-      <c r="D616" s="2" t="n"/>
-      <c r="Q616" s="2" t="n"/>
+      <c r="D616" s="3" t="n"/>
+      <c r="Q616" s="3" t="n"/>
     </row>
     <row r="617">
-      <c r="D617" s="2" t="n"/>
-      <c r="Q617" s="2" t="n"/>
+      <c r="D617" s="3" t="n"/>
+      <c r="Q617" s="3" t="n"/>
     </row>
     <row r="618">
-      <c r="D618" s="2" t="n"/>
-      <c r="Q618" s="2" t="n"/>
+      <c r="D618" s="3" t="n"/>
+      <c r="Q618" s="3" t="n"/>
     </row>
     <row r="619">
-      <c r="D619" s="2" t="n"/>
-      <c r="Q619" s="2" t="n"/>
+      <c r="D619" s="3" t="n"/>
+      <c r="Q619" s="3" t="n"/>
     </row>
     <row r="620">
-      <c r="D620" s="2" t="n"/>
-      <c r="Q620" s="2" t="n"/>
+      <c r="D620" s="3" t="n"/>
+      <c r="Q620" s="3" t="n"/>
     </row>
     <row r="621">
-      <c r="D621" s="2" t="n"/>
-      <c r="Q621" s="2" t="n"/>
+      <c r="D621" s="3" t="n"/>
+      <c r="Q621" s="3" t="n"/>
     </row>
     <row r="622">
-      <c r="D622" s="2" t="n"/>
-      <c r="Q622" s="2" t="n"/>
+      <c r="D622" s="3" t="n"/>
+      <c r="Q622" s="3" t="n"/>
     </row>
     <row r="623">
-      <c r="D623" s="2" t="n"/>
-      <c r="Q623" s="2" t="n"/>
+      <c r="D623" s="3" t="n"/>
+      <c r="Q623" s="3" t="n"/>
     </row>
     <row r="624">
-      <c r="D624" s="2" t="n"/>
-      <c r="Q624" s="2" t="n"/>
+      <c r="D624" s="3" t="n"/>
+      <c r="Q624" s="3" t="n"/>
     </row>
     <row r="625">
-      <c r="D625" s="2" t="n"/>
-      <c r="Q625" s="2" t="n"/>
+      <c r="D625" s="3" t="n"/>
+      <c r="Q625" s="3" t="n"/>
     </row>
     <row r="626">
-      <c r="D626" s="2" t="n"/>
-      <c r="Q626" s="2" t="n"/>
+      <c r="D626" s="3" t="n"/>
+      <c r="Q626" s="3" t="n"/>
     </row>
     <row r="627">
-      <c r="D627" s="2" t="n"/>
-      <c r="Q627" s="2" t="n"/>
+      <c r="D627" s="3" t="n"/>
+      <c r="Q627" s="3" t="n"/>
     </row>
     <row r="628">
-      <c r="D628" s="2" t="n"/>
-      <c r="Q628" s="2" t="n"/>
+      <c r="D628" s="3" t="n"/>
+      <c r="Q628" s="3" t="n"/>
     </row>
     <row r="629">
-      <c r="D629" s="2" t="n"/>
-      <c r="Q629" s="2" t="n"/>
+      <c r="D629" s="3" t="n"/>
+      <c r="Q629" s="3" t="n"/>
     </row>
     <row r="630">
-      <c r="D630" s="2" t="n"/>
-      <c r="Q630" s="2" t="n"/>
+      <c r="D630" s="3" t="n"/>
+      <c r="Q630" s="3" t="n"/>
     </row>
     <row r="631">
-      <c r="D631" s="2" t="n"/>
-      <c r="Q631" s="2" t="n"/>
+      <c r="D631" s="3" t="n"/>
+      <c r="Q631" s="3" t="n"/>
     </row>
     <row r="632">
-      <c r="D632" s="2" t="n"/>
-      <c r="Q632" s="2" t="n"/>
+      <c r="D632" s="3" t="n"/>
+      <c r="Q632" s="3" t="n"/>
     </row>
     <row r="633">
-      <c r="D633" s="2" t="n"/>
-      <c r="Q633" s="2" t="n"/>
+      <c r="D633" s="3" t="n"/>
+      <c r="Q633" s="3" t="n"/>
     </row>
     <row r="634">
-      <c r="D634" s="2" t="n"/>
-      <c r="Q634" s="2" t="n"/>
+      <c r="D634" s="3" t="n"/>
+      <c r="Q634" s="3" t="n"/>
     </row>
     <row r="635">
-      <c r="D635" s="2" t="n"/>
-      <c r="Q635" s="2" t="n"/>
+      <c r="D635" s="3" t="n"/>
+      <c r="Q635" s="3" t="n"/>
     </row>
     <row r="636">
-      <c r="D636" s="2" t="n"/>
-      <c r="Q636" s="2" t="n"/>
+      <c r="D636" s="3" t="n"/>
+      <c r="Q636" s="3" t="n"/>
     </row>
     <row r="637">
-      <c r="D637" s="2" t="n"/>
-      <c r="Q637" s="2" t="n"/>
+      <c r="D637" s="3" t="n"/>
+      <c r="Q637" s="3" t="n"/>
     </row>
     <row r="638">
-      <c r="D638" s="2" t="n"/>
-      <c r="Q638" s="2" t="n"/>
+      <c r="D638" s="3" t="n"/>
+      <c r="Q638" s="3" t="n"/>
     </row>
     <row r="639">
-      <c r="D639" s="2" t="n"/>
-      <c r="Q639" s="2" t="n"/>
+      <c r="D639" s="3" t="n"/>
+      <c r="Q639" s="3" t="n"/>
     </row>
     <row r="640">
-      <c r="D640" s="2" t="n"/>
-      <c r="Q640" s="2" t="n"/>
+      <c r="D640" s="3" t="n"/>
+      <c r="Q640" s="3" t="n"/>
     </row>
     <row r="641">
-      <c r="D641" s="2" t="n"/>
-      <c r="Q641" s="2" t="n"/>
+      <c r="D641" s="3" t="n"/>
+      <c r="Q641" s="3" t="n"/>
     </row>
     <row r="642">
-      <c r="D642" s="2" t="n"/>
-      <c r="Q642" s="2" t="n"/>
+      <c r="D642" s="3" t="n"/>
+      <c r="Q642" s="3" t="n"/>
     </row>
     <row r="643">
-      <c r="D643" s="2" t="n"/>
-      <c r="Q643" s="2" t="n"/>
+      <c r="D643" s="3" t="n"/>
+      <c r="Q643" s="3" t="n"/>
     </row>
     <row r="644">
-      <c r="D644" s="2" t="n"/>
-      <c r="Q644" s="2" t="n"/>
+      <c r="D644" s="3" t="n"/>
+      <c r="Q644" s="3" t="n"/>
     </row>
     <row r="645">
-      <c r="D645" s="2" t="n"/>
-      <c r="Q645" s="2" t="n"/>
+      <c r="D645" s="3" t="n"/>
+      <c r="Q645" s="3" t="n"/>
     </row>
     <row r="646">
-      <c r="D646" s="2" t="n"/>
-      <c r="Q646" s="2" t="n"/>
+      <c r="D646" s="3" t="n"/>
+      <c r="Q646" s="3" t="n"/>
     </row>
     <row r="647">
-      <c r="D647" s="2" t="n"/>
-      <c r="Q647" s="2" t="n"/>
+      <c r="D647" s="3" t="n"/>
+      <c r="Q647" s="3" t="n"/>
     </row>
     <row r="648">
-      <c r="D648" s="2" t="n"/>
-      <c r="Q648" s="2" t="n"/>
+      <c r="D648" s="3" t="n"/>
+      <c r="Q648" s="3" t="n"/>
     </row>
     <row r="649">
-      <c r="D649" s="2" t="n"/>
-      <c r="Q649" s="2" t="n"/>
+      <c r="D649" s="3" t="n"/>
+      <c r="Q649" s="3" t="n"/>
     </row>
     <row r="650">
-      <c r="D650" s="2" t="n"/>
-      <c r="Q650" s="2" t="n"/>
+      <c r="D650" s="3" t="n"/>
+      <c r="Q650" s="3" t="n"/>
     </row>
     <row r="651">
-      <c r="D651" s="2" t="n"/>
-      <c r="Q651" s="2" t="n"/>
+      <c r="D651" s="3" t="n"/>
+      <c r="Q651" s="3" t="n"/>
     </row>
     <row r="652">
-      <c r="D652" s="2" t="n"/>
-      <c r="Q652" s="2" t="n"/>
+      <c r="D652" s="3" t="n"/>
+      <c r="Q652" s="3" t="n"/>
     </row>
     <row r="653">
-      <c r="D653" s="2" t="n"/>
-      <c r="Q653" s="2" t="n"/>
+      <c r="D653" s="3" t="n"/>
+      <c r="Q653" s="3" t="n"/>
     </row>
     <row r="654">
-      <c r="D654" s="2" t="n"/>
-      <c r="Q654" s="2" t="n"/>
+      <c r="D654" s="3" t="n"/>
+      <c r="Q654" s="3" t="n"/>
     </row>
     <row r="655">
-      <c r="D655" s="2" t="n"/>
-      <c r="Q655" s="2" t="n"/>
+      <c r="D655" s="3" t="n"/>
+      <c r="Q655" s="3" t="n"/>
     </row>
     <row r="656">
-      <c r="D656" s="2" t="n"/>
-      <c r="Q656" s="2" t="n"/>
+      <c r="D656" s="3" t="n"/>
+      <c r="Q656" s="3" t="n"/>
     </row>
     <row r="657">
-      <c r="D657" s="2" t="n"/>
-      <c r="Q657" s="2" t="n"/>
+      <c r="D657" s="3" t="n"/>
+      <c r="Q657" s="3" t="n"/>
     </row>
     <row r="658">
-      <c r="D658" s="2" t="n"/>
-      <c r="Q658" s="2" t="n"/>
+      <c r="D658" s="3" t="n"/>
+      <c r="Q658" s="3" t="n"/>
     </row>
     <row r="659">
-      <c r="D659" s="2" t="n"/>
-      <c r="Q659" s="2" t="n"/>
+      <c r="D659" s="3" t="n"/>
+      <c r="Q659" s="3" t="n"/>
     </row>
     <row r="660">
-      <c r="D660" s="2" t="n"/>
-      <c r="Q660" s="2" t="n"/>
+      <c r="D660" s="3" t="n"/>
+      <c r="Q660" s="3" t="n"/>
     </row>
     <row r="661">
-      <c r="D661" s="2" t="n"/>
-      <c r="Q661" s="2" t="n"/>
+      <c r="D661" s="3" t="n"/>
+      <c r="Q661" s="3" t="n"/>
     </row>
     <row r="662">
-      <c r="D662" s="2" t="n"/>
-      <c r="Q662" s="2" t="n"/>
+      <c r="D662" s="3" t="n"/>
+      <c r="Q662" s="3" t="n"/>
     </row>
     <row r="663">
-      <c r="D663" s="2" t="n"/>
-      <c r="Q663" s="2" t="n"/>
+      <c r="D663" s="3" t="n"/>
+      <c r="Q663" s="3" t="n"/>
     </row>
     <row r="664">
-      <c r="D664" s="2" t="n"/>
-      <c r="Q664" s="2" t="n"/>
+      <c r="D664" s="3" t="n"/>
+      <c r="Q664" s="3" t="n"/>
     </row>
     <row r="665">
-      <c r="D665" s="2" t="n"/>
-      <c r="Q665" s="2" t="n"/>
+      <c r="D665" s="3" t="n"/>
+      <c r="Q665" s="3" t="n"/>
     </row>
     <row r="666">
-      <c r="D666" s="2" t="n"/>
-      <c r="Q666" s="2" t="n"/>
+      <c r="D666" s="3" t="n"/>
+      <c r="Q666" s="3" t="n"/>
     </row>
     <row r="667">
-      <c r="D667" s="2" t="n"/>
-      <c r="Q667" s="2" t="n"/>
+      <c r="D667" s="3" t="n"/>
+      <c r="Q667" s="3" t="n"/>
     </row>
     <row r="668">
-      <c r="D668" s="2" t="n"/>
-      <c r="Q668" s="2" t="n"/>
+      <c r="D668" s="3" t="n"/>
+      <c r="Q668" s="3" t="n"/>
     </row>
     <row r="669">
-      <c r="D669" s="2" t="n"/>
-      <c r="Q669" s="2" t="n"/>
+      <c r="D669" s="3" t="n"/>
+      <c r="Q669" s="3" t="n"/>
     </row>
     <row r="670">
-      <c r="D670" s="2" t="n"/>
-      <c r="Q670" s="2" t="n"/>
+      <c r="D670" s="3" t="n"/>
+      <c r="Q670" s="3" t="n"/>
     </row>
     <row r="671">
-      <c r="D671" s="2" t="n"/>
-      <c r="Q671" s="2" t="n"/>
+      <c r="D671" s="3" t="n"/>
+      <c r="Q671" s="3" t="n"/>
     </row>
     <row r="672">
-      <c r="D672" s="2" t="n"/>
-      <c r="Q672" s="2" t="n"/>
+      <c r="D672" s="3" t="n"/>
+      <c r="Q672" s="3" t="n"/>
     </row>
     <row r="673">
-      <c r="D673" s="2" t="n"/>
-      <c r="Q673" s="2" t="n"/>
+      <c r="D673" s="3" t="n"/>
+      <c r="Q673" s="3" t="n"/>
     </row>
     <row r="674">
-      <c r="D674" s="2" t="n"/>
-      <c r="Q674" s="2" t="n"/>
+      <c r="D674" s="3" t="n"/>
+      <c r="Q674" s="3" t="n"/>
     </row>
     <row r="675">
-      <c r="D675" s="2" t="n"/>
-      <c r="Q675" s="2" t="n"/>
+      <c r="D675" s="3" t="n"/>
+      <c r="Q675" s="3" t="n"/>
     </row>
     <row r="676">
-      <c r="D676" s="2" t="n"/>
-      <c r="Q676" s="2" t="n"/>
+      <c r="D676" s="3" t="n"/>
+      <c r="Q676" s="3" t="n"/>
     </row>
     <row r="677">
-      <c r="D677" s="2" t="n"/>
-      <c r="Q677" s="2" t="n"/>
+      <c r="D677" s="3" t="n"/>
+      <c r="Q677" s="3" t="n"/>
     </row>
     <row r="678">
-      <c r="D678" s="2" t="n"/>
-      <c r="Q678" s="2" t="n"/>
+      <c r="D678" s="3" t="n"/>
+      <c r="Q678" s="3" t="n"/>
     </row>
     <row r="679">
-      <c r="D679" s="2" t="n"/>
-      <c r="Q679" s="2" t="n"/>
+      <c r="D679" s="3" t="n"/>
+      <c r="Q679" s="3" t="n"/>
     </row>
     <row r="680">
-      <c r="D680" s="2" t="n"/>
-      <c r="Q680" s="2" t="n"/>
+      <c r="D680" s="3" t="n"/>
+      <c r="Q680" s="3" t="n"/>
     </row>
     <row r="681">
-      <c r="D681" s="2" t="n"/>
-      <c r="Q681" s="2" t="n"/>
+      <c r="D681" s="3" t="n"/>
+      <c r="Q681" s="3" t="n"/>
     </row>
     <row r="682">
-      <c r="D682" s="2" t="n"/>
-      <c r="Q682" s="2" t="n"/>
+      <c r="D682" s="3" t="n"/>
+      <c r="Q682" s="3" t="n"/>
     </row>
     <row r="683">
-      <c r="D683" s="2" t="n"/>
-      <c r="Q683" s="2" t="n"/>
+      <c r="D683" s="3" t="n"/>
+      <c r="Q683" s="3" t="n"/>
     </row>
     <row r="684">
-      <c r="D684" s="2" t="n"/>
-      <c r="Q684" s="2" t="n"/>
+      <c r="D684" s="3" t="n"/>
+      <c r="Q684" s="3" t="n"/>
     </row>
     <row r="685">
-      <c r="D685" s="2" t="n"/>
-      <c r="Q685" s="2" t="n"/>
+      <c r="D685" s="3" t="n"/>
+      <c r="Q685" s="3" t="n"/>
     </row>
     <row r="686">
-      <c r="D686" s="2" t="n"/>
-      <c r="Q686" s="2" t="n"/>
+      <c r="D686" s="3" t="n"/>
+      <c r="Q686" s="3" t="n"/>
     </row>
     <row r="687">
-      <c r="D687" s="2" t="n"/>
-      <c r="Q687" s="2" t="n"/>
+      <c r="D687" s="3" t="n"/>
+      <c r="Q687" s="3" t="n"/>
     </row>
     <row r="688">
-      <c r="D688" s="2" t="n"/>
-      <c r="Q688" s="2" t="n"/>
+      <c r="D688" s="3" t="n"/>
+      <c r="Q688" s="3" t="n"/>
     </row>
     <row r="689">
-      <c r="D689" s="2" t="n"/>
-      <c r="Q689" s="2" t="n"/>
+      <c r="D689" s="3" t="n"/>
+      <c r="Q689" s="3" t="n"/>
     </row>
     <row r="690">
-      <c r="D690" s="2" t="n"/>
-      <c r="Q690" s="2" t="n"/>
+      <c r="D690" s="3" t="n"/>
+      <c r="Q690" s="3" t="n"/>
     </row>
     <row r="691">
-      <c r="D691" s="2" t="n"/>
-      <c r="Q691" s="2" t="n"/>
+      <c r="D691" s="3" t="n"/>
+      <c r="Q691" s="3" t="n"/>
     </row>
     <row r="692">
-      <c r="D692" s="2" t="n"/>
-      <c r="Q692" s="2" t="n"/>
+      <c r="D692" s="3" t="n"/>
+      <c r="Q692" s="3" t="n"/>
     </row>
     <row r="693">
-      <c r="D693" s="2" t="n"/>
-      <c r="Q693" s="2" t="n"/>
+      <c r="D693" s="3" t="n"/>
+      <c r="Q693" s="3" t="n"/>
     </row>
     <row r="694">
-      <c r="D694" s="2" t="n"/>
-      <c r="Q694" s="2" t="n"/>
+      <c r="D694" s="3" t="n"/>
+      <c r="Q694" s="3" t="n"/>
     </row>
     <row r="695">
-      <c r="D695" s="2" t="n"/>
-      <c r="Q695" s="2" t="n"/>
+      <c r="D695" s="3" t="n"/>
+      <c r="Q695" s="3" t="n"/>
     </row>
     <row r="696">
-      <c r="D696" s="2" t="n"/>
-      <c r="Q696" s="2" t="n"/>
+      <c r="D696" s="3" t="n"/>
+      <c r="Q696" s="3" t="n"/>
     </row>
     <row r="697">
-      <c r="D697" s="2" t="n"/>
-      <c r="Q697" s="2" t="n"/>
+      <c r="D697" s="3" t="n"/>
+      <c r="Q697" s="3" t="n"/>
     </row>
     <row r="698">
-      <c r="D698" s="2" t="n"/>
-      <c r="Q698" s="2" t="n"/>
+      <c r="D698" s="3" t="n"/>
+      <c r="Q698" s="3" t="n"/>
     </row>
     <row r="699">
-      <c r="D699" s="2" t="n"/>
-      <c r="Q699" s="2" t="n"/>
+      <c r="D699" s="3" t="n"/>
+      <c r="Q699" s="3" t="n"/>
     </row>
     <row r="700">
-      <c r="D700" s="2" t="n"/>
-      <c r="Q700" s="2" t="n"/>
+      <c r="D700" s="3" t="n"/>
+      <c r="Q700" s="3" t="n"/>
     </row>
     <row r="701">
-      <c r="D701" s="2" t="n"/>
-      <c r="Q701" s="2" t="n"/>
+      <c r="D701" s="3" t="n"/>
+      <c r="Q701" s="3" t="n"/>
     </row>
     <row r="702">
-      <c r="D702" s="2" t="n"/>
-      <c r="Q702" s="2" t="n"/>
+      <c r="D702" s="3" t="n"/>
+      <c r="Q702" s="3" t="n"/>
     </row>
     <row r="703">
-      <c r="D703" s="2" t="n"/>
-      <c r="Q703" s="2" t="n"/>
+      <c r="D703" s="3" t="n"/>
+      <c r="Q703" s="3" t="n"/>
     </row>
     <row r="704">
-      <c r="D704" s="2" t="n"/>
-      <c r="Q704" s="2" t="n"/>
+      <c r="D704" s="3" t="n"/>
+      <c r="Q704" s="3" t="n"/>
     </row>
     <row r="705">
-      <c r="D705" s="2" t="n"/>
-      <c r="Q705" s="2" t="n"/>
+      <c r="D705" s="3" t="n"/>
+      <c r="Q705" s="3" t="n"/>
     </row>
     <row r="706">
-      <c r="D706" s="2" t="n"/>
-      <c r="Q706" s="2" t="n"/>
+      <c r="D706" s="3" t="n"/>
+      <c r="Q706" s="3" t="n"/>
     </row>
     <row r="707">
-      <c r="D707" s="2" t="n"/>
-      <c r="Q707" s="2" t="n"/>
+      <c r="D707" s="3" t="n"/>
+      <c r="Q707" s="3" t="n"/>
     </row>
     <row r="708">
-      <c r="D708" s="2" t="n"/>
-      <c r="Q708" s="2" t="n"/>
+      <c r="D708" s="3" t="n"/>
+      <c r="Q708" s="3" t="n"/>
     </row>
     <row r="709">
-      <c r="D709" s="2" t="n"/>
-      <c r="Q709" s="2" t="n"/>
+      <c r="D709" s="3" t="n"/>
+      <c r="Q709" s="3" t="n"/>
     </row>
     <row r="710">
-      <c r="D710" s="2" t="n"/>
-      <c r="Q710" s="2" t="n"/>
+      <c r="D710" s="3" t="n"/>
+      <c r="Q710" s="3" t="n"/>
     </row>
     <row r="711">
-      <c r="D711" s="2" t="n"/>
-      <c r="Q711" s="2" t="n"/>
+      <c r="D711" s="3" t="n"/>
+      <c r="Q711" s="3" t="n"/>
     </row>
     <row r="712">
-      <c r="D712" s="2" t="n"/>
-      <c r="Q712" s="2" t="n"/>
+      <c r="D712" s="3" t="n"/>
+      <c r="Q712" s="3" t="n"/>
     </row>
     <row r="713">
-      <c r="D713" s="2" t="n"/>
-      <c r="Q713" s="2" t="n"/>
+      <c r="D713" s="3" t="n"/>
+      <c r="Q713" s="3" t="n"/>
     </row>
     <row r="714">
-      <c r="D714" s="2" t="n"/>
-      <c r="Q714" s="2" t="n"/>
+      <c r="D714" s="3" t="n"/>
+      <c r="Q714" s="3" t="n"/>
     </row>
     <row r="715">
-      <c r="D715" s="2" t="n"/>
-      <c r="Q715" s="2" t="n"/>
+      <c r="D715" s="3" t="n"/>
+      <c r="Q715" s="3" t="n"/>
     </row>
     <row r="716">
-      <c r="D716" s="2" t="n"/>
-      <c r="Q716" s="2" t="n"/>
+      <c r="D716" s="3" t="n"/>
+      <c r="Q716" s="3" t="n"/>
     </row>
     <row r="717">
-      <c r="D717" s="2" t="n"/>
-      <c r="Q717" s="2" t="n"/>
+      <c r="D717" s="3" t="n"/>
+      <c r="Q717" s="3" t="n"/>
     </row>
     <row r="718">
-      <c r="D718" s="2" t="n"/>
-      <c r="Q718" s="2" t="n"/>
+      <c r="D718" s="3" t="n"/>
+      <c r="Q718" s="3" t="n"/>
     </row>
     <row r="719">
-      <c r="D719" s="2" t="n"/>
-      <c r="Q719" s="2" t="n"/>
+      <c r="D719" s="3" t="n"/>
+      <c r="Q719" s="3" t="n"/>
     </row>
     <row r="720">
-      <c r="D720" s="2" t="n"/>
-      <c r="Q720" s="2" t="n"/>
+      <c r="D720" s="3" t="n"/>
+      <c r="Q720" s="3" t="n"/>
     </row>
     <row r="721">
-      <c r="D721" s="2" t="n"/>
-      <c r="Q721" s="2" t="n"/>
+      <c r="D721" s="3" t="n"/>
+      <c r="Q721" s="3" t="n"/>
     </row>
     <row r="722">
-      <c r="D722" s="2" t="n"/>
-      <c r="Q722" s="2" t="n"/>
+      <c r="D722" s="3" t="n"/>
+      <c r="Q722" s="3" t="n"/>
     </row>
     <row r="723">
-      <c r="D723" s="2" t="n"/>
-      <c r="Q723" s="2" t="n"/>
+      <c r="D723" s="3" t="n"/>
+      <c r="Q723" s="3" t="n"/>
     </row>
     <row r="724">
-      <c r="D724" s="2" t="n"/>
-      <c r="Q724" s="2" t="n"/>
+      <c r="D724" s="3" t="n"/>
+      <c r="Q724" s="3" t="n"/>
     </row>
     <row r="725">
-      <c r="D725" s="2" t="n"/>
-      <c r="Q725" s="2" t="n"/>
+      <c r="D725" s="3" t="n"/>
+      <c r="Q725" s="3" t="n"/>
     </row>
     <row r="726">
-      <c r="D726" s="2" t="n"/>
-      <c r="Q726" s="2" t="n"/>
+      <c r="D726" s="3" t="n"/>
+      <c r="Q726" s="3" t="n"/>
     </row>
     <row r="727">
-      <c r="D727" s="2" t="n"/>
-      <c r="Q727" s="2" t="n"/>
+      <c r="D727" s="3" t="n"/>
+      <c r="Q727" s="3" t="n"/>
     </row>
     <row r="728">
-      <c r="D728" s="2" t="n"/>
-      <c r="Q728" s="2" t="n"/>
+      <c r="D728" s="3" t="n"/>
+      <c r="Q728" s="3" t="n"/>
     </row>
     <row r="729">
-      <c r="D729" s="2" t="n"/>
-      <c r="Q729" s="2" t="n"/>
+      <c r="D729" s="3" t="n"/>
+      <c r="Q729" s="3" t="n"/>
     </row>
     <row r="730">
-      <c r="D730" s="2" t="n"/>
-      <c r="Q730" s="2" t="n"/>
+      <c r="D730" s="3" t="n"/>
+      <c r="Q730" s="3" t="n"/>
     </row>
     <row r="731">
-      <c r="D731" s="2" t="n"/>
-      <c r="Q731" s="2" t="n"/>
+      <c r="D731" s="3" t="n"/>
+      <c r="Q731" s="3" t="n"/>
     </row>
     <row r="732">
-      <c r="D732" s="2" t="n"/>
-      <c r="Q732" s="2" t="n"/>
+      <c r="D732" s="3" t="n"/>
+      <c r="Q732" s="3" t="n"/>
     </row>
     <row r="733">
-      <c r="D733" s="2" t="n"/>
-      <c r="Q733" s="2" t="n"/>
+      <c r="D733" s="3" t="n"/>
+      <c r="Q733" s="3" t="n"/>
     </row>
     <row r="734">
-      <c r="D734" s="2" t="n"/>
-      <c r="Q734" s="2" t="n"/>
+      <c r="D734" s="3" t="n"/>
+      <c r="Q734" s="3" t="n"/>
     </row>
     <row r="735">
-      <c r="D735" s="2" t="n"/>
-      <c r="Q735" s="2" t="n"/>
+      <c r="D735" s="3" t="n"/>
+      <c r="Q735" s="3" t="n"/>
     </row>
     <row r="736">
-      <c r="D736" s="2" t="n"/>
-      <c r="Q736" s="2" t="n"/>
+      <c r="D736" s="3" t="n"/>
+      <c r="Q736" s="3" t="n"/>
     </row>
     <row r="737">
-      <c r="D737" s="2" t="n"/>
-      <c r="Q737" s="2" t="n"/>
+      <c r="D737" s="3" t="n"/>
+      <c r="Q737" s="3" t="n"/>
     </row>
     <row r="738">
-      <c r="D738" s="2" t="n"/>
-      <c r="Q738" s="2" t="n"/>
+      <c r="D738" s="3" t="n"/>
+      <c r="Q738" s="3" t="n"/>
     </row>
     <row r="739">
-      <c r="D739" s="2" t="n"/>
-      <c r="Q739" s="2" t="n"/>
+      <c r="D739" s="3" t="n"/>
+      <c r="Q739" s="3" t="n"/>
     </row>
     <row r="740">
-      <c r="D740" s="2" t="n"/>
-      <c r="Q740" s="2" t="n"/>
+      <c r="D740" s="3" t="n"/>
+      <c r="Q740" s="3" t="n"/>
     </row>
     <row r="741">
-      <c r="D741" s="2" t="n"/>
-      <c r="Q741" s="2" t="n"/>
+      <c r="D741" s="3" t="n"/>
+      <c r="Q741" s="3" t="n"/>
     </row>
     <row r="742">
-      <c r="D742" s="2" t="n"/>
-      <c r="Q742" s="2" t="n"/>
+      <c r="D742" s="3" t="n"/>
+      <c r="Q742" s="3" t="n"/>
     </row>
     <row r="743">
-      <c r="D743" s="2" t="n"/>
-      <c r="Q743" s="2" t="n"/>
+      <c r="D743" s="3" t="n"/>
+      <c r="Q743" s="3" t="n"/>
     </row>
     <row r="744">
-      <c r="D744" s="2" t="n"/>
-      <c r="Q744" s="2" t="n"/>
+      <c r="D744" s="3" t="n"/>
+      <c r="Q744" s="3" t="n"/>
     </row>
     <row r="745">
-      <c r="D745" s="2" t="n"/>
-      <c r="Q745" s="2" t="n"/>
+      <c r="D745" s="3" t="n"/>
+      <c r="Q745" s="3" t="n"/>
     </row>
     <row r="746">
-      <c r="D746" s="2" t="n"/>
-      <c r="Q746" s="2" t="n"/>
+      <c r="D746" s="3" t="n"/>
+      <c r="Q746" s="3" t="n"/>
     </row>
     <row r="747">
-      <c r="D747" s="2" t="n"/>
-      <c r="Q747" s="2" t="n"/>
+      <c r="D747" s="3" t="n"/>
+      <c r="Q747" s="3" t="n"/>
     </row>
     <row r="748">
-      <c r="D748" s="2" t="n"/>
-      <c r="Q748" s="2" t="n"/>
+      <c r="D748" s="3" t="n"/>
+      <c r="Q748" s="3" t="n"/>
     </row>
     <row r="749">
-      <c r="D749" s="2" t="n"/>
-      <c r="Q749" s="2" t="n"/>
+      <c r="D749" s="3" t="n"/>
+      <c r="Q749" s="3" t="n"/>
     </row>
     <row r="750">
-      <c r="D750" s="2" t="n"/>
-      <c r="Q750" s="2" t="n"/>
+      <c r="D750" s="3" t="n"/>
+      <c r="Q750" s="3" t="n"/>
     </row>
     <row r="751">
-      <c r="D751" s="2" t="n"/>
-      <c r="Q751" s="2" t="n"/>
+      <c r="D751" s="3" t="n"/>
+      <c r="Q751" s="3" t="n"/>
     </row>
     <row r="752">
-      <c r="D752" s="2" t="n"/>
-      <c r="Q752" s="2" t="n"/>
+      <c r="D752" s="3" t="n"/>
+      <c r="Q752" s="3" t="n"/>
     </row>
     <row r="753">
-      <c r="D753" s="2" t="n"/>
-      <c r="Q753" s="2" t="n"/>
+      <c r="D753" s="3" t="n"/>
+      <c r="Q753" s="3" t="n"/>
     </row>
     <row r="754">
-      <c r="D754" s="2" t="n"/>
-      <c r="Q754" s="2" t="n"/>
+      <c r="D754" s="3" t="n"/>
+      <c r="Q754" s="3" t="n"/>
     </row>
     <row r="755">
-      <c r="D755" s="2" t="n"/>
-      <c r="Q755" s="2" t="n"/>
+      <c r="D755" s="3" t="n"/>
+      <c r="Q755" s="3" t="n"/>
     </row>
     <row r="756">
-      <c r="D756" s="2" t="n"/>
-      <c r="Q756" s="2" t="n"/>
+      <c r="D756" s="3" t="n"/>
+      <c r="Q756" s="3" t="n"/>
     </row>
     <row r="757">
-      <c r="D757" s="2" t="n"/>
-      <c r="Q757" s="2" t="n"/>
+      <c r="D757" s="3" t="n"/>
+      <c r="Q757" s="3" t="n"/>
     </row>
     <row r="758">
-      <c r="D758" s="2" t="n"/>
-      <c r="Q758" s="2" t="n"/>
+      <c r="D758" s="3" t="n"/>
+      <c r="Q758" s="3" t="n"/>
     </row>
     <row r="759">
-      <c r="D759" s="2" t="n"/>
-      <c r="Q759" s="2" t="n"/>
+      <c r="D759" s="3" t="n"/>
+      <c r="Q759" s="3" t="n"/>
     </row>
     <row r="760">
-      <c r="D760" s="2" t="n"/>
-      <c r="Q760" s="2" t="n"/>
+      <c r="D760" s="3" t="n"/>
+      <c r="Q760" s="3" t="n"/>
     </row>
     <row r="761">
-      <c r="D761" s="2" t="n"/>
-      <c r="Q761" s="2" t="n"/>
+      <c r="D761" s="3" t="n"/>
+      <c r="Q761" s="3" t="n"/>
     </row>
     <row r="762">
-      <c r="D762" s="2" t="n"/>
-      <c r="Q762" s="2" t="n"/>
+      <c r="D762" s="3" t="n"/>
+      <c r="Q762" s="3" t="n"/>
     </row>
     <row r="763">
-      <c r="D763" s="2" t="n"/>
-      <c r="Q763" s="2" t="n"/>
+      <c r="D763" s="3" t="n"/>
+      <c r="Q763" s="3" t="n"/>
     </row>
     <row r="764">
-      <c r="D764" s="2" t="n"/>
-      <c r="Q764" s="2" t="n"/>
+      <c r="D764" s="3" t="n"/>
+      <c r="Q764" s="3" t="n"/>
     </row>
     <row r="765">
-      <c r="D765" s="2" t="n"/>
-      <c r="Q765" s="2" t="n"/>
+      <c r="D765" s="3" t="n"/>
+      <c r="Q765" s="3" t="n"/>
     </row>
     <row r="766">
-      <c r="D766" s="2" t="n"/>
-      <c r="Q766" s="2" t="n"/>
+      <c r="D766" s="3" t="n"/>
+      <c r="Q766" s="3" t="n"/>
     </row>
     <row r="767">
-      <c r="D767" s="2" t="n"/>
-      <c r="Q767" s="2" t="n"/>
+      <c r="D767" s="3" t="n"/>
+      <c r="Q767" s="3" t="n"/>
     </row>
     <row r="768">
-      <c r="D768" s="2" t="n"/>
-      <c r="Q768" s="2" t="n"/>
+      <c r="D768" s="3" t="n"/>
+      <c r="Q768" s="3" t="n"/>
     </row>
     <row r="769">
-      <c r="D769" s="2" t="n"/>
-      <c r="Q769" s="2" t="n"/>
+      <c r="D769" s="3" t="n"/>
+      <c r="Q769" s="3" t="n"/>
     </row>
     <row r="770">
-      <c r="D770" s="2" t="n"/>
-      <c r="Q770" s="2" t="n"/>
+      <c r="D770" s="3" t="n"/>
+      <c r="Q770" s="3" t="n"/>
     </row>
     <row r="771">
-      <c r="D771" s="2" t="n"/>
-      <c r="Q771" s="2" t="n"/>
+      <c r="D771" s="3" t="n"/>
+      <c r="Q771" s="3" t="n"/>
     </row>
     <row r="772">
-      <c r="D772" s="2" t="n"/>
-      <c r="Q772" s="2" t="n"/>
+      <c r="D772" s="3" t="n"/>
+      <c r="Q772" s="3" t="n"/>
     </row>
     <row r="773">
-      <c r="D773" s="2" t="n"/>
-      <c r="Q773" s="2" t="n"/>
+      <c r="D773" s="3" t="n"/>
+      <c r="Q773" s="3" t="n"/>
     </row>
     <row r="774">
-      <c r="D774" s="2" t="n"/>
-      <c r="Q774" s="2" t="n"/>
+      <c r="D774" s="3" t="n"/>
+      <c r="Q774" s="3" t="n"/>
     </row>
     <row r="775">
-      <c r="D775" s="2" t="n"/>
-      <c r="Q775" s="2" t="n"/>
+      <c r="D775" s="3" t="n"/>
+      <c r="Q775" s="3" t="n"/>
     </row>
     <row r="776">
-      <c r="D776" s="2" t="n"/>
-      <c r="Q776" s="2" t="n"/>
+      <c r="D776" s="3" t="n"/>
+      <c r="Q776" s="3" t="n"/>
     </row>
     <row r="777">
-      <c r="D777" s="2" t="n"/>
-      <c r="Q777" s="2" t="n"/>
+      <c r="D777" s="3" t="n"/>
+      <c r="Q777" s="3" t="n"/>
     </row>
     <row r="778">
-      <c r="D778" s="2" t="n"/>
-      <c r="Q778" s="2" t="n"/>
+      <c r="D778" s="3" t="n"/>
+      <c r="Q778" s="3" t="n"/>
     </row>
     <row r="779">
-      <c r="D779" s="2" t="n"/>
-      <c r="Q779" s="2" t="n"/>
+      <c r="D779" s="3" t="n"/>
+      <c r="Q779" s="3" t="n"/>
     </row>
     <row r="780">
-      <c r="D780" s="2" t="n"/>
-      <c r="Q780" s="2" t="n"/>
+      <c r="D780" s="3" t="n"/>
+      <c r="Q780" s="3" t="n"/>
     </row>
     <row r="781">
-      <c r="D781" s="2" t="n"/>
-      <c r="Q781" s="2" t="n"/>
+      <c r="D781" s="3" t="n"/>
+      <c r="Q781" s="3" t="n"/>
     </row>
     <row r="782">
-      <c r="D782" s="2" t="n"/>
-      <c r="Q782" s="2" t="n"/>
+      <c r="D782" s="3" t="n"/>
+      <c r="Q782" s="3" t="n"/>
     </row>
     <row r="783">
-      <c r="D783" s="2" t="n"/>
-      <c r="Q783" s="2" t="n"/>
+      <c r="D783" s="3" t="n"/>
+      <c r="Q783" s="3" t="n"/>
     </row>
     <row r="784">
-      <c r="D784" s="2" t="n"/>
-      <c r="Q784" s="2" t="n"/>
+      <c r="D784" s="3" t="n"/>
+      <c r="Q784" s="3" t="n"/>
     </row>
     <row r="785">
-      <c r="D785" s="2" t="n"/>
-      <c r="Q785" s="2" t="n"/>
+      <c r="D785" s="3" t="n"/>
+      <c r="Q785" s="3" t="n"/>
     </row>
     <row r="786">
-      <c r="D786" s="2" t="n"/>
-      <c r="Q786" s="2" t="n"/>
+      <c r="D786" s="3" t="n"/>
+      <c r="Q786" s="3" t="n"/>
     </row>
     <row r="787">
-      <c r="D787" s="2" t="n"/>
-      <c r="Q787" s="2" t="n"/>
+      <c r="D787" s="3" t="n"/>
+      <c r="Q787" s="3" t="n"/>
     </row>
     <row r="788">
-      <c r="D788" s="2" t="n"/>
-      <c r="Q788" s="2" t="n"/>
+      <c r="D788" s="3" t="n"/>
+      <c r="Q788" s="3" t="n"/>
     </row>
     <row r="789">
-      <c r="D789" s="2" t="n"/>
-      <c r="Q789" s="2" t="n"/>
+      <c r="D789" s="3" t="n"/>
+      <c r="Q789" s="3" t="n"/>
     </row>
     <row r="790">
-      <c r="D790" s="2" t="n"/>
-      <c r="Q790" s="2" t="n"/>
+      <c r="D790" s="3" t="n"/>
+      <c r="Q790" s="3" t="n"/>
     </row>
     <row r="791">
-      <c r="D791" s="2" t="n"/>
-      <c r="Q791" s="2" t="n"/>
+      <c r="D791" s="3" t="n"/>
+      <c r="Q791" s="3" t="n"/>
     </row>
     <row r="792">
-      <c r="D792" s="2" t="n"/>
-      <c r="Q792" s="2" t="n"/>
+      <c r="D792" s="3" t="n"/>
+      <c r="Q792" s="3" t="n"/>
     </row>
     <row r="793">
-      <c r="D793" s="2" t="n"/>
-      <c r="Q793" s="2" t="n"/>
+      <c r="D793" s="3" t="n"/>
+      <c r="Q793" s="3" t="n"/>
     </row>
     <row r="794">
-      <c r="D794" s="2" t="n"/>
-      <c r="Q794" s="2" t="n"/>
+      <c r="D794" s="3" t="n"/>
+      <c r="Q794" s="3" t="n"/>
     </row>
     <row r="795">
-      <c r="D795" s="2" t="n"/>
-      <c r="Q795" s="2" t="n"/>
+      <c r="D795" s="3" t="n"/>
+      <c r="Q795" s="3" t="n"/>
     </row>
     <row r="796">
-      <c r="D796" s="2" t="n"/>
-      <c r="Q796" s="2" t="n"/>
+      <c r="D796" s="3" t="n"/>
+      <c r="Q796" s="3" t="n"/>
     </row>
     <row r="797">
-      <c r="D797" s="2" t="n"/>
-      <c r="Q797" s="2" t="n"/>
+      <c r="D797" s="3" t="n"/>
+      <c r="Q797" s="3" t="n"/>
     </row>
     <row r="798">
-      <c r="D798" s="2" t="n"/>
-      <c r="Q798" s="2" t="n"/>
+      <c r="D798" s="3" t="n"/>
+      <c r="Q798" s="3" t="n"/>
     </row>
     <row r="799">
-      <c r="D799" s="2" t="n"/>
-      <c r="Q799" s="2" t="n"/>
+      <c r="D799" s="3" t="n"/>
+      <c r="Q799" s="3" t="n"/>
     </row>
     <row r="800">
-      <c r="D800" s="2" t="n"/>
-      <c r="Q800" s="2" t="n"/>
+      <c r="D800" s="3" t="n"/>
+      <c r="Q800" s="3" t="n"/>
     </row>
     <row r="801">
-      <c r="D801" s="2" t="n"/>
-      <c r="Q801" s="2" t="n"/>
+      <c r="D801" s="3" t="n"/>
+      <c r="Q801" s="3" t="n"/>
     </row>
     <row r="802">
-      <c r="D802" s="2" t="n"/>
-      <c r="Q802" s="2" t="n"/>
+      <c r="D802" s="3" t="n"/>
+      <c r="Q802" s="3" t="n"/>
     </row>
     <row r="803">
-      <c r="D803" s="2" t="n"/>
-      <c r="Q803" s="2" t="n"/>
+      <c r="D803" s="3" t="n"/>
+      <c r="Q803" s="3" t="n"/>
     </row>
     <row r="804">
-      <c r="D804" s="2" t="n"/>
-      <c r="Q804" s="2" t="n"/>
+      <c r="D804" s="3" t="n"/>
+      <c r="Q804" s="3" t="n"/>
     </row>
     <row r="805">
-      <c r="D805" s="2" t="n"/>
-      <c r="Q805" s="2" t="n"/>
+      <c r="D805" s="3" t="n"/>
+      <c r="Q805" s="3" t="n"/>
     </row>
     <row r="806">
-      <c r="D806" s="2" t="n"/>
-      <c r="Q806" s="2" t="n"/>
+      <c r="D806" s="3" t="n"/>
+      <c r="Q806" s="3" t="n"/>
     </row>
     <row r="807">
-      <c r="D807" s="2" t="n"/>
-      <c r="Q807" s="2" t="n"/>
+      <c r="D807" s="3" t="n"/>
+      <c r="Q807" s="3" t="n"/>
     </row>
     <row r="808">
-      <c r="D808" s="2" t="n"/>
-      <c r="Q808" s="2" t="n"/>
+      <c r="D808" s="3" t="n"/>
+      <c r="Q808" s="3" t="n"/>
     </row>
     <row r="809">
-      <c r="D809" s="2" t="n"/>
-      <c r="Q809" s="2" t="n"/>
+      <c r="D809" s="3" t="n"/>
+      <c r="Q809" s="3" t="n"/>
     </row>
     <row r="810">
-      <c r="D810" s="2" t="n"/>
-      <c r="Q810" s="2" t="n"/>
+      <c r="D810" s="3" t="n"/>
+      <c r="Q810" s="3" t="n"/>
     </row>
     <row r="811">
-      <c r="D811" s="2" t="n"/>
-      <c r="Q811" s="2" t="n"/>
+      <c r="D811" s="3" t="n"/>
+      <c r="Q811" s="3" t="n"/>
     </row>
     <row r="812">
-      <c r="D812" s="2" t="n"/>
-      <c r="Q812" s="2" t="n"/>
+      <c r="D812" s="3" t="n"/>
+      <c r="Q812" s="3" t="n"/>
     </row>
     <row r="813">
-      <c r="D813" s="2" t="n"/>
-      <c r="Q813" s="2" t="n"/>
+      <c r="D813" s="3" t="n"/>
+      <c r="Q813" s="3" t="n"/>
     </row>
     <row r="814">
-      <c r="D814" s="2" t="n"/>
-      <c r="Q814" s="2" t="n"/>
+      <c r="D814" s="3" t="n"/>
+      <c r="Q814" s="3" t="n"/>
     </row>
     <row r="815">
-      <c r="D815" s="2" t="n"/>
-      <c r="Q815" s="2" t="n"/>
+      <c r="D815" s="3" t="n"/>
+      <c r="Q815" s="3" t="n"/>
     </row>
     <row r="816">
-      <c r="D816" s="2" t="n"/>
-      <c r="Q816" s="2" t="n"/>
+      <c r="D816" s="3" t="n"/>
+      <c r="Q816" s="3" t="n"/>
     </row>
     <row r="817">
-      <c r="D817" s="2" t="n"/>
-      <c r="Q817" s="2" t="n"/>
+      <c r="D817" s="3" t="n"/>
+      <c r="Q817" s="3" t="n"/>
     </row>
     <row r="818">
-      <c r="D818" s="2" t="n"/>
-      <c r="Q818" s="2" t="n"/>
+      <c r="D818" s="3" t="n"/>
+      <c r="Q818" s="3" t="n"/>
     </row>
     <row r="819">
-      <c r="D819" s="2" t="n"/>
-      <c r="Q819" s="2" t="n"/>
+      <c r="D819" s="3" t="n"/>
+      <c r="Q819" s="3" t="n"/>
     </row>
     <row r="820">
-      <c r="D820" s="2" t="n"/>
-      <c r="Q820" s="2" t="n"/>
+      <c r="D820" s="3" t="n"/>
+      <c r="Q820" s="3" t="n"/>
     </row>
     <row r="821">
-      <c r="D821" s="2" t="n"/>
-      <c r="Q821" s="2" t="n"/>
+      <c r="D821" s="3" t="n"/>
+      <c r="Q821" s="3" t="n"/>
     </row>
     <row r="822">
-      <c r="D822" s="2" t="n"/>
-      <c r="Q822" s="2" t="n"/>
+      <c r="D822" s="3" t="n"/>
+      <c r="Q822" s="3" t="n"/>
     </row>
     <row r="823">
-      <c r="D823" s="2" t="n"/>
-      <c r="Q823" s="2" t="n"/>
+      <c r="D823" s="3" t="n"/>
+      <c r="Q823" s="3" t="n"/>
     </row>
     <row r="824">
-      <c r="D824" s="2" t="n"/>
-      <c r="Q824" s="2" t="n"/>
+      <c r="D824" s="3" t="n"/>
+      <c r="Q824" s="3" t="n"/>
     </row>
     <row r="825">
-      <c r="D825" s="2" t="n"/>
-      <c r="Q825" s="2" t="n"/>
+      <c r="D825" s="3" t="n"/>
+      <c r="Q825" s="3" t="n"/>
     </row>
     <row r="826">
-      <c r="D826" s="2" t="n"/>
-      <c r="Q826" s="2" t="n"/>
+      <c r="D826" s="3" t="n"/>
+      <c r="Q826" s="3" t="n"/>
     </row>
     <row r="827">
-      <c r="D827" s="2" t="n"/>
-      <c r="Q827" s="2" t="n"/>
+      <c r="D827" s="3" t="n"/>
+      <c r="Q827" s="3" t="n"/>
     </row>
     <row r="828">
-      <c r="D828" s="2" t="n"/>
-      <c r="Q828" s="2" t="n"/>
+      <c r="D828" s="3" t="n"/>
+      <c r="Q828" s="3" t="n"/>
     </row>
     <row r="829">
-      <c r="D829" s="2" t="n"/>
-      <c r="Q829" s="2" t="n"/>
+      <c r="D829" s="3" t="n"/>
+      <c r="Q829" s="3" t="n"/>
     </row>
     <row r="830">
-      <c r="D830" s="2" t="n"/>
-      <c r="Q830" s="2" t="n"/>
+      <c r="D830" s="3" t="n"/>
+      <c r="Q830" s="3" t="n"/>
     </row>
     <row r="831">
-      <c r="D831" s="2" t="n"/>
-      <c r="Q831" s="2" t="n"/>
+      <c r="D831" s="3" t="n"/>
+      <c r="Q831" s="3" t="n"/>
     </row>
     <row r="832">
-      <c r="D832" s="2" t="n"/>
-      <c r="Q832" s="2" t="n"/>
+      <c r="D832" s="3" t="n"/>
+      <c r="Q832" s="3" t="n"/>
     </row>
     <row r="833">
-      <c r="D833" s="2" t="n"/>
-      <c r="Q833" s="2" t="n"/>
+      <c r="D833" s="3" t="n"/>
+      <c r="Q833" s="3" t="n"/>
     </row>
     <row r="834">
-      <c r="D834" s="2" t="n"/>
-      <c r="Q834" s="2" t="n"/>
+      <c r="D834" s="3" t="n"/>
+      <c r="Q834" s="3" t="n"/>
     </row>
     <row r="835">
-      <c r="D835" s="2" t="n"/>
-      <c r="Q835" s="2" t="n"/>
+      <c r="D835" s="3" t="n"/>
+      <c r="Q835" s="3" t="n"/>
     </row>
     <row r="836">
-      <c r="D836" s="2" t="n"/>
-      <c r="Q836" s="2" t="n"/>
+      <c r="D836" s="3" t="n"/>
+      <c r="Q836" s="3" t="n"/>
     </row>
     <row r="837">
-      <c r="D837" s="2" t="n"/>
-      <c r="Q837" s="2" t="n"/>
+      <c r="D837" s="3" t="n"/>
+      <c r="Q837" s="3" t="n"/>
     </row>
     <row r="838">
-      <c r="D838" s="2" t="n"/>
-      <c r="Q838" s="2" t="n"/>
+      <c r="D838" s="3" t="n"/>
+      <c r="Q838" s="3" t="n"/>
     </row>
     <row r="839">
-      <c r="D839" s="2" t="n"/>
-      <c r="Q839" s="2" t="n"/>
+      <c r="D839" s="3" t="n"/>
+      <c r="Q839" s="3" t="n"/>
     </row>
     <row r="840">
-      <c r="D840" s="2" t="n"/>
-      <c r="Q840" s="2" t="n"/>
+      <c r="D840" s="3" t="n"/>
+      <c r="Q840" s="3" t="n"/>
     </row>
     <row r="841">
-      <c r="D841" s="2" t="n"/>
-      <c r="Q841" s="2" t="n"/>
+      <c r="D841" s="3" t="n"/>
+      <c r="Q841" s="3" t="n"/>
     </row>
     <row r="842">
-      <c r="D842" s="2" t="n"/>
-      <c r="Q842" s="2" t="n"/>
+      <c r="D842" s="3" t="n"/>
+      <c r="Q842" s="3" t="n"/>
     </row>
     <row r="843">
-      <c r="D843" s="2" t="n"/>
-      <c r="Q843" s="2" t="n"/>
+      <c r="D843" s="3" t="n"/>
+      <c r="Q843" s="3" t="n"/>
     </row>
     <row r="844">
-      <c r="D844" s="2" t="n"/>
-      <c r="Q844" s="2" t="n"/>
+      <c r="D844" s="3" t="n"/>
+      <c r="Q844" s="3" t="n"/>
     </row>
     <row r="845">
-      <c r="D845" s="2" t="n"/>
-      <c r="Q845" s="2" t="n"/>
+      <c r="D845" s="3" t="n"/>
+      <c r="Q845" s="3" t="n"/>
     </row>
     <row r="846">
-      <c r="D846" s="2" t="n"/>
-      <c r="Q846" s="2" t="n"/>
+      <c r="D846" s="3" t="n"/>
+      <c r="Q846" s="3" t="n"/>
     </row>
     <row r="847">
-      <c r="D847" s="2" t="n"/>
-      <c r="Q847" s="2" t="n"/>
+      <c r="D847" s="3" t="n"/>
+      <c r="Q847" s="3" t="n"/>
     </row>
     <row r="848">
-      <c r="D848" s="2" t="n"/>
-      <c r="Q848" s="2" t="n"/>
+      <c r="D848" s="3" t="n"/>
+      <c r="Q848" s="3" t="n"/>
     </row>
     <row r="849">
-      <c r="D849" s="2" t="n"/>
-      <c r="Q849" s="2" t="n"/>
+      <c r="D849" s="3" t="n"/>
+      <c r="Q849" s="3" t="n"/>
     </row>
     <row r="850">
-      <c r="D850" s="2" t="n"/>
-      <c r="Q850" s="2" t="n"/>
+      <c r="D850" s="3" t="n"/>
+      <c r="Q850" s="3" t="n"/>
     </row>
     <row r="851">
-      <c r="D851" s="2" t="n"/>
-      <c r="Q851" s="2" t="n"/>
+      <c r="D851" s="3" t="n"/>
+      <c r="Q851" s="3" t="n"/>
     </row>
     <row r="852">
-      <c r="D852" s="2" t="n"/>
-      <c r="Q852" s="2" t="n"/>
+      <c r="D852" s="3" t="n"/>
+      <c r="Q852" s="3" t="n"/>
     </row>
     <row r="853">
-      <c r="D853" s="2" t="n"/>
-      <c r="Q853" s="2" t="n"/>
+      <c r="D853" s="3" t="n"/>
+      <c r="Q853" s="3" t="n"/>
     </row>
     <row r="854">
-      <c r="D854" s="2" t="n"/>
-      <c r="Q854" s="2" t="n"/>
+      <c r="D854" s="3" t="n"/>
+      <c r="Q854" s="3" t="n"/>
     </row>
     <row r="855">
-      <c r="D855" s="2" t="n"/>
-      <c r="Q855" s="2" t="n"/>
+      <c r="D855" s="3" t="n"/>
+      <c r="Q855" s="3" t="n"/>
     </row>
     <row r="856">
-      <c r="D856" s="2" t="n"/>
-      <c r="Q856" s="2" t="n"/>
+      <c r="D856" s="3" t="n"/>
+      <c r="Q856" s="3" t="n"/>
     </row>
     <row r="857">
-      <c r="D857" s="2" t="n"/>
-      <c r="Q857" s="2" t="n"/>
+      <c r="D857" s="3" t="n"/>
+      <c r="Q857" s="3" t="n"/>
     </row>
     <row r="858">
-      <c r="D858" s="2" t="n"/>
-      <c r="Q858" s="2" t="n"/>
+      <c r="D858" s="3" t="n"/>
+      <c r="Q858" s="3" t="n"/>
     </row>
     <row r="859">
-      <c r="D859" s="2" t="n"/>
-      <c r="Q859" s="2" t="n"/>
+      <c r="D859" s="3" t="n"/>
+      <c r="Q859" s="3" t="n"/>
     </row>
     <row r="860">
-      <c r="D860" s="2" t="n"/>
-      <c r="Q860" s="2" t="n"/>
+      <c r="D860" s="3" t="n"/>
+      <c r="Q860" s="3" t="n"/>
     </row>
     <row r="861">
-      <c r="D861" s="2" t="n"/>
-      <c r="Q861" s="2" t="n"/>
+      <c r="D861" s="3" t="n"/>
+      <c r="Q861" s="3" t="n"/>
     </row>
     <row r="862">
-      <c r="D862" s="2" t="n"/>
-      <c r="Q862" s="2" t="n"/>
+      <c r="D862" s="3" t="n"/>
+      <c r="Q862" s="3" t="n"/>
     </row>
     <row r="863">
-      <c r="D863" s="2" t="n"/>
-      <c r="Q863" s="2" t="n"/>
+      <c r="D863" s="3" t="n"/>
+      <c r="Q863" s="3" t="n"/>
     </row>
     <row r="864">
-      <c r="D864" s="2" t="n"/>
-      <c r="Q864" s="2" t="n"/>
+      <c r="D864" s="3" t="n"/>
+      <c r="Q864" s="3" t="n"/>
     </row>
     <row r="865">
-      <c r="D865" s="2" t="n"/>
-      <c r="Q865" s="2" t="n"/>
+      <c r="D865" s="3" t="n"/>
+      <c r="Q865" s="3" t="n"/>
     </row>
     <row r="866">
-      <c r="D866" s="2" t="n"/>
-      <c r="Q866" s="2" t="n"/>
+      <c r="D866" s="3" t="n"/>
+      <c r="Q866" s="3" t="n"/>
     </row>
     <row r="867">
-      <c r="D867" s="2" t="n"/>
-      <c r="Q867" s="2" t="n"/>
+      <c r="D867" s="3" t="n"/>
+      <c r="Q867" s="3" t="n"/>
     </row>
     <row r="868">
-      <c r="D868" s="2" t="n"/>
-      <c r="Q868" s="2" t="n"/>
+      <c r="D868" s="3" t="n"/>
+      <c r="Q868" s="3" t="n"/>
     </row>
     <row r="869">
-      <c r="D869" s="2" t="n"/>
-      <c r="Q869" s="2" t="n"/>
+      <c r="D869" s="3" t="n"/>
+      <c r="Q869" s="3" t="n"/>
     </row>
     <row r="870">
-      <c r="D870" s="2" t="n"/>
-      <c r="Q870" s="2" t="n"/>
+      <c r="D870" s="3" t="n"/>
+      <c r="Q870" s="3" t="n"/>
     </row>
     <row r="871">
-      <c r="D871" s="2" t="n"/>
-      <c r="Q871" s="2" t="n"/>
+      <c r="D871" s="3" t="n"/>
+      <c r="Q871" s="3" t="n"/>
     </row>
     <row r="872">
-      <c r="D872" s="2" t="n"/>
-      <c r="Q872" s="2" t="n"/>
+      <c r="D872" s="3" t="n"/>
+      <c r="Q872" s="3" t="n"/>
     </row>
     <row r="873">
-      <c r="D873" s="2" t="n"/>
-      <c r="Q873" s="2" t="n"/>
+      <c r="D873" s="3" t="n"/>
+      <c r="Q873" s="3" t="n"/>
     </row>
     <row r="874">
-      <c r="D874" s="2" t="n"/>
-      <c r="Q874" s="2" t="n"/>
+      <c r="D874" s="3" t="n"/>
+      <c r="Q874" s="3" t="n"/>
     </row>
     <row r="875">
-      <c r="D875" s="2" t="n"/>
-      <c r="Q875" s="2" t="n"/>
+      <c r="D875" s="3" t="n"/>
+      <c r="Q875" s="3" t="n"/>
     </row>
     <row r="876">
-      <c r="D876" s="2" t="n"/>
-      <c r="Q876" s="2" t="n"/>
+      <c r="D876" s="3" t="n"/>
+      <c r="Q876" s="3" t="n"/>
     </row>
     <row r="877">
-      <c r="D877" s="2" t="n"/>
-      <c r="Q877" s="2" t="n"/>
+      <c r="D877" s="3" t="n"/>
+      <c r="Q877" s="3" t="n"/>
     </row>
     <row r="878">
-      <c r="D878" s="2" t="n"/>
-      <c r="Q878" s="2" t="n"/>
+      <c r="D878" s="3" t="n"/>
+      <c r="Q878" s="3" t="n"/>
     </row>
     <row r="879">
-      <c r="D879" s="2" t="n"/>
-      <c r="Q879" s="2" t="n"/>
+      <c r="D879" s="3" t="n"/>
+      <c r="Q879" s="3" t="n"/>
     </row>
     <row r="880">
-      <c r="D880" s="2" t="n"/>
-      <c r="Q880" s="2" t="n"/>
+      <c r="D880" s="3" t="n"/>
+      <c r="Q880" s="3" t="n"/>
     </row>
     <row r="881">
-      <c r="D881" s="2" t="n"/>
-      <c r="Q881" s="2" t="n"/>
+      <c r="D881" s="3" t="n"/>
+      <c r="Q881" s="3" t="n"/>
     </row>
     <row r="882">
-      <c r="D882" s="2" t="n"/>
-      <c r="Q882" s="2" t="n"/>
+      <c r="D882" s="3" t="n"/>
+      <c r="Q882" s="3" t="n"/>
     </row>
     <row r="883">
-      <c r="D883" s="2" t="n"/>
-      <c r="Q883" s="2" t="n"/>
+      <c r="D883" s="3" t="n"/>
+      <c r="Q883" s="3" t="n"/>
     </row>
     <row r="884">
-      <c r="D884" s="2" t="n"/>
-      <c r="Q884" s="2" t="n"/>
+      <c r="D884" s="3" t="n"/>
+      <c r="Q884" s="3" t="n"/>
     </row>
     <row r="885">
-      <c r="D885" s="2" t="n"/>
-      <c r="Q885" s="2" t="n"/>
+      <c r="D885" s="3" t="n"/>
+      <c r="Q885" s="3" t="n"/>
     </row>
     <row r="886">
-      <c r="D886" s="2" t="n"/>
-      <c r="Q886" s="2" t="n"/>
+      <c r="D886" s="3" t="n"/>
+      <c r="Q886" s="3" t="n"/>
     </row>
     <row r="887">
-      <c r="D887" s="2" t="n"/>
-      <c r="Q887" s="2" t="n"/>
+      <c r="D887" s="3" t="n"/>
+      <c r="Q887" s="3" t="n"/>
     </row>
     <row r="888">
-      <c r="D888" s="2" t="n"/>
-      <c r="Q888" s="2" t="n"/>
+      <c r="D888" s="3" t="n"/>
+      <c r="Q888" s="3" t="n"/>
     </row>
     <row r="889">
-      <c r="D889" s="2" t="n"/>
-      <c r="Q889" s="2" t="n"/>
+      <c r="D889" s="3" t="n"/>
+      <c r="Q889" s="3" t="n"/>
     </row>
     <row r="890">
-      <c r="D890" s="2" t="n"/>
-      <c r="Q890" s="2" t="n"/>
+      <c r="D890" s="3" t="n"/>
+      <c r="Q890" s="3" t="n"/>
     </row>
     <row r="891">
-      <c r="D891" s="2" t="n"/>
-      <c r="Q891" s="2" t="n"/>
+      <c r="D891" s="3" t="n"/>
+      <c r="Q891" s="3" t="n"/>
     </row>
     <row r="892">
-      <c r="D892" s="2" t="n"/>
-      <c r="Q892" s="2" t="n"/>
+      <c r="D892" s="3" t="n"/>
+      <c r="Q892" s="3" t="n"/>
     </row>
     <row r="893">
-      <c r="D893" s="2" t="n"/>
-      <c r="Q893" s="2" t="n"/>
+      <c r="D893" s="3" t="n"/>
+      <c r="Q893" s="3" t="n"/>
     </row>
     <row r="894">
-      <c r="D894" s="2" t="n"/>
-      <c r="Q894" s="2" t="n"/>
+      <c r="D894" s="3" t="n"/>
+      <c r="Q894" s="3" t="n"/>
     </row>
     <row r="895">
-      <c r="D895" s="2" t="n"/>
-      <c r="Q895" s="2" t="n"/>
+      <c r="D895" s="3" t="n"/>
+      <c r="Q895" s="3" t="n"/>
     </row>
     <row r="896">
-      <c r="D896" s="2" t="n"/>
-      <c r="Q896" s="2" t="n"/>
+      <c r="D896" s="3" t="n"/>
+      <c r="Q896" s="3" t="n"/>
     </row>
     <row r="897">
-      <c r="D897" s="2" t="n"/>
-      <c r="Q897" s="2" t="n"/>
+      <c r="D897" s="3" t="n"/>
+      <c r="Q897" s="3" t="n"/>
     </row>
     <row r="898">
-      <c r="D898" s="2" t="n"/>
-      <c r="Q898" s="2" t="n"/>
+      <c r="D898" s="3" t="n"/>
+      <c r="Q898" s="3" t="n"/>
     </row>
     <row r="899">
-      <c r="D899" s="2" t="n"/>
-      <c r="Q899" s="2" t="n"/>
+      <c r="D899" s="3" t="n"/>
+      <c r="Q899" s="3" t="n"/>
     </row>
     <row r="900">
-      <c r="D900" s="2" t="n"/>
-      <c r="Q900" s="2" t="n"/>
+      <c r="D900" s="3" t="n"/>
+      <c r="Q900" s="3" t="n"/>
     </row>
     <row r="901">
-      <c r="D901" s="2" t="n"/>
-      <c r="Q901" s="2" t="n"/>
+      <c r="D901" s="3" t="n"/>
+      <c r="Q901" s="3" t="n"/>
     </row>
     <row r="902">
-      <c r="D902" s="2" t="n"/>
-      <c r="Q902" s="2" t="n"/>
+      <c r="D902" s="3" t="n"/>
+      <c r="Q902" s="3" t="n"/>
     </row>
     <row r="903">
-      <c r="D903" s="2" t="n"/>
-      <c r="Q903" s="2" t="n"/>
+      <c r="D903" s="3" t="n"/>
+      <c r="Q903" s="3" t="n"/>
     </row>
     <row r="904">
-      <c r="D904" s="2" t="n"/>
-      <c r="Q904" s="2" t="n"/>
+      <c r="D904" s="3" t="n"/>
+      <c r="Q904" s="3" t="n"/>
     </row>
     <row r="905">
-      <c r="D905" s="2" t="n"/>
-      <c r="Q905" s="2" t="n"/>
+      <c r="D905" s="3" t="n"/>
+      <c r="Q905" s="3" t="n"/>
     </row>
     <row r="906">
-      <c r="D906" s="2" t="n"/>
-      <c r="Q906" s="2" t="n"/>
+      <c r="D906" s="3" t="n"/>
+      <c r="Q906" s="3" t="n"/>
     </row>
     <row r="907">
-      <c r="D907" s="2" t="n"/>
-      <c r="Q907" s="2" t="n"/>
+      <c r="D907" s="3" t="n"/>
+      <c r="Q907" s="3" t="n"/>
     </row>
     <row r="908">
-      <c r="D908" s="2" t="n"/>
-      <c r="Q908" s="2" t="n"/>
+      <c r="D908" s="3" t="n"/>
+      <c r="Q908" s="3" t="n"/>
     </row>
     <row r="909">
-      <c r="D909" s="2" t="n"/>
-      <c r="Q909" s="2" t="n"/>
+      <c r="D909" s="3" t="n"/>
+      <c r="Q909" s="3" t="n"/>
     </row>
     <row r="910">
-      <c r="D910" s="2" t="n"/>
-      <c r="Q910" s="2" t="n"/>
+      <c r="D910" s="3" t="n"/>
+      <c r="Q910" s="3" t="n"/>
     </row>
     <row r="911">
-      <c r="D911" s="2" t="n"/>
-      <c r="Q911" s="2" t="n"/>
+      <c r="D911" s="3" t="n"/>
+      <c r="Q911" s="3" t="n"/>
     </row>
     <row r="912">
-      <c r="D912" s="2" t="n"/>
-      <c r="Q912" s="2" t="n"/>
+      <c r="D912" s="3" t="n"/>
+      <c r="Q912" s="3" t="n"/>
     </row>
     <row r="913">
-      <c r="D913" s="2" t="n"/>
-      <c r="Q913" s="2" t="n"/>
+      <c r="D913" s="3" t="n"/>
+      <c r="Q913" s="3" t="n"/>
     </row>
     <row r="914">
-      <c r="D914" s="2" t="n"/>
-      <c r="Q914" s="2" t="n"/>
+      <c r="D914" s="3" t="n"/>
+      <c r="Q914" s="3" t="n"/>
     </row>
     <row r="915">
-      <c r="D915" s="2" t="n"/>
-      <c r="Q915" s="2" t="n"/>
+      <c r="D915" s="3" t="n"/>
+      <c r="Q915" s="3" t="n"/>
     </row>
     <row r="916">
-      <c r="D916" s="2" t="n"/>
-      <c r="Q916" s="2" t="n"/>
+      <c r="D916" s="3" t="n"/>
+      <c r="Q916" s="3" t="n"/>
     </row>
     <row r="917">
-      <c r="D917" s="2" t="n"/>
-      <c r="Q917" s="2" t="n"/>
+      <c r="D917" s="3" t="n"/>
+      <c r="Q917" s="3" t="n"/>
     </row>
     <row r="918">
-      <c r="D918" s="2" t="n"/>
-      <c r="Q918" s="2" t="n"/>
+      <c r="D918" s="3" t="n"/>
+      <c r="Q918" s="3" t="n"/>
     </row>
     <row r="919">
-      <c r="D919" s="2" t="n"/>
-      <c r="Q919" s="2" t="n"/>
+      <c r="D919" s="3" t="n"/>
+      <c r="Q919" s="3" t="n"/>
     </row>
     <row r="920">
-      <c r="D920" s="2" t="n"/>
-      <c r="Q920" s="2" t="n"/>
+      <c r="D920" s="3" t="n"/>
+      <c r="Q920" s="3" t="n"/>
     </row>
     <row r="921">
-      <c r="D921" s="2" t="n"/>
-      <c r="Q921" s="2" t="n"/>
+      <c r="D921" s="3" t="n"/>
+      <c r="Q921" s="3" t="n"/>
     </row>
     <row r="922">
-      <c r="D922" s="2" t="n"/>
-      <c r="Q922" s="2" t="n"/>
+      <c r="D922" s="3" t="n"/>
+      <c r="Q922" s="3" t="n"/>
     </row>
     <row r="923">
-      <c r="D923" s="2" t="n"/>
-      <c r="Q923" s="2" t="n"/>
+      <c r="D923" s="3" t="n"/>
+      <c r="Q923" s="3" t="n"/>
     </row>
     <row r="924">
-      <c r="D924" s="2" t="n"/>
-      <c r="Q924" s="2" t="n"/>
+      <c r="D924" s="3" t="n"/>
+      <c r="Q924" s="3" t="n"/>
     </row>
     <row r="925">
-      <c r="D925" s="2" t="n"/>
-      <c r="Q925" s="2" t="n"/>
+      <c r="D925" s="3" t="n"/>
+      <c r="Q925" s="3" t="n"/>
     </row>
     <row r="926">
-      <c r="D926" s="2" t="n"/>
-      <c r="Q926" s="2" t="n"/>
+      <c r="D926" s="3" t="n"/>
+      <c r="Q926" s="3" t="n"/>
     </row>
     <row r="927">
-      <c r="D927" s="2" t="n"/>
-      <c r="Q927" s="2" t="n"/>
+      <c r="D927" s="3" t="n"/>
+      <c r="Q927" s="3" t="n"/>
     </row>
     <row r="928">
-      <c r="D928" s="2" t="n"/>
-      <c r="Q928" s="2" t="n"/>
+      <c r="D928" s="3" t="n"/>
+      <c r="Q928" s="3" t="n"/>
     </row>
     <row r="929">
-      <c r="D929" s="2" t="n"/>
-      <c r="Q929" s="2" t="n"/>
+      <c r="D929" s="3" t="n"/>
+      <c r="Q929" s="3" t="n"/>
     </row>
     <row r="930">
-      <c r="D930" s="2" t="n"/>
-      <c r="Q930" s="2" t="n"/>
+      <c r="D930" s="3" t="n"/>
+      <c r="Q930" s="3" t="n"/>
     </row>
     <row r="931">
-      <c r="D931" s="2" t="n"/>
-      <c r="Q931" s="2" t="n"/>
+      <c r="D931" s="3" t="n"/>
+      <c r="Q931" s="3" t="n"/>
     </row>
     <row r="932">
-      <c r="D932" s="2" t="n"/>
-      <c r="Q932" s="2" t="n"/>
+      <c r="D932" s="3" t="n"/>
+      <c r="Q932" s="3" t="n"/>
     </row>
     <row r="933">
-      <c r="D933" s="2" t="n"/>
-      <c r="Q933" s="2" t="n"/>
+      <c r="D933" s="3" t="n"/>
+      <c r="Q933" s="3" t="n"/>
     </row>
     <row r="934">
-      <c r="D934" s="2" t="n"/>
-      <c r="Q934" s="2" t="n"/>
+      <c r="D934" s="3" t="n"/>
+      <c r="Q934" s="3" t="n"/>
     </row>
     <row r="935">
-      <c r="D935" s="2" t="n"/>
-      <c r="Q935" s="2" t="n"/>
+      <c r="D935" s="3" t="n"/>
+      <c r="Q935" s="3" t="n"/>
     </row>
     <row r="936">
-      <c r="D936" s="2" t="n"/>
-      <c r="Q936" s="2" t="n"/>
+      <c r="D936" s="3" t="n"/>
+      <c r="Q936" s="3" t="n"/>
     </row>
     <row r="937">
-      <c r="D937" s="2" t="n"/>
-      <c r="Q937" s="2" t="n"/>
+      <c r="D937" s="3" t="n"/>
+      <c r="Q937" s="3" t="n"/>
     </row>
     <row r="938">
-      <c r="D938" s="2" t="n"/>
-      <c r="Q938" s="2" t="n"/>
+      <c r="D938" s="3" t="n"/>
+      <c r="Q938" s="3" t="n"/>
     </row>
     <row r="939">
-      <c r="D939" s="2" t="n"/>
-      <c r="Q939" s="2" t="n"/>
+      <c r="D939" s="3" t="n"/>
+      <c r="Q939" s="3" t="n"/>
     </row>
     <row r="940">
-      <c r="D940" s="2" t="n"/>
-      <c r="Q940" s="2" t="n"/>
+      <c r="D940" s="3" t="n"/>
+      <c r="Q940" s="3" t="n"/>
     </row>
     <row r="941">
-      <c r="D941" s="2" t="n"/>
-      <c r="Q941" s="2" t="n"/>
+      <c r="D941" s="3" t="n"/>
+      <c r="Q941" s="3" t="n"/>
     </row>
     <row r="942">
-      <c r="D942" s="2" t="n"/>
-      <c r="Q942" s="2" t="n"/>
+      <c r="D942" s="3" t="n"/>
+      <c r="Q942" s="3" t="n"/>
     </row>
     <row r="943">
-      <c r="D943" s="2" t="n"/>
-      <c r="Q943" s="2" t="n"/>
+      <c r="D943" s="3" t="n"/>
+      <c r="Q943" s="3" t="n"/>
     </row>
     <row r="944">
-      <c r="D944" s="2" t="n"/>
-      <c r="Q944" s="2" t="n"/>
+      <c r="D944" s="3" t="n"/>
+      <c r="Q944" s="3" t="n"/>
     </row>
     <row r="945">
-      <c r="D945" s="2" t="n"/>
-      <c r="Q945" s="2" t="n"/>
+      <c r="D945" s="3" t="n"/>
+      <c r="Q945" s="3" t="n"/>
     </row>
     <row r="946">
-      <c r="D946" s="2" t="n"/>
-      <c r="Q946" s="2" t="n"/>
+      <c r="D946" s="3" t="n"/>
+      <c r="Q946" s="3" t="n"/>
     </row>
     <row r="947">
-      <c r="D947" s="2" t="n"/>
-      <c r="Q947" s="2" t="n"/>
+      <c r="D947" s="3" t="n"/>
+      <c r="Q947" s="3" t="n"/>
     </row>
     <row r="948">
-      <c r="D948" s="2" t="n"/>
-      <c r="Q948" s="2" t="n"/>
+      <c r="D948" s="3" t="n"/>
+      <c r="Q948" s="3" t="n"/>
     </row>
     <row r="949">
-      <c r="D949" s="2" t="n"/>
-      <c r="Q949" s="2" t="n"/>
+      <c r="D949" s="3" t="n"/>
+      <c r="Q949" s="3" t="n"/>
     </row>
     <row r="950">
-      <c r="D950" s="2" t="n"/>
-      <c r="Q950" s="2" t="n"/>
+      <c r="D950" s="3" t="n"/>
+      <c r="Q950" s="3" t="n"/>
     </row>
     <row r="951">
-      <c r="D951" s="2" t="n"/>
-      <c r="Q951" s="2" t="n"/>
+      <c r="D951" s="3" t="n"/>
+      <c r="Q951" s="3" t="n"/>
     </row>
     <row r="952">
-      <c r="D952" s="2" t="n"/>
-      <c r="Q952" s="2" t="n"/>
+      <c r="D952" s="3" t="n"/>
+      <c r="Q952" s="3" t="n"/>
     </row>
     <row r="953">
-      <c r="D953" s="2" t="n"/>
-      <c r="Q953" s="2" t="n"/>
+      <c r="D953" s="3" t="n"/>
+      <c r="Q953" s="3" t="n"/>
     </row>
     <row r="954">
-      <c r="D954" s="2" t="n"/>
-      <c r="Q954" s="2" t="n"/>
+      <c r="D954" s="3" t="n"/>
+      <c r="Q954" s="3" t="n"/>
     </row>
     <row r="955">
-      <c r="D955" s="2" t="n"/>
-      <c r="Q955" s="2" t="n"/>
+      <c r="D955" s="3" t="n"/>
+      <c r="Q955" s="3" t="n"/>
     </row>
     <row r="956">
-      <c r="D956" s="2" t="n"/>
-      <c r="Q956" s="2" t="n"/>
+      <c r="D956" s="3" t="n"/>
+      <c r="Q956" s="3" t="n"/>
     </row>
     <row r="957">
-      <c r="D957" s="2" t="n"/>
-      <c r="Q957" s="2" t="n"/>
+      <c r="D957" s="3" t="n"/>
+      <c r="Q957" s="3" t="n"/>
     </row>
     <row r="958">
-      <c r="D958" s="2" t="n"/>
-      <c r="Q958" s="2" t="n"/>
+      <c r="D958" s="3" t="n"/>
+      <c r="Q958" s="3" t="n"/>
     </row>
     <row r="959">
-      <c r="D959" s="2" t="n"/>
-      <c r="Q959" s="2" t="n"/>
+      <c r="D959" s="3" t="n"/>
+      <c r="Q959" s="3" t="n"/>
     </row>
     <row r="960">
-      <c r="D960" s="2" t="n"/>
-      <c r="Q960" s="2" t="n"/>
+      <c r="D960" s="3" t="n"/>
+      <c r="Q960" s="3" t="n"/>
     </row>
     <row r="961">
-      <c r="D961" s="2" t="n"/>
-      <c r="Q961" s="2" t="n"/>
+      <c r="D961" s="3" t="n"/>
+      <c r="Q961" s="3" t="n"/>
     </row>
     <row r="962">
-      <c r="D962" s="2" t="n"/>
-      <c r="Q962" s="2" t="n"/>
+      <c r="D962" s="3" t="n"/>
+      <c r="Q962" s="3" t="n"/>
     </row>
     <row r="963">
-      <c r="D963" s="2" t="n"/>
-      <c r="Q963" s="2" t="n"/>
+      <c r="D963" s="3" t="n"/>
+      <c r="Q963" s="3" t="n"/>
     </row>
     <row r="964">
-      <c r="D964" s="2" t="n"/>
-      <c r="Q964" s="2" t="n"/>
+      <c r="D964" s="3" t="n"/>
+      <c r="Q964" s="3" t="n"/>
     </row>
     <row r="965">
-      <c r="D965" s="2" t="n"/>
-      <c r="Q965" s="2" t="n"/>
+      <c r="D965" s="3" t="n"/>
+      <c r="Q965" s="3" t="n"/>
     </row>
     <row r="966">
-      <c r="D966" s="2" t="n"/>
-      <c r="Q966" s="2" t="n"/>
+      <c r="D966" s="3" t="n"/>
+      <c r="Q966" s="3" t="n"/>
     </row>
     <row r="967">
-      <c r="D967" s="2" t="n"/>
-      <c r="Q967" s="2" t="n"/>
+      <c r="D967" s="3" t="n"/>
+      <c r="Q967" s="3" t="n"/>
     </row>
     <row r="968">
-      <c r="D968" s="2" t="n"/>
-      <c r="Q968" s="2" t="n"/>
+      <c r="D968" s="3" t="n"/>
+      <c r="Q968" s="3" t="n"/>
     </row>
     <row r="969">
-      <c r="D969" s="2" t="n"/>
-      <c r="Q969" s="2" t="n"/>
+      <c r="D969" s="3" t="n"/>
+      <c r="Q969" s="3" t="n"/>
     </row>
     <row r="970">
-      <c r="D970" s="2" t="n"/>
-      <c r="Q970" s="2" t="n"/>
+      <c r="D970" s="3" t="n"/>
+      <c r="Q970" s="3" t="n"/>
     </row>
     <row r="971">
-      <c r="D971" s="2" t="n"/>
-      <c r="Q971" s="2" t="n"/>
+      <c r="D971" s="3" t="n"/>
+      <c r="Q971" s="3" t="n"/>
     </row>
     <row r="972">
-      <c r="D972" s="2" t="n"/>
-      <c r="Q972" s="2" t="n"/>
+      <c r="D972" s="3" t="n"/>
+      <c r="Q972" s="3" t="n"/>
     </row>
     <row r="973">
-      <c r="D973" s="2" t="n"/>
-      <c r="Q973" s="2" t="n"/>
+      <c r="D973" s="3" t="n"/>
+      <c r="Q973" s="3" t="n"/>
     </row>
     <row r="974">
-      <c r="D974" s="2" t="n"/>
-      <c r="Q974" s="2" t="n"/>
+      <c r="D974" s="3" t="n"/>
+      <c r="Q974" s="3" t="n"/>
     </row>
     <row r="975">
-      <c r="D975" s="2" t="n"/>
-      <c r="Q975" s="2" t="n"/>
+      <c r="D975" s="3" t="n"/>
+      <c r="Q975" s="3" t="n"/>
     </row>
     <row r="976">
-      <c r="D976" s="2" t="n"/>
-      <c r="Q976" s="2" t="n"/>
+      <c r="D976" s="3" t="n"/>
+      <c r="Q976" s="3" t="n"/>
     </row>
     <row r="977">
-      <c r="D977" s="2" t="n"/>
-      <c r="Q977" s="2" t="n"/>
+      <c r="D977" s="3" t="n"/>
+      <c r="Q977" s="3" t="n"/>
     </row>
     <row r="978">
-      <c r="D978" s="2" t="n"/>
-      <c r="Q978" s="2" t="n"/>
+      <c r="D978" s="3" t="n"/>
+      <c r="Q978" s="3" t="n"/>
     </row>
     <row r="979">
-      <c r="D979" s="2" t="n"/>
-      <c r="Q979" s="2" t="n"/>
+      <c r="D979" s="3" t="n"/>
+      <c r="Q979" s="3" t="n"/>
     </row>
     <row r="980">
-      <c r="D980" s="2" t="n"/>
-      <c r="Q980" s="2" t="n"/>
+      <c r="D980" s="3" t="n"/>
+      <c r="Q980" s="3" t="n"/>
     </row>
     <row r="981">
-      <c r="D981" s="2" t="n"/>
-      <c r="Q981" s="2" t="n"/>
+      <c r="D981" s="3" t="n"/>
+      <c r="Q981" s="3" t="n"/>
     </row>
     <row r="982">
-      <c r="D982" s="2" t="n"/>
-      <c r="Q982" s="2" t="n"/>
+      <c r="D982" s="3" t="n"/>
+      <c r="Q982" s="3" t="n"/>
     </row>
     <row r="983">
-      <c r="D983" s="2" t="n"/>
-      <c r="Q983" s="2" t="n"/>
+      <c r="D983" s="3" t="n"/>
+      <c r="Q983" s="3" t="n"/>
     </row>
     <row r="984">
-      <c r="D984" s="2" t="n"/>
-      <c r="Q984" s="2" t="n"/>
+      <c r="D984" s="3" t="n"/>
+      <c r="Q984" s="3" t="n"/>
     </row>
     <row r="985">
-      <c r="D985" s="2" t="n"/>
-      <c r="Q985" s="2" t="n"/>
+      <c r="D985" s="3" t="n"/>
+      <c r="Q985" s="3" t="n"/>
     </row>
     <row r="986">
-      <c r="D986" s="2" t="n"/>
-      <c r="Q986" s="2" t="n"/>
+      <c r="D986" s="3" t="n"/>
+      <c r="Q986" s="3" t="n"/>
     </row>
     <row r="987">
-      <c r="D987" s="2" t="n"/>
-      <c r="Q987" s="2" t="n"/>
+      <c r="D987" s="3" t="n"/>
+      <c r="Q987" s="3" t="n"/>
     </row>
     <row r="988">
-      <c r="D988" s="2" t="n"/>
-      <c r="Q988" s="2" t="n"/>
+      <c r="D988" s="3" t="n"/>
+      <c r="Q988" s="3" t="n"/>
     </row>
     <row r="989">
-      <c r="D989" s="2" t="n"/>
-      <c r="Q989" s="2" t="n"/>
+      <c r="D989" s="3" t="n"/>
+      <c r="Q989" s="3" t="n"/>
     </row>
     <row r="990">
-      <c r="D990" s="2" t="n"/>
-      <c r="Q990" s="2" t="n"/>
+      <c r="D990" s="3" t="n"/>
+      <c r="Q990" s="3" t="n"/>
     </row>
     <row r="991">
-      <c r="D991" s="2" t="n"/>
-      <c r="Q991" s="2" t="n"/>
+      <c r="D991" s="3" t="n"/>
+      <c r="Q991" s="3" t="n"/>
     </row>
     <row r="992">
-      <c r="D992" s="2" t="n"/>
-      <c r="Q992" s="2" t="n"/>
+      <c r="D992" s="3" t="n"/>
+      <c r="Q992" s="3" t="n"/>
     </row>
     <row r="993">
-      <c r="D993" s="2" t="n"/>
-      <c r="Q993" s="2" t="n"/>
+      <c r="D993" s="3" t="n"/>
+      <c r="Q993" s="3" t="n"/>
     </row>
     <row r="994">
-      <c r="D994" s="2" t="n"/>
-      <c r="Q994" s="2" t="n"/>
+      <c r="D994" s="3" t="n"/>
+      <c r="Q994" s="3" t="n"/>
     </row>
     <row r="995">
-      <c r="D995" s="2" t="n"/>
-      <c r="Q995" s="2" t="n"/>
+      <c r="D995" s="3" t="n"/>
+      <c r="Q995" s="3" t="n"/>
     </row>
     <row r="996">
-      <c r="D996" s="2" t="n"/>
-      <c r="Q996" s="2" t="n"/>
+      <c r="D996" s="3" t="n"/>
+      <c r="Q996" s="3" t="n"/>
     </row>
     <row r="997">
-      <c r="D997" s="2" t="n"/>
-      <c r="Q997" s="2" t="n"/>
+      <c r="D997" s="3" t="n"/>
+      <c r="Q997" s="3" t="n"/>
     </row>
     <row r="998">
-      <c r="D998" s="2" t="n"/>
-      <c r="Q998" s="2" t="n"/>
+      <c r="D998" s="3" t="n"/>
+      <c r="Q998" s="3" t="n"/>
     </row>
     <row r="999">
-      <c r="D999" s="2" t="n"/>
-      <c r="Q999" s="2" t="n"/>
+      <c r="D999" s="3" t="n"/>
+      <c r="Q999" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
